--- a/reports/paper_trade_trx.xlsx
+++ b/reports/paper_trade_trx.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="225">
   <si>
     <t>NAV</t>
   </si>
@@ -36,7 +36,7 @@
     <t>last_updated</t>
   </si>
   <si>
-    <t>2026-10-05 18:01:01</t>
+    <t>2026-10-06 18:00:56</t>
   </si>
   <si>
     <t>pf_id</t>
@@ -69,6 +69,9 @@
     <t>date</t>
   </si>
   <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
     <t>2026-10-05</t>
   </si>
   <si>
@@ -78,6 +81,9 @@
     <t>2026-09-29</t>
   </si>
   <si>
+    <t>AMAT</t>
+  </si>
+  <si>
     <t>AAPL</t>
   </si>
   <si>
@@ -109,6 +115,9 @@
   </si>
   <si>
     <t>initial</t>
+  </si>
+  <si>
+    <t>2026-10-06_53d2d3c2d4f2ff367a516a1f406e1bbb</t>
   </si>
   <si>
     <t>2026-10-05_59e0a8bb4acd7dbfa1963226e5a0766c</t>
@@ -1206,7 +1215,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>9970</v>
+        <v>9951</v>
       </c>
       <c r="C2" s="2">
         <v>100</v>
@@ -1230,7 +1239,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>9970</v>
+        <v>9951</v>
       </c>
       <c r="C4" s="2">
         <v>100</v>
@@ -1301,7 +1310,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
@@ -1347,42 +1356,42 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>-332.7950134277344</v>
+        <v>-546</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>-52.58</v>
+        <v>-332.7950134277344</v>
       </c>
       <c r="G3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1393,157 +1402,157 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>-733.2050170898438</v>
+        <v>-52.58</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>-236.0549926757812</v>
+        <v>-733.2050170898438</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>-124.1699981689453</v>
+        <v>-236.0549926757812</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>-636.4500122070312</v>
+        <v>-124.1699981689453</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>-290</v>
+        <v>-636.4500122070312</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E9">
-        <v>-186.384994506836</v>
+        <v>-290</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E10">
-        <v>-406.4700012207031</v>
+        <v>-186.384994506836</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1553,23 +1562,46 @@
       <c r="B11" t="s">
         <v>2</v>
       </c>
-      <c r="C11">
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11">
+        <v>-406.4700012207031</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12">
         <v>10000</v>
       </c>
-      <c r="H11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J11" t="s">
-        <v>40</v>
+      <c r="H12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B11">
+  <conditionalFormatting sqref="B2:B12">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>$B2="option"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C11">
+  <conditionalFormatting sqref="C2:C12">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1577,7 +1609,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E11">
+  <conditionalFormatting sqref="E2:E12">
     <cfRule type="cellIs" dxfId="4" priority="4" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1585,7 +1617,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F11">
+  <conditionalFormatting sqref="F2:F12">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1593,7 +1625,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G11">
+  <conditionalFormatting sqref="G2:G12">
     <cfRule type="cellIs" dxfId="4" priority="8" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1607,7 +1639,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:GA4"/>
+  <dimension ref="A1:GA5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
@@ -1615,10 +1647,10 @@
   <sheetData>
     <row r="1" spans="1:183">
       <c r="A1" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>3</v>
@@ -1627,541 +1659,541 @@
         <v>8</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AL1" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="BE1" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="BF1" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="BL1" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="BM1" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="BN1" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="BO1" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="BP1" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="BQ1" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="BR1" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="BS1" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BT1" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="BU1" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="BV1" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="BW1" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="BX1" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="BY1" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="BZ1" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="CA1" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="CB1" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="CC1" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="CD1" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="CE1" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="CF1" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="CH1" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="CI1" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="CJ1" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="CK1" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="CL1" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="CM1" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="CN1" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="CO1" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="CP1" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="CQ1" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="CR1" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="CS1" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="CT1" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="CU1" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="CV1" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="CW1" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="CX1" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="CY1" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="CZ1" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="DA1" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="DB1" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="DC1" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="DD1" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="DE1" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="DF1" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="DG1" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="DH1" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="DI1" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="DJ1" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="DK1" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="DL1" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="DM1" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="DN1" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="DO1" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="DP1" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="DQ1" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="DR1" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="DS1" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="DT1" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="DU1" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="DV1" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="DW1" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="DX1" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="DY1" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="DZ1" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="EA1" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="EB1" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="EC1" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="ED1" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="EE1" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="EF1" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="EG1" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="EH1" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="EI1" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="EJ1" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EK1" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="EL1" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="EM1" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="EN1" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="EO1" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="EP1" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EQ1" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="ER1" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="ES1" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="ET1" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="EU1" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="EV1" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="EW1" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="EX1" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EY1" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EZ1" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="FA1" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="FB1" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="FC1" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="FD1" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="FE1" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="FF1" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="FG1" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="FH1" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="FI1" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="FJ1" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="FK1" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="FL1" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="FM1" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="FN1" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="FO1" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="FP1" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="FQ1" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="FR1" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="FS1" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="FT1" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="FU1" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="FV1" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="FW1" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="FX1" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="FY1" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="FZ1" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="GA1" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:183">
@@ -2169,46 +2201,43 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>9970.279909493622</v>
+        <v>9950.788089754853</v>
       </c>
       <c r="C2">
-        <v>2464.739893319305</v>
+        <v>1918.657993319305</v>
       </c>
       <c r="D2">
-        <v>-1612.271831359497</v>
+        <v>-546.0819</v>
       </c>
       <c r="E2">
         <v>10000</v>
       </c>
       <c r="F2">
-        <v>-0.00297200905063788</v>
+        <v>-0.004921191024514715</v>
       </c>
       <c r="G2">
-        <v>0.004000164794920671</v>
+        <v>-0.1015996582031256</v>
       </c>
       <c r="H2">
-        <v>-0.001029921399637063</v>
+        <v>-0.001922883262771803</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>-332.7950134277344</v>
-      </c>
       <c r="K2">
-        <v>332.8900146484375</v>
+        <v>333.6300048828125</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <v>2</v>
       </c>
       <c r="N2">
-        <v>0.095001220703125</v>
+        <v>0.834991455078125</v>
       </c>
       <c r="O2">
-        <v>0.0002854646760617197</v>
+        <v>0.00250902634170469</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -2241,7 +2270,7 @@
         <v>1</v>
       </c>
       <c r="AM2">
-        <v>741.9000244140625</v>
+        <v>738.8800048828125</v>
       </c>
       <c r="AN2">
         <v>0</v>
@@ -2250,10 +2279,10 @@
         <v>1</v>
       </c>
       <c r="AP2">
-        <v>8.69500732421875</v>
+        <v>5.67498779296875</v>
       </c>
       <c r="AQ2">
-        <v>0.01185890320108562</v>
+        <v>0.007739974032765495</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2268,7 +2297,7 @@
         <v>1</v>
       </c>
       <c r="BA2">
-        <v>238.8999938964844</v>
+        <v>239.2400054931641</v>
       </c>
       <c r="BB2">
         <v>0</v>
@@ -2277,10 +2306,10 @@
         <v>4</v>
       </c>
       <c r="BD2">
-        <v>2.845001220703153</v>
+        <v>3.185012817382841</v>
       </c>
       <c r="BE2">
-        <v>0.0120522814978572</v>
+        <v>0.01349267296268297</v>
       </c>
       <c r="BF2">
         <v>0</v>
@@ -2294,23 +2323,20 @@
       <c r="BM2">
         <v>1</v>
       </c>
-      <c r="BN2">
-        <v>-52.58</v>
-      </c>
       <c r="BO2">
-        <v>54.40999984741211</v>
+        <v>54.61000061035156</v>
       </c>
       <c r="BP2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
         <v>18</v>
       </c>
       <c r="BR2">
-        <v>1.829999847412111</v>
+        <v>2.030000610351564</v>
       </c>
       <c r="BS2">
-        <v>0.03480410512385146</v>
+        <v>0.03860784728702105</v>
       </c>
       <c r="BT2">
         <v>0</v>
@@ -2334,7 +2360,7 @@
         <v>1</v>
       </c>
       <c r="CJ2">
-        <v>116.1900024414062</v>
+        <v>112.5</v>
       </c>
       <c r="CK2">
         <v>0</v>
@@ -2343,10 +2369,10 @@
         <v>8</v>
       </c>
       <c r="CM2">
-        <v>-7.979995727539091</v>
+        <v>-11.66999816894533</v>
       </c>
       <c r="CN2">
-        <v>-0.06426669763400927</v>
+        <v>-0.09398404075892119</v>
       </c>
       <c r="CO2">
         <v>0</v>
@@ -2397,7 +2423,7 @@
         <v>1</v>
       </c>
       <c r="DZ2">
-        <v>631.75</v>
+        <v>649.4199829101562</v>
       </c>
       <c r="EA2">
         <v>0</v>
@@ -2406,16 +2432,16 @@
         <v>1</v>
       </c>
       <c r="EC2">
-        <v>-4.70001220703125</v>
+        <v>12.969970703125</v>
       </c>
       <c r="ED2">
-        <v>-0.007384731113026288</v>
+        <v>0.02037861647319139</v>
       </c>
       <c r="EE2">
         <v>1</v>
       </c>
       <c r="EG2">
-        <v>294.8999938964844</v>
+        <v>297.2300109863281</v>
       </c>
       <c r="EH2">
         <v>0</v>
@@ -2424,10 +2450,10 @@
         <v>3</v>
       </c>
       <c r="EJ2">
-        <v>4.899993896484375</v>
+        <v>7.230010986328125</v>
       </c>
       <c r="EK2">
-        <v>0.01689653067753238</v>
+        <v>0.02493107236664871</v>
       </c>
       <c r="EL2">
         <v>0</v>
@@ -2451,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="FB2">
-        <v>180.7899932861328</v>
+        <v>181.0299987792969</v>
       </c>
       <c r="FC2">
         <v>0</v>
@@ -2460,16 +2486,16 @@
         <v>5</v>
       </c>
       <c r="FE2">
-        <v>-5.595001220703153</v>
+        <v>-5.354995727539091</v>
       </c>
       <c r="FF2">
-        <v>-0.03001851750730899</v>
+        <v>-0.02873083072866511</v>
       </c>
       <c r="FG2">
         <v>1</v>
       </c>
       <c r="FI2">
-        <v>406.4800109863281</v>
+        <v>404.760009765625</v>
       </c>
       <c r="FJ2">
         <v>0</v>
@@ -2478,10 +2504,10 @@
         <v>2</v>
       </c>
       <c r="FL2">
-        <v>0.010009765625</v>
+        <v>-1.709991455078125</v>
       </c>
       <c r="FM2">
-        <v>2.46260870295778E-05</v>
+        <v>-0.004206931507719447</v>
       </c>
       <c r="FN2">
         <v>0</v>
@@ -2493,13 +2519,25 @@
         <v>0</v>
       </c>
       <c r="FU2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FV2">
+        <v>-546</v>
+      </c>
+      <c r="FW2">
+        <v>530.27001953125</v>
       </c>
       <c r="FX2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FY2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FZ2">
+        <v>-15.72998046875</v>
+      </c>
+      <c r="GA2">
+        <v>-0.02880948803800365</v>
       </c>
     </row>
     <row r="3" spans="1:183">
@@ -2507,28 +2545,31 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>9919.091680733491</v>
+        <v>9970.279909493622</v>
       </c>
       <c r="C3">
-        <v>4077.011724678802</v>
+        <v>2464.739893319305</v>
       </c>
       <c r="D3">
-        <v>-5922.988275321198</v>
+        <v>-1612.271831359497</v>
       </c>
       <c r="E3">
         <v>10000</v>
       </c>
       <c r="F3">
-        <v>-0.008090831926650943</v>
+        <v>-0.00297200905063788</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>-332.7950134277344</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -2560,11 +2601,8 @@
       <c r="AK3">
         <v>1</v>
       </c>
-      <c r="AL3">
-        <v>-733.2050170898438</v>
-      </c>
       <c r="AN3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO3">
         <v>1</v>
@@ -2581,11 +2619,8 @@
       <c r="AY3">
         <v>1</v>
       </c>
-      <c r="AZ3">
-        <v>-236.0549926757812</v>
-      </c>
       <c r="BB3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BC3">
         <v>4</v>
@@ -2600,13 +2635,16 @@
         <v>0</v>
       </c>
       <c r="BM3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BN3">
+        <v>-52.58</v>
       </c>
       <c r="BP3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BQ3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BT3">
         <v>0</v>
@@ -2629,11 +2667,8 @@
       <c r="CH3">
         <v>1</v>
       </c>
-      <c r="CI3">
-        <v>-124.1699981689453</v>
-      </c>
       <c r="CK3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CL3">
         <v>8</v>
@@ -2686,11 +2721,8 @@
       <c r="DX3">
         <v>1</v>
       </c>
-      <c r="DY3">
-        <v>-636.4500122070312</v>
-      </c>
       <c r="EA3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB3">
         <v>1</v>
@@ -2698,11 +2730,8 @@
       <c r="EE3">
         <v>1</v>
       </c>
-      <c r="EF3">
-        <v>-290</v>
-      </c>
       <c r="EH3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="EI3">
         <v>3</v>
@@ -2728,11 +2757,8 @@
       <c r="EZ3">
         <v>1</v>
       </c>
-      <c r="FA3">
-        <v>-186.384994506836</v>
-      </c>
       <c r="FC3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="FD3">
         <v>5</v>
@@ -2740,11 +2766,8 @@
       <c r="FG3">
         <v>1</v>
       </c>
-      <c r="FH3">
-        <v>-406.4700012207031</v>
-      </c>
       <c r="FJ3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="FK3">
         <v>2</v>
@@ -2773,19 +2796,19 @@
         <v>19</v>
       </c>
       <c r="B4">
-        <v>10000</v>
+        <v>9919.091680733491</v>
       </c>
       <c r="C4">
-        <v>10000</v>
+        <v>4077.011724678802</v>
       </c>
       <c r="D4">
-        <v>10000</v>
+        <v>-5922.988275321198</v>
       </c>
       <c r="E4">
         <v>10000</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>-0.008090831926650943</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2824,13 +2847,16 @@
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AL4">
+        <v>-733.2050170898438</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2842,13 +2868,16 @@
         <v>0</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AZ4">
+        <v>-236.0549926757812</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF4">
         <v>0</v>
@@ -2887,13 +2916,16 @@
         <v>0</v>
       </c>
       <c r="CH4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CI4">
+        <v>-124.1699981689453</v>
       </c>
       <c r="CK4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CL4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CO4">
         <v>0</v>
@@ -2941,22 +2973,28 @@
         <v>0</v>
       </c>
       <c r="DX4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="DY4">
+        <v>-636.4500122070312</v>
       </c>
       <c r="EA4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EB4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EE4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="EF4">
+        <v>-290</v>
       </c>
       <c r="EH4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="EI4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="EL4">
         <v>0</v>
@@ -2977,22 +3015,28 @@
         <v>0</v>
       </c>
       <c r="EZ4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FA4">
+        <v>-186.384994506836</v>
       </c>
       <c r="FC4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="FD4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="FG4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FH4">
+        <v>-406.4700012207031</v>
       </c>
       <c r="FJ4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="FK4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="FN4">
         <v>0</v>
@@ -3010,11 +3054,256 @@
         <v>0</v>
       </c>
       <c r="FY4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:183">
+      <c r="A5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>10000</v>
+      </c>
+      <c r="C5">
+        <v>10000</v>
+      </c>
+      <c r="D5">
+        <v>10000</v>
+      </c>
+      <c r="E5">
+        <v>10000</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CD5">
+        <v>0</v>
+      </c>
+      <c r="CE5">
+        <v>0</v>
+      </c>
+      <c r="CH5">
+        <v>0</v>
+      </c>
+      <c r="CK5">
+        <v>0</v>
+      </c>
+      <c r="CL5">
+        <v>0</v>
+      </c>
+      <c r="CO5">
+        <v>0</v>
+      </c>
+      <c r="CR5">
+        <v>0</v>
+      </c>
+      <c r="CS5">
+        <v>0</v>
+      </c>
+      <c r="CV5">
+        <v>0</v>
+      </c>
+      <c r="CY5">
+        <v>0</v>
+      </c>
+      <c r="CZ5">
+        <v>0</v>
+      </c>
+      <c r="DC5">
+        <v>0</v>
+      </c>
+      <c r="DF5">
+        <v>0</v>
+      </c>
+      <c r="DG5">
+        <v>0</v>
+      </c>
+      <c r="DJ5">
+        <v>0</v>
+      </c>
+      <c r="DM5">
+        <v>0</v>
+      </c>
+      <c r="DN5">
+        <v>0</v>
+      </c>
+      <c r="DQ5">
+        <v>0</v>
+      </c>
+      <c r="DT5">
+        <v>0</v>
+      </c>
+      <c r="DU5">
+        <v>0</v>
+      </c>
+      <c r="DX5">
+        <v>0</v>
+      </c>
+      <c r="EA5">
+        <v>0</v>
+      </c>
+      <c r="EB5">
+        <v>0</v>
+      </c>
+      <c r="EE5">
+        <v>0</v>
+      </c>
+      <c r="EH5">
+        <v>0</v>
+      </c>
+      <c r="EI5">
+        <v>0</v>
+      </c>
+      <c r="EL5">
+        <v>0</v>
+      </c>
+      <c r="EO5">
+        <v>0</v>
+      </c>
+      <c r="EP5">
+        <v>0</v>
+      </c>
+      <c r="ES5">
+        <v>0</v>
+      </c>
+      <c r="EV5">
+        <v>0</v>
+      </c>
+      <c r="EW5">
+        <v>0</v>
+      </c>
+      <c r="EZ5">
+        <v>0</v>
+      </c>
+      <c r="FC5">
+        <v>0</v>
+      </c>
+      <c r="FD5">
+        <v>0</v>
+      </c>
+      <c r="FG5">
+        <v>0</v>
+      </c>
+      <c r="FJ5">
+        <v>0</v>
+      </c>
+      <c r="FK5">
+        <v>0</v>
+      </c>
+      <c r="FN5">
+        <v>0</v>
+      </c>
+      <c r="FQ5">
+        <v>0</v>
+      </c>
+      <c r="FR5">
+        <v>0</v>
+      </c>
+      <c r="FU5">
+        <v>0</v>
+      </c>
+      <c r="FX5">
+        <v>0</v>
+      </c>
+      <c r="FY5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AA2:AA4">
+  <conditionalFormatting sqref="AA2:AA5">
     <cfRule type="cellIs" dxfId="4" priority="25" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3022,7 +3311,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE2:AE4">
+  <conditionalFormatting sqref="AE2:AE5">
     <cfRule type="cellIs" dxfId="4" priority="27" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3030,7 +3319,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF2:AF4">
+  <conditionalFormatting sqref="AF2:AF5">
     <cfRule type="cellIs" dxfId="4" priority="29" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3038,7 +3327,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG2:AG4">
+  <conditionalFormatting sqref="AG2:AG5">
     <cfRule type="cellIs" dxfId="4" priority="31" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3046,7 +3335,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH2:AH4">
+  <conditionalFormatting sqref="AH2:AH5">
     <cfRule type="cellIs" dxfId="4" priority="33" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3054,7 +3343,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL2:AL4">
+  <conditionalFormatting sqref="AL2:AL5">
     <cfRule type="cellIs" dxfId="4" priority="35" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3062,7 +3351,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM2:AM4">
+  <conditionalFormatting sqref="AM2:AM5">
     <cfRule type="cellIs" dxfId="4" priority="37" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3070,7 +3359,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AN2:AN4">
+  <conditionalFormatting sqref="AN2:AN5">
     <cfRule type="cellIs" dxfId="4" priority="39" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3078,7 +3367,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AO2:AO4">
+  <conditionalFormatting sqref="AO2:AO5">
     <cfRule type="cellIs" dxfId="4" priority="41" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3086,7 +3375,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AS2:AS4">
+  <conditionalFormatting sqref="AS2:AS5">
     <cfRule type="cellIs" dxfId="4" priority="43" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3094,7 +3383,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AT2:AT4">
+  <conditionalFormatting sqref="AT2:AT5">
     <cfRule type="cellIs" dxfId="4" priority="45" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3102,7 +3391,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU2:AU4">
+  <conditionalFormatting sqref="AU2:AU5">
     <cfRule type="cellIs" dxfId="4" priority="47" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3110,7 +3399,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AV2:AV4">
+  <conditionalFormatting sqref="AV2:AV5">
     <cfRule type="cellIs" dxfId="4" priority="49" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3118,7 +3407,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AZ2:AZ4">
+  <conditionalFormatting sqref="AZ2:AZ5">
     <cfRule type="cellIs" dxfId="4" priority="51" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3126,7 +3415,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BA2:BA4">
+  <conditionalFormatting sqref="BA2:BA5">
     <cfRule type="cellIs" dxfId="4" priority="53" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3134,7 +3423,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB2:BB4">
+  <conditionalFormatting sqref="BB2:BB5">
     <cfRule type="cellIs" dxfId="4" priority="55" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3142,7 +3431,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BC2:BC4">
+  <conditionalFormatting sqref="BC2:BC5">
     <cfRule type="cellIs" dxfId="4" priority="57" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3150,7 +3439,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BG2:BG4">
+  <conditionalFormatting sqref="BG2:BG5">
     <cfRule type="cellIs" dxfId="4" priority="59" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3158,7 +3447,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BH2:BH4">
+  <conditionalFormatting sqref="BH2:BH5">
     <cfRule type="cellIs" dxfId="4" priority="61" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3166,7 +3455,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BI2:BI4">
+  <conditionalFormatting sqref="BI2:BI5">
     <cfRule type="cellIs" dxfId="4" priority="63" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3174,7 +3463,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BJ2:BJ4">
+  <conditionalFormatting sqref="BJ2:BJ5">
     <cfRule type="cellIs" dxfId="4" priority="65" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3182,7 +3471,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BN2:BN4">
+  <conditionalFormatting sqref="BN2:BN5">
     <cfRule type="cellIs" dxfId="4" priority="67" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3190,7 +3479,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BO2:BO4">
+  <conditionalFormatting sqref="BO2:BO5">
     <cfRule type="cellIs" dxfId="4" priority="69" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3198,7 +3487,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BP2:BP4">
+  <conditionalFormatting sqref="BP2:BP5">
     <cfRule type="cellIs" dxfId="4" priority="71" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3206,7 +3495,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BQ2:BQ4">
+  <conditionalFormatting sqref="BQ2:BQ5">
     <cfRule type="cellIs" dxfId="4" priority="73" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3214,7 +3503,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BU2:BU4">
+  <conditionalFormatting sqref="BU2:BU5">
     <cfRule type="cellIs" dxfId="4" priority="75" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3222,7 +3511,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BV2:BV4">
+  <conditionalFormatting sqref="BV2:BV5">
     <cfRule type="cellIs" dxfId="4" priority="77" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3230,7 +3519,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BW2:BW4">
+  <conditionalFormatting sqref="BW2:BW5">
     <cfRule type="cellIs" dxfId="4" priority="79" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3238,7 +3527,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BX2:BX4">
+  <conditionalFormatting sqref="BX2:BX5">
     <cfRule type="cellIs" dxfId="4" priority="81" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3246,7 +3535,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CB2:CB4">
+  <conditionalFormatting sqref="CB2:CB5">
     <cfRule type="cellIs" dxfId="4" priority="83" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3254,7 +3543,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CC2:CC4">
+  <conditionalFormatting sqref="CC2:CC5">
     <cfRule type="cellIs" dxfId="4" priority="85" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3262,7 +3551,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CD2:CD4">
+  <conditionalFormatting sqref="CD2:CD5">
     <cfRule type="cellIs" dxfId="4" priority="87" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3270,7 +3559,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CE2:CE4">
+  <conditionalFormatting sqref="CE2:CE5">
     <cfRule type="cellIs" dxfId="4" priority="89" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3278,7 +3567,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CI2:CI4">
+  <conditionalFormatting sqref="CI2:CI5">
     <cfRule type="cellIs" dxfId="4" priority="91" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3286,7 +3575,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CJ2:CJ4">
+  <conditionalFormatting sqref="CJ2:CJ5">
     <cfRule type="cellIs" dxfId="4" priority="93" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3294,7 +3583,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CK2:CK4">
+  <conditionalFormatting sqref="CK2:CK5">
     <cfRule type="cellIs" dxfId="4" priority="95" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3302,7 +3591,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CL2:CL4">
+  <conditionalFormatting sqref="CL2:CL5">
     <cfRule type="cellIs" dxfId="4" priority="97" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3310,7 +3599,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CP2:CP4">
+  <conditionalFormatting sqref="CP2:CP5">
     <cfRule type="cellIs" dxfId="4" priority="99" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3318,7 +3607,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CQ2:CQ4">
+  <conditionalFormatting sqref="CQ2:CQ5">
     <cfRule type="cellIs" dxfId="4" priority="101" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3326,7 +3615,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CR2:CR4">
+  <conditionalFormatting sqref="CR2:CR5">
     <cfRule type="cellIs" dxfId="4" priority="103" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3334,7 +3623,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CS2:CS4">
+  <conditionalFormatting sqref="CS2:CS5">
     <cfRule type="cellIs" dxfId="4" priority="105" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3342,7 +3631,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CW2:CW4">
+  <conditionalFormatting sqref="CW2:CW5">
     <cfRule type="cellIs" dxfId="4" priority="107" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3350,7 +3639,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CX2:CX4">
+  <conditionalFormatting sqref="CX2:CX5">
     <cfRule type="cellIs" dxfId="4" priority="109" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3358,7 +3647,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CY2:CY4">
+  <conditionalFormatting sqref="CY2:CY5">
     <cfRule type="cellIs" dxfId="4" priority="111" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3366,7 +3655,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CZ2:CZ4">
+  <conditionalFormatting sqref="CZ2:CZ5">
     <cfRule type="cellIs" dxfId="4" priority="113" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3374,7 +3663,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4">
+  <conditionalFormatting sqref="D2:D5">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3382,7 +3671,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DD2:DD4">
+  <conditionalFormatting sqref="DD2:DD5">
     <cfRule type="cellIs" dxfId="4" priority="115" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3390,7 +3679,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DE2:DE4">
+  <conditionalFormatting sqref="DE2:DE5">
     <cfRule type="cellIs" dxfId="4" priority="117" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3398,7 +3687,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DF2:DF4">
+  <conditionalFormatting sqref="DF2:DF5">
     <cfRule type="cellIs" dxfId="4" priority="119" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3406,7 +3695,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DG2:DG4">
+  <conditionalFormatting sqref="DG2:DG5">
     <cfRule type="cellIs" dxfId="4" priority="121" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3414,7 +3703,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DK2:DK4">
+  <conditionalFormatting sqref="DK2:DK5">
     <cfRule type="cellIs" dxfId="4" priority="123" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3422,7 +3711,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DL2:DL4">
+  <conditionalFormatting sqref="DL2:DL5">
     <cfRule type="cellIs" dxfId="4" priority="125" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3430,7 +3719,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DM2:DM4">
+  <conditionalFormatting sqref="DM2:DM5">
     <cfRule type="cellIs" dxfId="4" priority="127" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3438,7 +3727,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DN2:DN4">
+  <conditionalFormatting sqref="DN2:DN5">
     <cfRule type="cellIs" dxfId="4" priority="129" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3446,7 +3735,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DR2:DR4">
+  <conditionalFormatting sqref="DR2:DR5">
     <cfRule type="cellIs" dxfId="4" priority="131" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3454,7 +3743,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DS2:DS4">
+  <conditionalFormatting sqref="DS2:DS5">
     <cfRule type="cellIs" dxfId="4" priority="133" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3462,7 +3751,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DT2:DT4">
+  <conditionalFormatting sqref="DT2:DT5">
     <cfRule type="cellIs" dxfId="4" priority="135" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3470,7 +3759,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DU2:DU4">
+  <conditionalFormatting sqref="DU2:DU5">
     <cfRule type="cellIs" dxfId="4" priority="137" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3478,7 +3767,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DY2:DY4">
+  <conditionalFormatting sqref="DY2:DY5">
     <cfRule type="cellIs" dxfId="4" priority="139" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3486,7 +3775,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DZ2:DZ4">
+  <conditionalFormatting sqref="DZ2:DZ5">
     <cfRule type="cellIs" dxfId="4" priority="141" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3494,7 +3783,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EA2:EA4">
+  <conditionalFormatting sqref="EA2:EA5">
     <cfRule type="cellIs" dxfId="4" priority="143" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3502,7 +3791,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EB2:EB4">
+  <conditionalFormatting sqref="EB2:EB5">
     <cfRule type="cellIs" dxfId="4" priority="145" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3510,7 +3799,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EF2:EF4">
+  <conditionalFormatting sqref="EF2:EF5">
     <cfRule type="cellIs" dxfId="4" priority="147" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3518,7 +3807,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EG2:EG4">
+  <conditionalFormatting sqref="EG2:EG5">
     <cfRule type="cellIs" dxfId="4" priority="149" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3526,7 +3815,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EH2:EH4">
+  <conditionalFormatting sqref="EH2:EH5">
     <cfRule type="cellIs" dxfId="4" priority="151" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3534,7 +3823,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EI2:EI4">
+  <conditionalFormatting sqref="EI2:EI5">
     <cfRule type="cellIs" dxfId="4" priority="153" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3542,7 +3831,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EM2:EM4">
+  <conditionalFormatting sqref="EM2:EM5">
     <cfRule type="cellIs" dxfId="4" priority="155" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3550,7 +3839,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EN2:EN4">
+  <conditionalFormatting sqref="EN2:EN5">
     <cfRule type="cellIs" dxfId="4" priority="157" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3558,7 +3847,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EO2:EO4">
+  <conditionalFormatting sqref="EO2:EO5">
     <cfRule type="cellIs" dxfId="4" priority="159" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3566,7 +3855,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EP2:EP4">
+  <conditionalFormatting sqref="EP2:EP5">
     <cfRule type="cellIs" dxfId="4" priority="161" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3574,7 +3863,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="ET2:ET4">
+  <conditionalFormatting sqref="ET2:ET5">
     <cfRule type="cellIs" dxfId="4" priority="163" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3582,7 +3871,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EU2:EU4">
+  <conditionalFormatting sqref="EU2:EU5">
     <cfRule type="cellIs" dxfId="4" priority="165" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3590,7 +3879,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EV2:EV4">
+  <conditionalFormatting sqref="EV2:EV5">
     <cfRule type="cellIs" dxfId="4" priority="167" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3598,7 +3887,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EW2:EW4">
+  <conditionalFormatting sqref="EW2:EW5">
     <cfRule type="cellIs" dxfId="4" priority="169" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3606,7 +3895,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FA2:FA4">
+  <conditionalFormatting sqref="FA2:FA5">
     <cfRule type="cellIs" dxfId="4" priority="171" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3614,7 +3903,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FB2:FB4">
+  <conditionalFormatting sqref="FB2:FB5">
     <cfRule type="cellIs" dxfId="4" priority="173" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3622,7 +3911,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FC2:FC4">
+  <conditionalFormatting sqref="FC2:FC5">
     <cfRule type="cellIs" dxfId="4" priority="175" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3630,7 +3919,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FD2:FD4">
+  <conditionalFormatting sqref="FD2:FD5">
     <cfRule type="cellIs" dxfId="4" priority="177" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3638,7 +3927,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FH2:FH4">
+  <conditionalFormatting sqref="FH2:FH5">
     <cfRule type="cellIs" dxfId="4" priority="179" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3646,7 +3935,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FI2:FI4">
+  <conditionalFormatting sqref="FI2:FI5">
     <cfRule type="cellIs" dxfId="4" priority="181" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3654,7 +3943,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FJ2:FJ4">
+  <conditionalFormatting sqref="FJ2:FJ5">
     <cfRule type="cellIs" dxfId="4" priority="183" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3662,7 +3951,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FK2:FK4">
+  <conditionalFormatting sqref="FK2:FK5">
     <cfRule type="cellIs" dxfId="4" priority="185" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3670,7 +3959,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FO2:FO4">
+  <conditionalFormatting sqref="FO2:FO5">
     <cfRule type="cellIs" dxfId="4" priority="187" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3678,7 +3967,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FP2:FP4">
+  <conditionalFormatting sqref="FP2:FP5">
     <cfRule type="cellIs" dxfId="4" priority="189" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3686,7 +3975,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FQ2:FQ4">
+  <conditionalFormatting sqref="FQ2:FQ5">
     <cfRule type="cellIs" dxfId="4" priority="191" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3694,7 +3983,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FR2:FR4">
+  <conditionalFormatting sqref="FR2:FR5">
     <cfRule type="cellIs" dxfId="4" priority="193" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3702,7 +3991,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FV2:FV4">
+  <conditionalFormatting sqref="FV2:FV5">
     <cfRule type="cellIs" dxfId="4" priority="195" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3710,7 +3999,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FW2:FW4">
+  <conditionalFormatting sqref="FW2:FW5">
     <cfRule type="cellIs" dxfId="4" priority="197" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3718,7 +4007,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FX2:FX4">
+  <conditionalFormatting sqref="FX2:FX5">
     <cfRule type="cellIs" dxfId="4" priority="199" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3726,7 +4015,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FY2:FY4">
+  <conditionalFormatting sqref="FY2:FY5">
     <cfRule type="cellIs" dxfId="4" priority="201" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3734,7 +4023,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J4">
+  <conditionalFormatting sqref="J2:J5">
     <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3742,7 +4031,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K4">
+  <conditionalFormatting sqref="K2:K5">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3750,7 +4039,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L4">
+  <conditionalFormatting sqref="L2:L5">
     <cfRule type="cellIs" dxfId="4" priority="7" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3758,7 +4047,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M4">
+  <conditionalFormatting sqref="M2:M5">
     <cfRule type="cellIs" dxfId="4" priority="9" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3766,7 +4055,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q4">
+  <conditionalFormatting sqref="Q2:Q5">
     <cfRule type="cellIs" dxfId="4" priority="11" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3774,7 +4063,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R4">
+  <conditionalFormatting sqref="R2:R5">
     <cfRule type="cellIs" dxfId="4" priority="13" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3782,7 +4071,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S4">
+  <conditionalFormatting sqref="S2:S5">
     <cfRule type="cellIs" dxfId="4" priority="15" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3790,7 +4079,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T4">
+  <conditionalFormatting sqref="T2:T5">
     <cfRule type="cellIs" dxfId="4" priority="17" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3798,7 +4087,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X4">
+  <conditionalFormatting sqref="X2:X5">
     <cfRule type="cellIs" dxfId="4" priority="19" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3806,7 +4095,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y4">
+  <conditionalFormatting sqref="Y2:Y5">
     <cfRule type="cellIs" dxfId="4" priority="21" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3814,7 +4103,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:Z4">
+  <conditionalFormatting sqref="Z2:Z5">
     <cfRule type="cellIs" dxfId="4" priority="23" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>

--- a/reports/paper_trade_trx.xlsx
+++ b/reports/paper_trade_trx.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="228">
   <si>
     <t>NAV</t>
   </si>
@@ -36,7 +36,7 @@
     <t>last_updated</t>
   </si>
   <si>
-    <t>2026-10-06 18:00:56</t>
+    <t>2026-10-07 18:01:08</t>
   </si>
   <si>
     <t>pf_id</t>
@@ -69,6 +69,9 @@
     <t>date</t>
   </si>
   <si>
+    <t>2026-10-07</t>
+  </si>
+  <si>
     <t>2026-10-06</t>
   </si>
   <si>
@@ -81,6 +84,9 @@
     <t>2026-09-29</t>
   </si>
   <si>
+    <t>TSLA</t>
+  </si>
+  <si>
     <t>AMAT</t>
   </si>
   <si>
@@ -115,6 +121,9 @@
   </si>
   <si>
     <t>initial</t>
+  </si>
+  <si>
+    <t>2026-10-07_dc7e32e4c69a2eb8b2d77f7cc32b45cf</t>
   </si>
   <si>
     <t>2026-10-06_53d2d3c2d4f2ff367a516a1f406e1bbb</t>
@@ -1215,7 +1224,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>9951</v>
+        <v>9904</v>
       </c>
       <c r="C2" s="2">
         <v>100</v>
@@ -1239,7 +1248,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>9951</v>
+        <v>9904</v>
       </c>
       <c r="C4" s="2">
         <v>100</v>
@@ -1310,7 +1319,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
@@ -1356,19 +1365,19 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>-546</v>
+        <v>-378.3500061035156</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1379,42 +1388,42 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>-332.7950134277344</v>
+        <v>-546</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>-52.58</v>
+        <v>-332.7950134277344</v>
       </c>
       <c r="G4">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1425,157 +1434,157 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>-733.2050170898438</v>
+        <v>-52.58</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>-236.0549926757812</v>
+        <v>-733.2050170898438</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7">
-        <v>-124.1699981689453</v>
+        <v>-236.0549926757812</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E8">
-        <v>-636.4500122070312</v>
+        <v>-124.1699981689453</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9">
-        <v>-290</v>
+        <v>-636.4500122070312</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10">
-        <v>-186.384994506836</v>
+        <v>-290</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11">
-        <v>-406.4700012207031</v>
+        <v>-186.384994506836</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1585,23 +1594,46 @@
       <c r="B12" t="s">
         <v>2</v>
       </c>
-      <c r="C12">
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12">
+        <v>-406.4700012207031</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13">
         <v>10000</v>
       </c>
-      <c r="H12" t="s">
-        <v>32</v>
-      </c>
-      <c r="J12" t="s">
-        <v>43</v>
+      <c r="H13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J13" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B12">
+  <conditionalFormatting sqref="B2:B13">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>$B2="option"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C12">
+  <conditionalFormatting sqref="C2:C13">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1609,7 +1641,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E12">
+  <conditionalFormatting sqref="E2:E13">
     <cfRule type="cellIs" dxfId="4" priority="4" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1617,7 +1649,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F12">
+  <conditionalFormatting sqref="F2:F13">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1625,7 +1657,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G12">
+  <conditionalFormatting sqref="G2:G13">
     <cfRule type="cellIs" dxfId="4" priority="8" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1639,7 +1671,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:GA5"/>
+  <dimension ref="A1:GA6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
@@ -1647,10 +1679,10 @@
   <sheetData>
     <row r="1" spans="1:183">
       <c r="A1" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>3</v>
@@ -1659,541 +1691,541 @@
         <v>8</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AL1" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="BE1" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="BF1" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="BL1" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="BM1" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="BN1" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="BO1" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="BP1" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BQ1" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="BR1" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="BS1" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="BT1" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="BU1" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="BV1" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="BW1" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="BX1" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="BY1" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="BZ1" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="CA1" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="CB1" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="CC1" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="CD1" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="CE1" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="CF1" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="CH1" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="CI1" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="CJ1" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="CK1" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="CL1" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="CM1" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="CN1" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="CO1" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="CP1" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="CQ1" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="CR1" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="CS1" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="CT1" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="CU1" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="CV1" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="CW1" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="CX1" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="CY1" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="CZ1" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="DA1" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="DB1" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="DC1" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="DD1" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="DE1" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="DF1" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="DG1" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="DH1" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="DI1" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="DJ1" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="DK1" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="DL1" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="DM1" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="DN1" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="DO1" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="DP1" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="DQ1" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="DR1" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="DS1" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="DT1" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="DU1" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="DV1" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="DW1" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="DX1" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="DY1" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="DZ1" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="EA1" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="EB1" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="EC1" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="ED1" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="EE1" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="EF1" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="EG1" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="EH1" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="EI1" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="EJ1" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="EK1" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="EL1" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="EM1" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EN1" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="EO1" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="EP1" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="EQ1" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="ER1" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="ES1" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="ET1" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="EU1" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EV1" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EW1" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="EX1" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="EY1" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="EZ1" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="FA1" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="FB1" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="FC1" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="FD1" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="FE1" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="FF1" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="FG1" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="FH1" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="FI1" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="FJ1" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="FK1" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="FL1" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="FM1" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="FN1" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="FO1" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="FP1" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="FQ1" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="FR1" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="FS1" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="FT1" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="FU1" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="FV1" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="FW1" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="FX1" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="FY1" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="FZ1" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="GA1" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:183">
@@ -2201,31 +2233,31 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>9950.788089754853</v>
+        <v>9904.144532567963</v>
       </c>
       <c r="C2">
-        <v>1918.657993319305</v>
+        <v>1161.844476110443</v>
       </c>
       <c r="D2">
-        <v>-546.0819</v>
+        <v>-756.8135172088623</v>
       </c>
       <c r="E2">
         <v>10000</v>
       </c>
       <c r="F2">
-        <v>-0.004921191024514715</v>
+        <v>-0.009585546743203666</v>
       </c>
       <c r="G2">
-        <v>-0.1015996582031256</v>
+        <v>-1.360000689697267</v>
       </c>
       <c r="H2">
-        <v>-0.001922883262771803</v>
+        <v>-0.004359760145087859</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>333.6300048828125</v>
+        <v>336.6700134277344</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2234,10 +2266,10 @@
         <v>2</v>
       </c>
       <c r="N2">
-        <v>0.834991455078125</v>
+        <v>3.875</v>
       </c>
       <c r="O2">
-        <v>0.00250902634170469</v>
+        <v>0.01164380427485412</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -2270,7 +2302,7 @@
         <v>1</v>
       </c>
       <c r="AM2">
-        <v>738.8800048828125</v>
+        <v>721.3099975585938</v>
       </c>
       <c r="AN2">
         <v>0</v>
@@ -2279,25 +2311,37 @@
         <v>1</v>
       </c>
       <c r="AP2">
-        <v>5.67498779296875</v>
+        <v>-11.89501953125</v>
       </c>
       <c r="AQ2">
-        <v>0.007739974032765495</v>
+        <v>-0.01622331988188297</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AS2">
+        <v>-378.3500061035156</v>
+      </c>
+      <c r="AT2">
+        <v>377.8099975585938</v>
       </c>
       <c r="AU2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AW2">
+        <v>-0.540008544921875</v>
+      </c>
+      <c r="AX2">
+        <v>-0.001427272462562468</v>
       </c>
       <c r="AY2">
         <v>1</v>
       </c>
       <c r="BA2">
-        <v>239.2400054931641</v>
+        <v>237.4700012207031</v>
       </c>
       <c r="BB2">
         <v>0</v>
@@ -2306,10 +2350,10 @@
         <v>4</v>
       </c>
       <c r="BD2">
-        <v>3.185012817382841</v>
+        <v>1.415008544921875</v>
       </c>
       <c r="BE2">
-        <v>0.01349267296268297</v>
+        <v>0.005994402104705143</v>
       </c>
       <c r="BF2">
         <v>0</v>
@@ -2324,7 +2368,7 @@
         <v>1</v>
       </c>
       <c r="BO2">
-        <v>54.61000061035156</v>
+        <v>54.95000076293945</v>
       </c>
       <c r="BP2">
         <v>0</v>
@@ -2333,10 +2377,10 @@
         <v>18</v>
       </c>
       <c r="BR2">
-        <v>2.030000610351564</v>
+        <v>2.370000762939455</v>
       </c>
       <c r="BS2">
-        <v>0.03860784728702105</v>
+        <v>0.045074187199305</v>
       </c>
       <c r="BT2">
         <v>0</v>
@@ -2360,7 +2404,7 @@
         <v>1</v>
       </c>
       <c r="CJ2">
-        <v>112.5</v>
+        <v>113.120002746582</v>
       </c>
       <c r="CK2">
         <v>0</v>
@@ -2369,10 +2413,10 @@
         <v>8</v>
       </c>
       <c r="CM2">
-        <v>-11.66999816894533</v>
+        <v>-11.04999542236328</v>
       </c>
       <c r="CN2">
-        <v>-0.09398404075892119</v>
+        <v>-0.08899086401957335</v>
       </c>
       <c r="CO2">
         <v>0</v>
@@ -2423,7 +2467,7 @@
         <v>1</v>
       </c>
       <c r="DZ2">
-        <v>649.4199829101562</v>
+        <v>645.8599853515625</v>
       </c>
       <c r="EA2">
         <v>0</v>
@@ -2432,16 +2476,16 @@
         <v>1</v>
       </c>
       <c r="EC2">
-        <v>12.969970703125</v>
+        <v>9.40997314453125</v>
       </c>
       <c r="ED2">
-        <v>0.02037861647319139</v>
+        <v>0.0147850938236298</v>
       </c>
       <c r="EE2">
         <v>1</v>
       </c>
       <c r="EG2">
-        <v>297.2300109863281</v>
+        <v>288.9800109863281</v>
       </c>
       <c r="EH2">
         <v>0</v>
@@ -2450,10 +2494,10 @@
         <v>3</v>
       </c>
       <c r="EJ2">
-        <v>7.230010986328125</v>
+        <v>-1.019989013671875</v>
       </c>
       <c r="EK2">
-        <v>0.02493107236664871</v>
+        <v>-0.003517203495420285</v>
       </c>
       <c r="EL2">
         <v>0</v>
@@ -2477,7 +2521,7 @@
         <v>1</v>
       </c>
       <c r="FB2">
-        <v>181.0299987792969</v>
+        <v>177.1199951171875</v>
       </c>
       <c r="FC2">
         <v>0</v>
@@ -2486,16 +2530,16 @@
         <v>5</v>
       </c>
       <c r="FE2">
-        <v>-5.354995727539091</v>
+        <v>-9.264999389648466</v>
       </c>
       <c r="FF2">
-        <v>-0.02873083072866511</v>
+        <v>-0.04970893399526677</v>
       </c>
       <c r="FG2">
         <v>1</v>
       </c>
       <c r="FI2">
-        <v>404.760009765625</v>
+        <v>414.5199890136719</v>
       </c>
       <c r="FJ2">
         <v>0</v>
@@ -2504,10 +2548,10 @@
         <v>2</v>
       </c>
       <c r="FL2">
-        <v>-1.709991455078125</v>
+        <v>8.04998779296875</v>
       </c>
       <c r="FM2">
-        <v>-0.004206931507719447</v>
+        <v>0.01980462953918649</v>
       </c>
       <c r="FN2">
         <v>0</v>
@@ -2521,23 +2565,20 @@
       <c r="FU2">
         <v>1</v>
       </c>
-      <c r="FV2">
-        <v>-546</v>
-      </c>
       <c r="FW2">
-        <v>530.27001953125</v>
+        <v>520.6500244140625</v>
       </c>
       <c r="FX2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FY2">
         <v>1</v>
       </c>
       <c r="FZ2">
-        <v>-15.72998046875</v>
+        <v>-25.3499755859375</v>
       </c>
       <c r="GA2">
-        <v>-0.02880948803800365</v>
+        <v>-0.04642852671417119</v>
       </c>
     </row>
     <row r="3" spans="1:183">
@@ -2545,28 +2586,25 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>9970.279909493622</v>
+        <v>9950.788089754853</v>
       </c>
       <c r="C3">
-        <v>2464.739893319305</v>
+        <v>1918.657993319305</v>
       </c>
       <c r="D3">
-        <v>-1612.271831359497</v>
+        <v>-546.0819</v>
       </c>
       <c r="E3">
         <v>10000</v>
       </c>
       <c r="F3">
-        <v>-0.00297200905063788</v>
+        <v>-0.004921191024514715</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
-      <c r="J3">
-        <v>-332.7950134277344</v>
-      </c>
       <c r="L3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -2637,11 +2675,8 @@
       <c r="BM3">
         <v>1</v>
       </c>
-      <c r="BN3">
-        <v>-52.58</v>
-      </c>
       <c r="BP3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
         <v>18</v>
@@ -2782,13 +2817,16 @@
         <v>0</v>
       </c>
       <c r="FU3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FV3">
+        <v>-546</v>
       </c>
       <c r="FX3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FY3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:183">
@@ -2796,28 +2834,31 @@
         <v>19</v>
       </c>
       <c r="B4">
-        <v>9919.091680733491</v>
+        <v>9970.279909493622</v>
       </c>
       <c r="C4">
-        <v>4077.011724678802</v>
+        <v>2464.739893319305</v>
       </c>
       <c r="D4">
-        <v>-5922.988275321198</v>
+        <v>-1612.271831359497</v>
       </c>
       <c r="E4">
         <v>10000</v>
       </c>
       <c r="F4">
-        <v>-0.008090831926650943</v>
+        <v>-0.00297200905063788</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>-332.7950134277344</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -2849,11 +2890,8 @@
       <c r="AK4">
         <v>1</v>
       </c>
-      <c r="AL4">
-        <v>-733.2050170898438</v>
-      </c>
       <c r="AN4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO4">
         <v>1</v>
@@ -2870,11 +2908,8 @@
       <c r="AY4">
         <v>1</v>
       </c>
-      <c r="AZ4">
-        <v>-236.0549926757812</v>
-      </c>
       <c r="BB4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BC4">
         <v>4</v>
@@ -2889,13 +2924,16 @@
         <v>0</v>
       </c>
       <c r="BM4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BN4">
+        <v>-52.58</v>
       </c>
       <c r="BP4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BQ4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BT4">
         <v>0</v>
@@ -2918,11 +2956,8 @@
       <c r="CH4">
         <v>1</v>
       </c>
-      <c r="CI4">
-        <v>-124.1699981689453</v>
-      </c>
       <c r="CK4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CL4">
         <v>8</v>
@@ -2975,11 +3010,8 @@
       <c r="DX4">
         <v>1</v>
       </c>
-      <c r="DY4">
-        <v>-636.4500122070312</v>
-      </c>
       <c r="EA4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB4">
         <v>1</v>
@@ -2987,11 +3019,8 @@
       <c r="EE4">
         <v>1</v>
       </c>
-      <c r="EF4">
-        <v>-290</v>
-      </c>
       <c r="EH4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="EI4">
         <v>3</v>
@@ -3017,11 +3046,8 @@
       <c r="EZ4">
         <v>1</v>
       </c>
-      <c r="FA4">
-        <v>-186.384994506836</v>
-      </c>
       <c r="FC4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="FD4">
         <v>5</v>
@@ -3029,11 +3055,8 @@
       <c r="FG4">
         <v>1</v>
       </c>
-      <c r="FH4">
-        <v>-406.4700012207031</v>
-      </c>
       <c r="FJ4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="FK4">
         <v>2</v>
@@ -3062,19 +3085,19 @@
         <v>20</v>
       </c>
       <c r="B5">
-        <v>10000</v>
+        <v>9919.091680733491</v>
       </c>
       <c r="C5">
-        <v>10000</v>
+        <v>4077.011724678802</v>
       </c>
       <c r="D5">
-        <v>10000</v>
+        <v>-5922.988275321198</v>
       </c>
       <c r="E5">
         <v>10000</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>-0.008090831926650943</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3113,13 +3136,16 @@
         <v>0</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <v>-733.2050170898438</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -3131,13 +3157,16 @@
         <v>0</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AZ5">
+        <v>-236.0549926757812</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF5">
         <v>0</v>
@@ -3176,13 +3205,16 @@
         <v>0</v>
       </c>
       <c r="CH5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CI5">
+        <v>-124.1699981689453</v>
       </c>
       <c r="CK5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CL5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CO5">
         <v>0</v>
@@ -3230,22 +3262,28 @@
         <v>0</v>
       </c>
       <c r="DX5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="DY5">
+        <v>-636.4500122070312</v>
       </c>
       <c r="EA5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EB5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EE5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="EF5">
+        <v>-290</v>
       </c>
       <c r="EH5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="EI5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="EL5">
         <v>0</v>
@@ -3266,22 +3304,28 @@
         <v>0</v>
       </c>
       <c r="EZ5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FA5">
+        <v>-186.384994506836</v>
       </c>
       <c r="FC5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="FD5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="FG5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FH5">
+        <v>-406.4700012207031</v>
       </c>
       <c r="FJ5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="FK5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="FN5">
         <v>0</v>
@@ -3299,11 +3343,256 @@
         <v>0</v>
       </c>
       <c r="FY5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:183">
+      <c r="A6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
+        <v>10000</v>
+      </c>
+      <c r="C6">
+        <v>10000</v>
+      </c>
+      <c r="D6">
+        <v>10000</v>
+      </c>
+      <c r="E6">
+        <v>10000</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CD6">
+        <v>0</v>
+      </c>
+      <c r="CE6">
+        <v>0</v>
+      </c>
+      <c r="CH6">
+        <v>0</v>
+      </c>
+      <c r="CK6">
+        <v>0</v>
+      </c>
+      <c r="CL6">
+        <v>0</v>
+      </c>
+      <c r="CO6">
+        <v>0</v>
+      </c>
+      <c r="CR6">
+        <v>0</v>
+      </c>
+      <c r="CS6">
+        <v>0</v>
+      </c>
+      <c r="CV6">
+        <v>0</v>
+      </c>
+      <c r="CY6">
+        <v>0</v>
+      </c>
+      <c r="CZ6">
+        <v>0</v>
+      </c>
+      <c r="DC6">
+        <v>0</v>
+      </c>
+      <c r="DF6">
+        <v>0</v>
+      </c>
+      <c r="DG6">
+        <v>0</v>
+      </c>
+      <c r="DJ6">
+        <v>0</v>
+      </c>
+      <c r="DM6">
+        <v>0</v>
+      </c>
+      <c r="DN6">
+        <v>0</v>
+      </c>
+      <c r="DQ6">
+        <v>0</v>
+      </c>
+      <c r="DT6">
+        <v>0</v>
+      </c>
+      <c r="DU6">
+        <v>0</v>
+      </c>
+      <c r="DX6">
+        <v>0</v>
+      </c>
+      <c r="EA6">
+        <v>0</v>
+      </c>
+      <c r="EB6">
+        <v>0</v>
+      </c>
+      <c r="EE6">
+        <v>0</v>
+      </c>
+      <c r="EH6">
+        <v>0</v>
+      </c>
+      <c r="EI6">
+        <v>0</v>
+      </c>
+      <c r="EL6">
+        <v>0</v>
+      </c>
+      <c r="EO6">
+        <v>0</v>
+      </c>
+      <c r="EP6">
+        <v>0</v>
+      </c>
+      <c r="ES6">
+        <v>0</v>
+      </c>
+      <c r="EV6">
+        <v>0</v>
+      </c>
+      <c r="EW6">
+        <v>0</v>
+      </c>
+      <c r="EZ6">
+        <v>0</v>
+      </c>
+      <c r="FC6">
+        <v>0</v>
+      </c>
+      <c r="FD6">
+        <v>0</v>
+      </c>
+      <c r="FG6">
+        <v>0</v>
+      </c>
+      <c r="FJ6">
+        <v>0</v>
+      </c>
+      <c r="FK6">
+        <v>0</v>
+      </c>
+      <c r="FN6">
+        <v>0</v>
+      </c>
+      <c r="FQ6">
+        <v>0</v>
+      </c>
+      <c r="FR6">
+        <v>0</v>
+      </c>
+      <c r="FU6">
+        <v>0</v>
+      </c>
+      <c r="FX6">
+        <v>0</v>
+      </c>
+      <c r="FY6">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AA2:AA5">
+  <conditionalFormatting sqref="AA2:AA6">
     <cfRule type="cellIs" dxfId="4" priority="25" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3311,7 +3600,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE2:AE5">
+  <conditionalFormatting sqref="AE2:AE6">
     <cfRule type="cellIs" dxfId="4" priority="27" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3319,7 +3608,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF2:AF5">
+  <conditionalFormatting sqref="AF2:AF6">
     <cfRule type="cellIs" dxfId="4" priority="29" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3327,7 +3616,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG2:AG5">
+  <conditionalFormatting sqref="AG2:AG6">
     <cfRule type="cellIs" dxfId="4" priority="31" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3335,7 +3624,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH2:AH5">
+  <conditionalFormatting sqref="AH2:AH6">
     <cfRule type="cellIs" dxfId="4" priority="33" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3343,7 +3632,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL2:AL5">
+  <conditionalFormatting sqref="AL2:AL6">
     <cfRule type="cellIs" dxfId="4" priority="35" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3351,7 +3640,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM2:AM5">
+  <conditionalFormatting sqref="AM2:AM6">
     <cfRule type="cellIs" dxfId="4" priority="37" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3359,7 +3648,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AN2:AN5">
+  <conditionalFormatting sqref="AN2:AN6">
     <cfRule type="cellIs" dxfId="4" priority="39" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3367,7 +3656,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AO2:AO5">
+  <conditionalFormatting sqref="AO2:AO6">
     <cfRule type="cellIs" dxfId="4" priority="41" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3375,7 +3664,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AS2:AS5">
+  <conditionalFormatting sqref="AS2:AS6">
     <cfRule type="cellIs" dxfId="4" priority="43" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3383,7 +3672,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AT2:AT5">
+  <conditionalFormatting sqref="AT2:AT6">
     <cfRule type="cellIs" dxfId="4" priority="45" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3391,7 +3680,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU2:AU5">
+  <conditionalFormatting sqref="AU2:AU6">
     <cfRule type="cellIs" dxfId="4" priority="47" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3399,7 +3688,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AV2:AV5">
+  <conditionalFormatting sqref="AV2:AV6">
     <cfRule type="cellIs" dxfId="4" priority="49" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3407,7 +3696,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AZ2:AZ5">
+  <conditionalFormatting sqref="AZ2:AZ6">
     <cfRule type="cellIs" dxfId="4" priority="51" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3415,7 +3704,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BA2:BA5">
+  <conditionalFormatting sqref="BA2:BA6">
     <cfRule type="cellIs" dxfId="4" priority="53" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3423,7 +3712,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB2:BB5">
+  <conditionalFormatting sqref="BB2:BB6">
     <cfRule type="cellIs" dxfId="4" priority="55" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3431,7 +3720,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BC2:BC5">
+  <conditionalFormatting sqref="BC2:BC6">
     <cfRule type="cellIs" dxfId="4" priority="57" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3439,7 +3728,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BG2:BG5">
+  <conditionalFormatting sqref="BG2:BG6">
     <cfRule type="cellIs" dxfId="4" priority="59" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3447,7 +3736,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BH2:BH5">
+  <conditionalFormatting sqref="BH2:BH6">
     <cfRule type="cellIs" dxfId="4" priority="61" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3455,7 +3744,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BI2:BI5">
+  <conditionalFormatting sqref="BI2:BI6">
     <cfRule type="cellIs" dxfId="4" priority="63" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3463,7 +3752,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BJ2:BJ5">
+  <conditionalFormatting sqref="BJ2:BJ6">
     <cfRule type="cellIs" dxfId="4" priority="65" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3471,7 +3760,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BN2:BN5">
+  <conditionalFormatting sqref="BN2:BN6">
     <cfRule type="cellIs" dxfId="4" priority="67" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3479,7 +3768,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BO2:BO5">
+  <conditionalFormatting sqref="BO2:BO6">
     <cfRule type="cellIs" dxfId="4" priority="69" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3487,7 +3776,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BP2:BP5">
+  <conditionalFormatting sqref="BP2:BP6">
     <cfRule type="cellIs" dxfId="4" priority="71" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3495,7 +3784,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BQ2:BQ5">
+  <conditionalFormatting sqref="BQ2:BQ6">
     <cfRule type="cellIs" dxfId="4" priority="73" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3503,7 +3792,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BU2:BU5">
+  <conditionalFormatting sqref="BU2:BU6">
     <cfRule type="cellIs" dxfId="4" priority="75" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3511,7 +3800,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BV2:BV5">
+  <conditionalFormatting sqref="BV2:BV6">
     <cfRule type="cellIs" dxfId="4" priority="77" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3519,7 +3808,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BW2:BW5">
+  <conditionalFormatting sqref="BW2:BW6">
     <cfRule type="cellIs" dxfId="4" priority="79" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3527,7 +3816,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BX2:BX5">
+  <conditionalFormatting sqref="BX2:BX6">
     <cfRule type="cellIs" dxfId="4" priority="81" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3535,7 +3824,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CB2:CB5">
+  <conditionalFormatting sqref="CB2:CB6">
     <cfRule type="cellIs" dxfId="4" priority="83" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3543,7 +3832,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CC2:CC5">
+  <conditionalFormatting sqref="CC2:CC6">
     <cfRule type="cellIs" dxfId="4" priority="85" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3551,7 +3840,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CD2:CD5">
+  <conditionalFormatting sqref="CD2:CD6">
     <cfRule type="cellIs" dxfId="4" priority="87" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3559,7 +3848,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CE2:CE5">
+  <conditionalFormatting sqref="CE2:CE6">
     <cfRule type="cellIs" dxfId="4" priority="89" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3567,7 +3856,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CI2:CI5">
+  <conditionalFormatting sqref="CI2:CI6">
     <cfRule type="cellIs" dxfId="4" priority="91" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3575,7 +3864,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CJ2:CJ5">
+  <conditionalFormatting sqref="CJ2:CJ6">
     <cfRule type="cellIs" dxfId="4" priority="93" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3583,7 +3872,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CK2:CK5">
+  <conditionalFormatting sqref="CK2:CK6">
     <cfRule type="cellIs" dxfId="4" priority="95" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3591,7 +3880,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CL2:CL5">
+  <conditionalFormatting sqref="CL2:CL6">
     <cfRule type="cellIs" dxfId="4" priority="97" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3599,7 +3888,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CP2:CP5">
+  <conditionalFormatting sqref="CP2:CP6">
     <cfRule type="cellIs" dxfId="4" priority="99" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3607,7 +3896,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CQ2:CQ5">
+  <conditionalFormatting sqref="CQ2:CQ6">
     <cfRule type="cellIs" dxfId="4" priority="101" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3615,7 +3904,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CR2:CR5">
+  <conditionalFormatting sqref="CR2:CR6">
     <cfRule type="cellIs" dxfId="4" priority="103" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3623,7 +3912,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CS2:CS5">
+  <conditionalFormatting sqref="CS2:CS6">
     <cfRule type="cellIs" dxfId="4" priority="105" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3631,7 +3920,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CW2:CW5">
+  <conditionalFormatting sqref="CW2:CW6">
     <cfRule type="cellIs" dxfId="4" priority="107" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3639,7 +3928,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CX2:CX5">
+  <conditionalFormatting sqref="CX2:CX6">
     <cfRule type="cellIs" dxfId="4" priority="109" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3647,7 +3936,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CY2:CY5">
+  <conditionalFormatting sqref="CY2:CY6">
     <cfRule type="cellIs" dxfId="4" priority="111" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3655,7 +3944,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CZ2:CZ5">
+  <conditionalFormatting sqref="CZ2:CZ6">
     <cfRule type="cellIs" dxfId="4" priority="113" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3663,7 +3952,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D5">
+  <conditionalFormatting sqref="D2:D6">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3671,7 +3960,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DD2:DD5">
+  <conditionalFormatting sqref="DD2:DD6">
     <cfRule type="cellIs" dxfId="4" priority="115" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3679,7 +3968,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DE2:DE5">
+  <conditionalFormatting sqref="DE2:DE6">
     <cfRule type="cellIs" dxfId="4" priority="117" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3687,7 +3976,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DF2:DF5">
+  <conditionalFormatting sqref="DF2:DF6">
     <cfRule type="cellIs" dxfId="4" priority="119" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3695,7 +3984,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DG2:DG5">
+  <conditionalFormatting sqref="DG2:DG6">
     <cfRule type="cellIs" dxfId="4" priority="121" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3703,7 +3992,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DK2:DK5">
+  <conditionalFormatting sqref="DK2:DK6">
     <cfRule type="cellIs" dxfId="4" priority="123" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3711,7 +4000,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DL2:DL5">
+  <conditionalFormatting sqref="DL2:DL6">
     <cfRule type="cellIs" dxfId="4" priority="125" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3719,7 +4008,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DM2:DM5">
+  <conditionalFormatting sqref="DM2:DM6">
     <cfRule type="cellIs" dxfId="4" priority="127" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3727,7 +4016,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DN2:DN5">
+  <conditionalFormatting sqref="DN2:DN6">
     <cfRule type="cellIs" dxfId="4" priority="129" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3735,7 +4024,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DR2:DR5">
+  <conditionalFormatting sqref="DR2:DR6">
     <cfRule type="cellIs" dxfId="4" priority="131" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3743,7 +4032,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DS2:DS5">
+  <conditionalFormatting sqref="DS2:DS6">
     <cfRule type="cellIs" dxfId="4" priority="133" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3751,7 +4040,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DT2:DT5">
+  <conditionalFormatting sqref="DT2:DT6">
     <cfRule type="cellIs" dxfId="4" priority="135" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3759,7 +4048,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DU2:DU5">
+  <conditionalFormatting sqref="DU2:DU6">
     <cfRule type="cellIs" dxfId="4" priority="137" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3767,7 +4056,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DY2:DY5">
+  <conditionalFormatting sqref="DY2:DY6">
     <cfRule type="cellIs" dxfId="4" priority="139" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3775,7 +4064,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DZ2:DZ5">
+  <conditionalFormatting sqref="DZ2:DZ6">
     <cfRule type="cellIs" dxfId="4" priority="141" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3783,7 +4072,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EA2:EA5">
+  <conditionalFormatting sqref="EA2:EA6">
     <cfRule type="cellIs" dxfId="4" priority="143" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3791,7 +4080,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EB2:EB5">
+  <conditionalFormatting sqref="EB2:EB6">
     <cfRule type="cellIs" dxfId="4" priority="145" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3799,7 +4088,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EF2:EF5">
+  <conditionalFormatting sqref="EF2:EF6">
     <cfRule type="cellIs" dxfId="4" priority="147" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3807,7 +4096,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EG2:EG5">
+  <conditionalFormatting sqref="EG2:EG6">
     <cfRule type="cellIs" dxfId="4" priority="149" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3815,7 +4104,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EH2:EH5">
+  <conditionalFormatting sqref="EH2:EH6">
     <cfRule type="cellIs" dxfId="4" priority="151" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3823,7 +4112,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EI2:EI5">
+  <conditionalFormatting sqref="EI2:EI6">
     <cfRule type="cellIs" dxfId="4" priority="153" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3831,7 +4120,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EM2:EM5">
+  <conditionalFormatting sqref="EM2:EM6">
     <cfRule type="cellIs" dxfId="4" priority="155" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3839,7 +4128,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EN2:EN5">
+  <conditionalFormatting sqref="EN2:EN6">
     <cfRule type="cellIs" dxfId="4" priority="157" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3847,7 +4136,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EO2:EO5">
+  <conditionalFormatting sqref="EO2:EO6">
     <cfRule type="cellIs" dxfId="4" priority="159" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3855,7 +4144,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EP2:EP5">
+  <conditionalFormatting sqref="EP2:EP6">
     <cfRule type="cellIs" dxfId="4" priority="161" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3863,7 +4152,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="ET2:ET5">
+  <conditionalFormatting sqref="ET2:ET6">
     <cfRule type="cellIs" dxfId="4" priority="163" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3871,7 +4160,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EU2:EU5">
+  <conditionalFormatting sqref="EU2:EU6">
     <cfRule type="cellIs" dxfId="4" priority="165" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3879,7 +4168,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EV2:EV5">
+  <conditionalFormatting sqref="EV2:EV6">
     <cfRule type="cellIs" dxfId="4" priority="167" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3887,7 +4176,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EW2:EW5">
+  <conditionalFormatting sqref="EW2:EW6">
     <cfRule type="cellIs" dxfId="4" priority="169" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3895,7 +4184,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FA2:FA5">
+  <conditionalFormatting sqref="FA2:FA6">
     <cfRule type="cellIs" dxfId="4" priority="171" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3903,7 +4192,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FB2:FB5">
+  <conditionalFormatting sqref="FB2:FB6">
     <cfRule type="cellIs" dxfId="4" priority="173" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3911,7 +4200,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FC2:FC5">
+  <conditionalFormatting sqref="FC2:FC6">
     <cfRule type="cellIs" dxfId="4" priority="175" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3919,7 +4208,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FD2:FD5">
+  <conditionalFormatting sqref="FD2:FD6">
     <cfRule type="cellIs" dxfId="4" priority="177" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3927,7 +4216,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FH2:FH5">
+  <conditionalFormatting sqref="FH2:FH6">
     <cfRule type="cellIs" dxfId="4" priority="179" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3935,7 +4224,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FI2:FI5">
+  <conditionalFormatting sqref="FI2:FI6">
     <cfRule type="cellIs" dxfId="4" priority="181" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3943,7 +4232,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FJ2:FJ5">
+  <conditionalFormatting sqref="FJ2:FJ6">
     <cfRule type="cellIs" dxfId="4" priority="183" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3951,7 +4240,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FK2:FK5">
+  <conditionalFormatting sqref="FK2:FK6">
     <cfRule type="cellIs" dxfId="4" priority="185" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3959,7 +4248,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FO2:FO5">
+  <conditionalFormatting sqref="FO2:FO6">
     <cfRule type="cellIs" dxfId="4" priority="187" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3967,7 +4256,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FP2:FP5">
+  <conditionalFormatting sqref="FP2:FP6">
     <cfRule type="cellIs" dxfId="4" priority="189" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3975,7 +4264,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FQ2:FQ5">
+  <conditionalFormatting sqref="FQ2:FQ6">
     <cfRule type="cellIs" dxfId="4" priority="191" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3983,7 +4272,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FR2:FR5">
+  <conditionalFormatting sqref="FR2:FR6">
     <cfRule type="cellIs" dxfId="4" priority="193" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3991,7 +4280,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FV2:FV5">
+  <conditionalFormatting sqref="FV2:FV6">
     <cfRule type="cellIs" dxfId="4" priority="195" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3999,7 +4288,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FW2:FW5">
+  <conditionalFormatting sqref="FW2:FW6">
     <cfRule type="cellIs" dxfId="4" priority="197" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4007,7 +4296,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FX2:FX5">
+  <conditionalFormatting sqref="FX2:FX6">
     <cfRule type="cellIs" dxfId="4" priority="199" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4015,7 +4304,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FY2:FY5">
+  <conditionalFormatting sqref="FY2:FY6">
     <cfRule type="cellIs" dxfId="4" priority="201" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4023,7 +4312,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J5">
+  <conditionalFormatting sqref="J2:J6">
     <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4031,7 +4320,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K5">
+  <conditionalFormatting sqref="K2:K6">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4039,7 +4328,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L5">
+  <conditionalFormatting sqref="L2:L6">
     <cfRule type="cellIs" dxfId="4" priority="7" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4047,7 +4336,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M5">
+  <conditionalFormatting sqref="M2:M6">
     <cfRule type="cellIs" dxfId="4" priority="9" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4055,7 +4344,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q5">
+  <conditionalFormatting sqref="Q2:Q6">
     <cfRule type="cellIs" dxfId="4" priority="11" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4063,7 +4352,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R5">
+  <conditionalFormatting sqref="R2:R6">
     <cfRule type="cellIs" dxfId="4" priority="13" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4071,7 +4360,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S5">
+  <conditionalFormatting sqref="S2:S6">
     <cfRule type="cellIs" dxfId="4" priority="15" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4079,7 +4368,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T5">
+  <conditionalFormatting sqref="T2:T6">
     <cfRule type="cellIs" dxfId="4" priority="17" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4087,7 +4376,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X5">
+  <conditionalFormatting sqref="X2:X6">
     <cfRule type="cellIs" dxfId="4" priority="19" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4095,7 +4384,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y5">
+  <conditionalFormatting sqref="Y2:Y6">
     <cfRule type="cellIs" dxfId="4" priority="21" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4103,7 +4392,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:Z5">
+  <conditionalFormatting sqref="Z2:Z6">
     <cfRule type="cellIs" dxfId="4" priority="23" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>

--- a/reports/paper_trade_trx.xlsx
+++ b/reports/paper_trade_trx.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="237">
   <si>
     <t>NAV</t>
   </si>
@@ -36,7 +36,7 @@
     <t>last_updated</t>
   </si>
   <si>
-    <t>2026-10-07 18:01:08</t>
+    <t>2026-10-09 18:01:22</t>
   </si>
   <si>
     <t>pf_id</t>
@@ -69,6 +69,9 @@
     <t>date</t>
   </si>
   <si>
+    <t>2026-10-09</t>
+  </si>
+  <si>
     <t>2026-10-07</t>
   </si>
   <si>
@@ -84,6 +87,18 @@
     <t>2026-09-29</t>
   </si>
   <si>
+    <t>MSFT</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>CSCO</t>
+  </si>
+  <si>
+    <t>COST</t>
+  </si>
+  <si>
     <t>TSLA</t>
   </si>
   <si>
@@ -121,6 +136,18 @@
   </si>
   <si>
     <t>initial</t>
+  </si>
+  <si>
+    <t>2026-10-09_4c574a6fffe0157d7c23fe8d2682dfb9</t>
+  </si>
+  <si>
+    <t>2026-10-09_603d3f285d1e0ad7f8d04d423ef9ecc5</t>
+  </si>
+  <si>
+    <t>2026-10-09_a65360c396f5991e9fa841dde59b8684</t>
+  </si>
+  <si>
+    <t>2026-10-09_cbfa34b7b92b8c9ddd53b2ba7394c363</t>
   </si>
   <si>
     <t>2026-10-07_dc7e32e4c69a2eb8b2d77f7cc32b45cf</t>
@@ -1224,7 +1251,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>9904</v>
+        <v>9805</v>
       </c>
       <c r="C2" s="2">
         <v>100</v>
@@ -1248,7 +1275,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>9904</v>
+        <v>9805</v>
       </c>
       <c r="C4" s="2">
         <v>100</v>
@@ -1319,7 +1346,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
@@ -1365,134 +1392,134 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>-378.3500061035156</v>
+        <v>-528.2349853515625</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>-546</v>
+        <v>-256.2999877929688</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>-332.7950134277344</v>
+        <v>-116.7699966430664</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>-52.58</v>
+        <v>-945</v>
       </c>
       <c r="G5">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>-733.2050170898438</v>
+        <v>-378.3500061035156</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7">
-        <v>-236.0549926757812</v>
+        <v>-546</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1503,19 +1530,19 @@
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8">
-        <v>-124.1699981689453</v>
+        <v>-332.7950134277344</v>
       </c>
       <c r="G8">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1526,88 +1553,88 @@
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9">
-        <v>-636.4500122070312</v>
+        <v>-52.58</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J9" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10">
-        <v>-290</v>
+        <v>-733.2050170898438</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J10" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11">
-        <v>-186.384994506836</v>
+        <v>-236.0549926757812</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12">
-        <v>-406.4700012207031</v>
+        <v>-124.1699981689453</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H12" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J12" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1617,23 +1644,115 @@
       <c r="B13" t="s">
         <v>2</v>
       </c>
-      <c r="C13">
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13">
+        <v>-636.4500122070312</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14">
+        <v>-290</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15">
+        <v>-186.384994506836</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15" t="s">
+        <v>38</v>
+      </c>
+      <c r="J15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16">
+        <v>-406.4700012207031</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16" t="s">
+        <v>38</v>
+      </c>
+      <c r="J16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17">
         <v>10000</v>
       </c>
-      <c r="H13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J13" t="s">
-        <v>46</v>
+      <c r="H17" t="s">
+        <v>39</v>
+      </c>
+      <c r="J17" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B13">
+  <conditionalFormatting sqref="B2:B17">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>$B2="option"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C13">
+  <conditionalFormatting sqref="C2:C17">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1641,7 +1760,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E13">
+  <conditionalFormatting sqref="E2:E17">
     <cfRule type="cellIs" dxfId="4" priority="4" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1649,7 +1768,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
+  <conditionalFormatting sqref="F2:F17">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1657,7 +1776,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G13">
+  <conditionalFormatting sqref="G2:G17">
     <cfRule type="cellIs" dxfId="4" priority="8" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1671,7 +1790,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:GA6"/>
+  <dimension ref="A1:GA7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
@@ -1679,10 +1798,10 @@
   <sheetData>
     <row r="1" spans="1:183">
       <c r="A1" s="3" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>3</v>
@@ -1691,541 +1810,541 @@
         <v>8</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AL1" s="3" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="BE1" s="3" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="BF1" s="3" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="BL1" s="3" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="BM1" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="BN1" s="3" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="BO1" s="3" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="BP1" s="3" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="BQ1" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="BR1" s="3" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="BS1" s="3" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="BT1" s="3" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="BU1" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="BV1" s="3" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="BW1" s="3" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="BX1" s="3" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="BY1" s="3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="BZ1" s="3" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="CA1" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="CB1" s="3" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="CC1" s="3" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="CD1" s="3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="CE1" s="3" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="CF1" s="3" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="CH1" s="3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="CI1" s="3" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="CJ1" s="3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="CK1" s="3" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="CL1" s="3" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="CM1" s="3" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="CN1" s="3" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="CO1" s="3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="CP1" s="3" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="CQ1" s="3" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="CR1" s="3" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="CS1" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="CT1" s="3" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="CU1" s="3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="CV1" s="3" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="CW1" s="3" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="CX1" s="3" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="CY1" s="3" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="CZ1" s="3" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="DA1" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="DB1" s="3" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="DC1" s="3" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="DD1" s="3" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="DE1" s="3" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="DF1" s="3" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="DG1" s="3" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="DH1" s="3" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="DI1" s="3" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="DJ1" s="3" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="DK1" s="3" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="DL1" s="3" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="DM1" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="DN1" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="DO1" s="3" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="DP1" s="3" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="DQ1" s="3" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="DR1" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="DS1" s="3" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="DT1" s="3" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="DU1" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="DV1" s="3" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="DW1" s="3" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="DX1" s="3" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="DY1" s="3" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="DZ1" s="3" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="EA1" s="3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="EB1" s="3" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="EC1" s="3" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="ED1" s="3" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="EE1" s="3" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="EF1" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="EG1" s="3" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="EH1" s="3" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="EI1" s="3" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="EJ1" s="3" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="EK1" s="3" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="EL1" s="3" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="EM1" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="EN1" s="3" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="EO1" s="3" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="EP1" s="3" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="EQ1" s="3" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="ER1" s="3" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="ES1" s="3" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="ET1" s="3" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="EU1" s="3" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="EV1" s="3" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="EW1" s="3" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="EX1" s="3" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="EY1" s="3" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="EZ1" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="FA1" s="3" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="FB1" s="3" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="FC1" s="3" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="FD1" s="3" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="FE1" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="FF1" s="3" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="FG1" s="3" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="FH1" s="3" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="FI1" s="3" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="FJ1" s="3" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="FK1" s="3" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="FL1" s="3" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="FM1" s="3" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="FN1" s="3" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="FO1" s="3" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="FP1" s="3" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="FQ1" s="3" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="FR1" s="3" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="FS1" s="3" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="FT1" s="3" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="FU1" s="3" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="FV1" s="3" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="FW1" s="3" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="FX1" s="3" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="FY1" s="3" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="FZ1" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="GA1" s="3" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:183">
@@ -2233,31 +2352,31 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>9904.144532567963</v>
+        <v>9804.852986706146</v>
       </c>
       <c r="C2">
-        <v>1161.844476110443</v>
+        <v>-2014.926890002838</v>
       </c>
       <c r="D2">
-        <v>-756.8135172088623</v>
+        <v>-3176.771366113281</v>
       </c>
       <c r="E2">
         <v>10000</v>
       </c>
       <c r="F2">
-        <v>-0.009585546743203666</v>
+        <v>-0.01951470132938538</v>
       </c>
       <c r="G2">
-        <v>-1.360000689697267</v>
+        <v>-3.204202502441404</v>
       </c>
       <c r="H2">
-        <v>-0.004359760145087859</v>
+        <v>-0.009051351127888043</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>336.6700134277344</v>
+        <v>336.6400146484375</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2266,19 +2385,31 @@
         <v>2</v>
       </c>
       <c r="N2">
-        <v>3.875</v>
+        <v>3.845001220703125</v>
       </c>
       <c r="O2">
-        <v>0.01164380427485412</v>
+        <v>0.01155366236140454</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>-528.2349853515625</v>
+      </c>
+      <c r="R2">
+        <v>535.0700073242188</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>6.83502197265625</v>
+      </c>
+      <c r="V2">
+        <v>0.01293935873654273</v>
       </c>
       <c r="W2">
         <v>0</v>
@@ -2290,19 +2421,31 @@
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AE2">
+        <v>-256.2999877929688</v>
+      </c>
+      <c r="AF2">
+        <v>262.4299926757812</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="AI2">
+        <v>6.1300048828125</v>
+      </c>
+      <c r="AJ2">
+        <v>0.02391730462259778</v>
       </c>
       <c r="AK2">
         <v>1</v>
       </c>
       <c r="AM2">
-        <v>721.3099975585938</v>
+        <v>718.6699829101562</v>
       </c>
       <c r="AN2">
         <v>0</v>
@@ -2311,37 +2454,34 @@
         <v>1</v>
       </c>
       <c r="AP2">
-        <v>-11.89501953125</v>
+        <v>-14.5350341796875</v>
       </c>
       <c r="AQ2">
-        <v>-0.01622331988188297</v>
+        <v>-0.01982396988686519</v>
       </c>
       <c r="AR2">
         <v>1</v>
       </c>
-      <c r="AS2">
-        <v>-378.3500061035156</v>
-      </c>
       <c r="AT2">
-        <v>377.8099975585938</v>
+        <v>382.7000122070313</v>
       </c>
       <c r="AU2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV2">
         <v>2</v>
       </c>
       <c r="AW2">
-        <v>-0.540008544921875</v>
+        <v>4.350006103515682</v>
       </c>
       <c r="AX2">
-        <v>-0.001427272462562468</v>
+        <v>0.01149730681469996</v>
       </c>
       <c r="AY2">
         <v>1</v>
       </c>
       <c r="BA2">
-        <v>237.4700012207031</v>
+        <v>229.2799987792969</v>
       </c>
       <c r="BB2">
         <v>0</v>
@@ -2350,10 +2490,10 @@
         <v>4</v>
       </c>
       <c r="BD2">
-        <v>1.415008544921875</v>
+        <v>-6.774993896484375</v>
       </c>
       <c r="BE2">
-        <v>0.005994402104705143</v>
+        <v>-0.02870091337483271</v>
       </c>
       <c r="BF2">
         <v>0</v>
@@ -2368,7 +2508,7 @@
         <v>1</v>
       </c>
       <c r="BO2">
-        <v>54.95000076293945</v>
+        <v>55.52999877929688</v>
       </c>
       <c r="BP2">
         <v>0</v>
@@ -2377,10 +2517,10 @@
         <v>18</v>
       </c>
       <c r="BR2">
-        <v>2.370000762939455</v>
+        <v>2.949998779296884</v>
       </c>
       <c r="BS2">
-        <v>0.045074187199305</v>
+        <v>0.0561049596671146</v>
       </c>
       <c r="BT2">
         <v>0</v>
@@ -2404,7 +2544,7 @@
         <v>1</v>
       </c>
       <c r="CJ2">
-        <v>113.120002746582</v>
+        <v>104.6999969482422</v>
       </c>
       <c r="CK2">
         <v>0</v>
@@ -2413,28 +2553,52 @@
         <v>8</v>
       </c>
       <c r="CM2">
-        <v>-11.04999542236328</v>
+        <v>-19.47000122070312</v>
       </c>
       <c r="CN2">
-        <v>-0.08899086401957335</v>
+        <v>-0.1568011718435584</v>
       </c>
       <c r="CO2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CP2">
+        <v>-116.7699966430664</v>
+      </c>
+      <c r="CQ2">
+        <v>118.3899993896484</v>
       </c>
       <c r="CR2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CS2">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="CT2">
+        <v>1.620002746582031</v>
+      </c>
+      <c r="CU2">
+        <v>0.01387345031390153</v>
       </c>
       <c r="CV2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CW2">
+        <v>-945</v>
+      </c>
+      <c r="CX2">
+        <v>946.9199829101562</v>
       </c>
       <c r="CY2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CZ2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="DA2">
+        <v>1.91998291015625</v>
+      </c>
+      <c r="DB2">
+        <v>0.002031727947255257</v>
       </c>
       <c r="DC2">
         <v>0</v>
@@ -2467,7 +2631,7 @@
         <v>1</v>
       </c>
       <c r="DZ2">
-        <v>645.8599853515625</v>
+        <v>608.0999755859375</v>
       </c>
       <c r="EA2">
         <v>0</v>
@@ -2476,16 +2640,16 @@
         <v>1</v>
       </c>
       <c r="EC2">
-        <v>9.40997314453125</v>
+        <v>-28.35003662109375</v>
       </c>
       <c r="ED2">
-        <v>0.0147850938236298</v>
+        <v>-0.04454401143427389</v>
       </c>
       <c r="EE2">
         <v>1</v>
       </c>
       <c r="EG2">
-        <v>288.9800109863281</v>
+        <v>283.739990234375</v>
       </c>
       <c r="EH2">
         <v>0</v>
@@ -2494,10 +2658,10 @@
         <v>3</v>
       </c>
       <c r="EJ2">
-        <v>-1.019989013671875</v>
+        <v>-6.260009765625</v>
       </c>
       <c r="EK2">
-        <v>-0.003517203495420285</v>
+        <v>-0.02158624057112069</v>
       </c>
       <c r="EL2">
         <v>0</v>
@@ -2521,7 +2685,7 @@
         <v>1</v>
       </c>
       <c r="FB2">
-        <v>177.1199951171875</v>
+        <v>175.5</v>
       </c>
       <c r="FC2">
         <v>0</v>
@@ -2530,16 +2694,16 @@
         <v>5</v>
       </c>
       <c r="FE2">
-        <v>-9.264999389648466</v>
+        <v>-10.88499450683597</v>
       </c>
       <c r="FF2">
-        <v>-0.04970893399526677</v>
+        <v>-0.05840059461673419</v>
       </c>
       <c r="FG2">
         <v>1</v>
       </c>
       <c r="FI2">
-        <v>414.5199890136719</v>
+        <v>423.9599914550781</v>
       </c>
       <c r="FJ2">
         <v>0</v>
@@ -2548,10 +2712,10 @@
         <v>2</v>
       </c>
       <c r="FL2">
-        <v>8.04998779296875</v>
+        <v>17.489990234375</v>
       </c>
       <c r="FM2">
-        <v>0.01980462953918649</v>
+        <v>0.04302898167601388</v>
       </c>
       <c r="FN2">
         <v>0</v>
@@ -2566,7 +2730,7 @@
         <v>1</v>
       </c>
       <c r="FW2">
-        <v>520.6500244140625</v>
+        <v>507.0299987792969</v>
       </c>
       <c r="FX2">
         <v>0</v>
@@ -2575,10 +2739,10 @@
         <v>1</v>
       </c>
       <c r="FZ2">
-        <v>-25.3499755859375</v>
+        <v>-38.97000122070312</v>
       </c>
       <c r="GA2">
-        <v>-0.04642852671417119</v>
+        <v>-0.07137362860934637</v>
       </c>
     </row>
     <row r="3" spans="1:183">
@@ -2586,19 +2750,19 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>9950.788089754853</v>
+        <v>9904.144532567963</v>
       </c>
       <c r="C3">
-        <v>1918.657993319305</v>
+        <v>1161.844476110443</v>
       </c>
       <c r="D3">
-        <v>-546.0819</v>
+        <v>-756.8135172088623</v>
       </c>
       <c r="E3">
         <v>10000</v>
       </c>
       <c r="F3">
-        <v>-0.004921191024514715</v>
+        <v>-0.009585546743203666</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -2646,13 +2810,16 @@
         <v>1</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AS3">
+        <v>-378.3500061035156</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY3">
         <v>1</v>
@@ -2819,11 +2986,8 @@
       <c r="FU3">
         <v>1</v>
       </c>
-      <c r="FV3">
-        <v>-546</v>
-      </c>
       <c r="FX3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FY3">
         <v>1</v>
@@ -2834,28 +2998,25 @@
         <v>19</v>
       </c>
       <c r="B4">
-        <v>9970.279909493622</v>
+        <v>9950.788089754853</v>
       </c>
       <c r="C4">
-        <v>2464.739893319305</v>
+        <v>1918.657993319305</v>
       </c>
       <c r="D4">
-        <v>-1612.271831359497</v>
+        <v>-546.0819</v>
       </c>
       <c r="E4">
         <v>10000</v>
       </c>
       <c r="F4">
-        <v>-0.00297200905063788</v>
+        <v>-0.004921191024514715</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
-      <c r="J4">
-        <v>-332.7950134277344</v>
-      </c>
       <c r="L4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4">
         <v>2</v>
@@ -2926,11 +3087,8 @@
       <c r="BM4">
         <v>1</v>
       </c>
-      <c r="BN4">
-        <v>-52.58</v>
-      </c>
       <c r="BP4">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
         <v>18</v>
@@ -3071,13 +3229,16 @@
         <v>0</v>
       </c>
       <c r="FU4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FV4">
+        <v>-546</v>
       </c>
       <c r="FX4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FY4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:183">
@@ -3085,28 +3246,31 @@
         <v>20</v>
       </c>
       <c r="B5">
-        <v>9919.091680733491</v>
+        <v>9970.279909493622</v>
       </c>
       <c r="C5">
-        <v>4077.011724678802</v>
+        <v>2464.739893319305</v>
       </c>
       <c r="D5">
-        <v>-5922.988275321198</v>
+        <v>-1612.271831359497</v>
       </c>
       <c r="E5">
         <v>10000</v>
       </c>
       <c r="F5">
-        <v>-0.008090831926650943</v>
+        <v>-0.00297200905063788</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>-332.7950134277344</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -3138,11 +3302,8 @@
       <c r="AK5">
         <v>1</v>
       </c>
-      <c r="AL5">
-        <v>-733.2050170898438</v>
-      </c>
       <c r="AN5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO5">
         <v>1</v>
@@ -3159,11 +3320,8 @@
       <c r="AY5">
         <v>1</v>
       </c>
-      <c r="AZ5">
-        <v>-236.0549926757812</v>
-      </c>
       <c r="BB5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BC5">
         <v>4</v>
@@ -3178,13 +3336,16 @@
         <v>0</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BN5">
+        <v>-52.58</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BT5">
         <v>0</v>
@@ -3207,11 +3368,8 @@
       <c r="CH5">
         <v>1</v>
       </c>
-      <c r="CI5">
-        <v>-124.1699981689453</v>
-      </c>
       <c r="CK5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CL5">
         <v>8</v>
@@ -3264,11 +3422,8 @@
       <c r="DX5">
         <v>1</v>
       </c>
-      <c r="DY5">
-        <v>-636.4500122070312</v>
-      </c>
       <c r="EA5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB5">
         <v>1</v>
@@ -3276,11 +3431,8 @@
       <c r="EE5">
         <v>1</v>
       </c>
-      <c r="EF5">
-        <v>-290</v>
-      </c>
       <c r="EH5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="EI5">
         <v>3</v>
@@ -3306,11 +3458,8 @@
       <c r="EZ5">
         <v>1</v>
       </c>
-      <c r="FA5">
-        <v>-186.384994506836</v>
-      </c>
       <c r="FC5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="FD5">
         <v>5</v>
@@ -3318,11 +3467,8 @@
       <c r="FG5">
         <v>1</v>
       </c>
-      <c r="FH5">
-        <v>-406.4700012207031</v>
-      </c>
       <c r="FJ5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="FK5">
         <v>2</v>
@@ -3351,19 +3497,19 @@
         <v>21</v>
       </c>
       <c r="B6">
-        <v>10000</v>
+        <v>9919.091680733491</v>
       </c>
       <c r="C6">
-        <v>10000</v>
+        <v>4077.011724678802</v>
       </c>
       <c r="D6">
-        <v>10000</v>
+        <v>-5922.988275321198</v>
       </c>
       <c r="E6">
         <v>10000</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>-0.008090831926650943</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3402,13 +3548,16 @@
         <v>0</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AL6">
+        <v>-733.2050170898438</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3420,13 +3569,16 @@
         <v>0</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AZ6">
+        <v>-236.0549926757812</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF6">
         <v>0</v>
@@ -3465,13 +3617,16 @@
         <v>0</v>
       </c>
       <c r="CH6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CI6">
+        <v>-124.1699981689453</v>
       </c>
       <c r="CK6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CL6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CO6">
         <v>0</v>
@@ -3519,22 +3674,28 @@
         <v>0</v>
       </c>
       <c r="DX6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="DY6">
+        <v>-636.4500122070312</v>
       </c>
       <c r="EA6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EB6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EE6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="EF6">
+        <v>-290</v>
       </c>
       <c r="EH6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="EI6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="EL6">
         <v>0</v>
@@ -3555,22 +3716,28 @@
         <v>0</v>
       </c>
       <c r="EZ6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FA6">
+        <v>-186.384994506836</v>
       </c>
       <c r="FC6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="FD6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="FG6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FH6">
+        <v>-406.4700012207031</v>
       </c>
       <c r="FJ6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="FK6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="FN6">
         <v>0</v>
@@ -3588,11 +3755,256 @@
         <v>0</v>
       </c>
       <c r="FY6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:183">
+      <c r="A7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
+        <v>10000</v>
+      </c>
+      <c r="C7">
+        <v>10000</v>
+      </c>
+      <c r="D7">
+        <v>10000</v>
+      </c>
+      <c r="E7">
+        <v>10000</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CD7">
+        <v>0</v>
+      </c>
+      <c r="CE7">
+        <v>0</v>
+      </c>
+      <c r="CH7">
+        <v>0</v>
+      </c>
+      <c r="CK7">
+        <v>0</v>
+      </c>
+      <c r="CL7">
+        <v>0</v>
+      </c>
+      <c r="CO7">
+        <v>0</v>
+      </c>
+      <c r="CR7">
+        <v>0</v>
+      </c>
+      <c r="CS7">
+        <v>0</v>
+      </c>
+      <c r="CV7">
+        <v>0</v>
+      </c>
+      <c r="CY7">
+        <v>0</v>
+      </c>
+      <c r="CZ7">
+        <v>0</v>
+      </c>
+      <c r="DC7">
+        <v>0</v>
+      </c>
+      <c r="DF7">
+        <v>0</v>
+      </c>
+      <c r="DG7">
+        <v>0</v>
+      </c>
+      <c r="DJ7">
+        <v>0</v>
+      </c>
+      <c r="DM7">
+        <v>0</v>
+      </c>
+      <c r="DN7">
+        <v>0</v>
+      </c>
+      <c r="DQ7">
+        <v>0</v>
+      </c>
+      <c r="DT7">
+        <v>0</v>
+      </c>
+      <c r="DU7">
+        <v>0</v>
+      </c>
+      <c r="DX7">
+        <v>0</v>
+      </c>
+      <c r="EA7">
+        <v>0</v>
+      </c>
+      <c r="EB7">
+        <v>0</v>
+      </c>
+      <c r="EE7">
+        <v>0</v>
+      </c>
+      <c r="EH7">
+        <v>0</v>
+      </c>
+      <c r="EI7">
+        <v>0</v>
+      </c>
+      <c r="EL7">
+        <v>0</v>
+      </c>
+      <c r="EO7">
+        <v>0</v>
+      </c>
+      <c r="EP7">
+        <v>0</v>
+      </c>
+      <c r="ES7">
+        <v>0</v>
+      </c>
+      <c r="EV7">
+        <v>0</v>
+      </c>
+      <c r="EW7">
+        <v>0</v>
+      </c>
+      <c r="EZ7">
+        <v>0</v>
+      </c>
+      <c r="FC7">
+        <v>0</v>
+      </c>
+      <c r="FD7">
+        <v>0</v>
+      </c>
+      <c r="FG7">
+        <v>0</v>
+      </c>
+      <c r="FJ7">
+        <v>0</v>
+      </c>
+      <c r="FK7">
+        <v>0</v>
+      </c>
+      <c r="FN7">
+        <v>0</v>
+      </c>
+      <c r="FQ7">
+        <v>0</v>
+      </c>
+      <c r="FR7">
+        <v>0</v>
+      </c>
+      <c r="FU7">
+        <v>0</v>
+      </c>
+      <c r="FX7">
+        <v>0</v>
+      </c>
+      <c r="FY7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AA2:AA6">
+  <conditionalFormatting sqref="AA2:AA7">
     <cfRule type="cellIs" dxfId="4" priority="25" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3600,7 +4012,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE2:AE6">
+  <conditionalFormatting sqref="AE2:AE7">
     <cfRule type="cellIs" dxfId="4" priority="27" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3608,7 +4020,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF2:AF6">
+  <conditionalFormatting sqref="AF2:AF7">
     <cfRule type="cellIs" dxfId="4" priority="29" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3616,7 +4028,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG2:AG6">
+  <conditionalFormatting sqref="AG2:AG7">
     <cfRule type="cellIs" dxfId="4" priority="31" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3624,7 +4036,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH2:AH6">
+  <conditionalFormatting sqref="AH2:AH7">
     <cfRule type="cellIs" dxfId="4" priority="33" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3632,7 +4044,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL2:AL6">
+  <conditionalFormatting sqref="AL2:AL7">
     <cfRule type="cellIs" dxfId="4" priority="35" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3640,7 +4052,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM2:AM6">
+  <conditionalFormatting sqref="AM2:AM7">
     <cfRule type="cellIs" dxfId="4" priority="37" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3648,7 +4060,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AN2:AN6">
+  <conditionalFormatting sqref="AN2:AN7">
     <cfRule type="cellIs" dxfId="4" priority="39" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3656,7 +4068,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AO2:AO6">
+  <conditionalFormatting sqref="AO2:AO7">
     <cfRule type="cellIs" dxfId="4" priority="41" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3664,7 +4076,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AS2:AS6">
+  <conditionalFormatting sqref="AS2:AS7">
     <cfRule type="cellIs" dxfId="4" priority="43" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3672,7 +4084,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AT2:AT6">
+  <conditionalFormatting sqref="AT2:AT7">
     <cfRule type="cellIs" dxfId="4" priority="45" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3680,7 +4092,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU2:AU6">
+  <conditionalFormatting sqref="AU2:AU7">
     <cfRule type="cellIs" dxfId="4" priority="47" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3688,7 +4100,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AV2:AV6">
+  <conditionalFormatting sqref="AV2:AV7">
     <cfRule type="cellIs" dxfId="4" priority="49" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3696,7 +4108,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AZ2:AZ6">
+  <conditionalFormatting sqref="AZ2:AZ7">
     <cfRule type="cellIs" dxfId="4" priority="51" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3704,7 +4116,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BA2:BA6">
+  <conditionalFormatting sqref="BA2:BA7">
     <cfRule type="cellIs" dxfId="4" priority="53" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3712,7 +4124,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB2:BB6">
+  <conditionalFormatting sqref="BB2:BB7">
     <cfRule type="cellIs" dxfId="4" priority="55" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3720,7 +4132,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BC2:BC6">
+  <conditionalFormatting sqref="BC2:BC7">
     <cfRule type="cellIs" dxfId="4" priority="57" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3728,7 +4140,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BG2:BG6">
+  <conditionalFormatting sqref="BG2:BG7">
     <cfRule type="cellIs" dxfId="4" priority="59" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3736,7 +4148,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BH2:BH6">
+  <conditionalFormatting sqref="BH2:BH7">
     <cfRule type="cellIs" dxfId="4" priority="61" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3744,7 +4156,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BI2:BI6">
+  <conditionalFormatting sqref="BI2:BI7">
     <cfRule type="cellIs" dxfId="4" priority="63" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3752,7 +4164,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BJ2:BJ6">
+  <conditionalFormatting sqref="BJ2:BJ7">
     <cfRule type="cellIs" dxfId="4" priority="65" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3760,7 +4172,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BN2:BN6">
+  <conditionalFormatting sqref="BN2:BN7">
     <cfRule type="cellIs" dxfId="4" priority="67" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3768,7 +4180,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BO2:BO6">
+  <conditionalFormatting sqref="BO2:BO7">
     <cfRule type="cellIs" dxfId="4" priority="69" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3776,7 +4188,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BP2:BP6">
+  <conditionalFormatting sqref="BP2:BP7">
     <cfRule type="cellIs" dxfId="4" priority="71" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3784,7 +4196,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BQ2:BQ6">
+  <conditionalFormatting sqref="BQ2:BQ7">
     <cfRule type="cellIs" dxfId="4" priority="73" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3792,7 +4204,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BU2:BU6">
+  <conditionalFormatting sqref="BU2:BU7">
     <cfRule type="cellIs" dxfId="4" priority="75" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3800,7 +4212,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BV2:BV6">
+  <conditionalFormatting sqref="BV2:BV7">
     <cfRule type="cellIs" dxfId="4" priority="77" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3808,7 +4220,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BW2:BW6">
+  <conditionalFormatting sqref="BW2:BW7">
     <cfRule type="cellIs" dxfId="4" priority="79" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3816,7 +4228,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BX2:BX6">
+  <conditionalFormatting sqref="BX2:BX7">
     <cfRule type="cellIs" dxfId="4" priority="81" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3824,7 +4236,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CB2:CB6">
+  <conditionalFormatting sqref="CB2:CB7">
     <cfRule type="cellIs" dxfId="4" priority="83" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3832,7 +4244,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CC2:CC6">
+  <conditionalFormatting sqref="CC2:CC7">
     <cfRule type="cellIs" dxfId="4" priority="85" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3840,7 +4252,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CD2:CD6">
+  <conditionalFormatting sqref="CD2:CD7">
     <cfRule type="cellIs" dxfId="4" priority="87" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3848,7 +4260,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CE2:CE6">
+  <conditionalFormatting sqref="CE2:CE7">
     <cfRule type="cellIs" dxfId="4" priority="89" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3856,7 +4268,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CI2:CI6">
+  <conditionalFormatting sqref="CI2:CI7">
     <cfRule type="cellIs" dxfId="4" priority="91" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3864,7 +4276,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CJ2:CJ6">
+  <conditionalFormatting sqref="CJ2:CJ7">
     <cfRule type="cellIs" dxfId="4" priority="93" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3872,7 +4284,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CK2:CK6">
+  <conditionalFormatting sqref="CK2:CK7">
     <cfRule type="cellIs" dxfId="4" priority="95" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3880,7 +4292,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CL2:CL6">
+  <conditionalFormatting sqref="CL2:CL7">
     <cfRule type="cellIs" dxfId="4" priority="97" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3888,7 +4300,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CP2:CP6">
+  <conditionalFormatting sqref="CP2:CP7">
     <cfRule type="cellIs" dxfId="4" priority="99" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3896,7 +4308,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CQ2:CQ6">
+  <conditionalFormatting sqref="CQ2:CQ7">
     <cfRule type="cellIs" dxfId="4" priority="101" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3904,7 +4316,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CR2:CR6">
+  <conditionalFormatting sqref="CR2:CR7">
     <cfRule type="cellIs" dxfId="4" priority="103" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3912,7 +4324,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CS2:CS6">
+  <conditionalFormatting sqref="CS2:CS7">
     <cfRule type="cellIs" dxfId="4" priority="105" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3920,7 +4332,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CW2:CW6">
+  <conditionalFormatting sqref="CW2:CW7">
     <cfRule type="cellIs" dxfId="4" priority="107" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3928,7 +4340,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CX2:CX6">
+  <conditionalFormatting sqref="CX2:CX7">
     <cfRule type="cellIs" dxfId="4" priority="109" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3936,7 +4348,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CY2:CY6">
+  <conditionalFormatting sqref="CY2:CY7">
     <cfRule type="cellIs" dxfId="4" priority="111" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3944,7 +4356,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CZ2:CZ6">
+  <conditionalFormatting sqref="CZ2:CZ7">
     <cfRule type="cellIs" dxfId="4" priority="113" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3952,7 +4364,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
+  <conditionalFormatting sqref="D2:D7">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3960,7 +4372,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DD2:DD6">
+  <conditionalFormatting sqref="DD2:DD7">
     <cfRule type="cellIs" dxfId="4" priority="115" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3968,7 +4380,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DE2:DE6">
+  <conditionalFormatting sqref="DE2:DE7">
     <cfRule type="cellIs" dxfId="4" priority="117" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3976,7 +4388,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DF2:DF6">
+  <conditionalFormatting sqref="DF2:DF7">
     <cfRule type="cellIs" dxfId="4" priority="119" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3984,7 +4396,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DG2:DG6">
+  <conditionalFormatting sqref="DG2:DG7">
     <cfRule type="cellIs" dxfId="4" priority="121" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3992,7 +4404,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DK2:DK6">
+  <conditionalFormatting sqref="DK2:DK7">
     <cfRule type="cellIs" dxfId="4" priority="123" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4000,7 +4412,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DL2:DL6">
+  <conditionalFormatting sqref="DL2:DL7">
     <cfRule type="cellIs" dxfId="4" priority="125" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4008,7 +4420,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DM2:DM6">
+  <conditionalFormatting sqref="DM2:DM7">
     <cfRule type="cellIs" dxfId="4" priority="127" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4016,7 +4428,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DN2:DN6">
+  <conditionalFormatting sqref="DN2:DN7">
     <cfRule type="cellIs" dxfId="4" priority="129" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4024,7 +4436,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DR2:DR6">
+  <conditionalFormatting sqref="DR2:DR7">
     <cfRule type="cellIs" dxfId="4" priority="131" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4032,7 +4444,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DS2:DS6">
+  <conditionalFormatting sqref="DS2:DS7">
     <cfRule type="cellIs" dxfId="4" priority="133" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4040,7 +4452,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DT2:DT6">
+  <conditionalFormatting sqref="DT2:DT7">
     <cfRule type="cellIs" dxfId="4" priority="135" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4048,7 +4460,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DU2:DU6">
+  <conditionalFormatting sqref="DU2:DU7">
     <cfRule type="cellIs" dxfId="4" priority="137" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4056,7 +4468,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DY2:DY6">
+  <conditionalFormatting sqref="DY2:DY7">
     <cfRule type="cellIs" dxfId="4" priority="139" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4064,7 +4476,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DZ2:DZ6">
+  <conditionalFormatting sqref="DZ2:DZ7">
     <cfRule type="cellIs" dxfId="4" priority="141" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4072,7 +4484,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EA2:EA6">
+  <conditionalFormatting sqref="EA2:EA7">
     <cfRule type="cellIs" dxfId="4" priority="143" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4080,7 +4492,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EB2:EB6">
+  <conditionalFormatting sqref="EB2:EB7">
     <cfRule type="cellIs" dxfId="4" priority="145" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4088,7 +4500,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EF2:EF6">
+  <conditionalFormatting sqref="EF2:EF7">
     <cfRule type="cellIs" dxfId="4" priority="147" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4096,7 +4508,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EG2:EG6">
+  <conditionalFormatting sqref="EG2:EG7">
     <cfRule type="cellIs" dxfId="4" priority="149" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4104,7 +4516,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EH2:EH6">
+  <conditionalFormatting sqref="EH2:EH7">
     <cfRule type="cellIs" dxfId="4" priority="151" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4112,7 +4524,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EI2:EI6">
+  <conditionalFormatting sqref="EI2:EI7">
     <cfRule type="cellIs" dxfId="4" priority="153" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4120,7 +4532,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EM2:EM6">
+  <conditionalFormatting sqref="EM2:EM7">
     <cfRule type="cellIs" dxfId="4" priority="155" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4128,7 +4540,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EN2:EN6">
+  <conditionalFormatting sqref="EN2:EN7">
     <cfRule type="cellIs" dxfId="4" priority="157" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4136,7 +4548,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EO2:EO6">
+  <conditionalFormatting sqref="EO2:EO7">
     <cfRule type="cellIs" dxfId="4" priority="159" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4144,7 +4556,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EP2:EP6">
+  <conditionalFormatting sqref="EP2:EP7">
     <cfRule type="cellIs" dxfId="4" priority="161" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4152,7 +4564,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="ET2:ET6">
+  <conditionalFormatting sqref="ET2:ET7">
     <cfRule type="cellIs" dxfId="4" priority="163" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4160,7 +4572,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EU2:EU6">
+  <conditionalFormatting sqref="EU2:EU7">
     <cfRule type="cellIs" dxfId="4" priority="165" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4168,7 +4580,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EV2:EV6">
+  <conditionalFormatting sqref="EV2:EV7">
     <cfRule type="cellIs" dxfId="4" priority="167" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4176,7 +4588,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EW2:EW6">
+  <conditionalFormatting sqref="EW2:EW7">
     <cfRule type="cellIs" dxfId="4" priority="169" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4184,7 +4596,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FA2:FA6">
+  <conditionalFormatting sqref="FA2:FA7">
     <cfRule type="cellIs" dxfId="4" priority="171" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4192,7 +4604,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FB2:FB6">
+  <conditionalFormatting sqref="FB2:FB7">
     <cfRule type="cellIs" dxfId="4" priority="173" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4200,7 +4612,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FC2:FC6">
+  <conditionalFormatting sqref="FC2:FC7">
     <cfRule type="cellIs" dxfId="4" priority="175" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4208,7 +4620,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FD2:FD6">
+  <conditionalFormatting sqref="FD2:FD7">
     <cfRule type="cellIs" dxfId="4" priority="177" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4216,7 +4628,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FH2:FH6">
+  <conditionalFormatting sqref="FH2:FH7">
     <cfRule type="cellIs" dxfId="4" priority="179" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4224,7 +4636,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FI2:FI6">
+  <conditionalFormatting sqref="FI2:FI7">
     <cfRule type="cellIs" dxfId="4" priority="181" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4232,7 +4644,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FJ2:FJ6">
+  <conditionalFormatting sqref="FJ2:FJ7">
     <cfRule type="cellIs" dxfId="4" priority="183" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4240,7 +4652,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FK2:FK6">
+  <conditionalFormatting sqref="FK2:FK7">
     <cfRule type="cellIs" dxfId="4" priority="185" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4248,7 +4660,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FO2:FO6">
+  <conditionalFormatting sqref="FO2:FO7">
     <cfRule type="cellIs" dxfId="4" priority="187" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4256,7 +4668,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FP2:FP6">
+  <conditionalFormatting sqref="FP2:FP7">
     <cfRule type="cellIs" dxfId="4" priority="189" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4264,7 +4676,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FQ2:FQ6">
+  <conditionalFormatting sqref="FQ2:FQ7">
     <cfRule type="cellIs" dxfId="4" priority="191" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4272,7 +4684,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FR2:FR6">
+  <conditionalFormatting sqref="FR2:FR7">
     <cfRule type="cellIs" dxfId="4" priority="193" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4280,7 +4692,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FV2:FV6">
+  <conditionalFormatting sqref="FV2:FV7">
     <cfRule type="cellIs" dxfId="4" priority="195" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4288,7 +4700,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FW2:FW6">
+  <conditionalFormatting sqref="FW2:FW7">
     <cfRule type="cellIs" dxfId="4" priority="197" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4296,7 +4708,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FX2:FX6">
+  <conditionalFormatting sqref="FX2:FX7">
     <cfRule type="cellIs" dxfId="4" priority="199" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4304,7 +4716,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FY2:FY6">
+  <conditionalFormatting sqref="FY2:FY7">
     <cfRule type="cellIs" dxfId="4" priority="201" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4312,7 +4724,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
+  <conditionalFormatting sqref="J2:J7">
     <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4320,7 +4732,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
+  <conditionalFormatting sqref="K2:K7">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4328,7 +4740,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
+  <conditionalFormatting sqref="L2:L7">
     <cfRule type="cellIs" dxfId="4" priority="7" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4336,7 +4748,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M6">
+  <conditionalFormatting sqref="M2:M7">
     <cfRule type="cellIs" dxfId="4" priority="9" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4344,7 +4756,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q6">
+  <conditionalFormatting sqref="Q2:Q7">
     <cfRule type="cellIs" dxfId="4" priority="11" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4352,7 +4764,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R6">
+  <conditionalFormatting sqref="R2:R7">
     <cfRule type="cellIs" dxfId="4" priority="13" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4360,7 +4772,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S6">
+  <conditionalFormatting sqref="S2:S7">
     <cfRule type="cellIs" dxfId="4" priority="15" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4368,7 +4780,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T6">
+  <conditionalFormatting sqref="T2:T7">
     <cfRule type="cellIs" dxfId="4" priority="17" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4376,7 +4788,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X6">
+  <conditionalFormatting sqref="X2:X7">
     <cfRule type="cellIs" dxfId="4" priority="19" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4384,7 +4796,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y6">
+  <conditionalFormatting sqref="Y2:Y7">
     <cfRule type="cellIs" dxfId="4" priority="21" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4392,7 +4804,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:Z6">
+  <conditionalFormatting sqref="Z2:Z7">
     <cfRule type="cellIs" dxfId="4" priority="23" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>

--- a/reports/paper_trade_trx.xlsx
+++ b/reports/paper_trade_trx.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="245">
   <si>
     <t>NAV</t>
   </si>
@@ -36,7 +36,7 @@
     <t>last_updated</t>
   </si>
   <si>
-    <t>2026-10-09 18:01:22</t>
+    <t>2026-10-14 18:01:25</t>
   </si>
   <si>
     <t>pf_id</t>
@@ -69,6 +69,12 @@
     <t>date</t>
   </si>
   <si>
+    <t>2026-10-14</t>
+  </si>
+  <si>
+    <t>2026-10-13</t>
+  </si>
+  <si>
     <t>2026-10-09</t>
   </si>
   <si>
@@ -87,100 +93,118 @@
     <t>2026-09-29</t>
   </si>
   <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t>INTU</t>
+  </si>
+  <si>
+    <t>INTC</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>COST</t>
+  </si>
+  <si>
+    <t>CSCO</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
     <t>MSFT</t>
   </si>
   <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>CSCO</t>
-  </si>
-  <si>
-    <t>COST</t>
-  </si>
-  <si>
     <t>TSLA</t>
   </si>
   <si>
-    <t>AMAT</t>
+    <t>PYPL</t>
   </si>
   <si>
     <t>AAPL</t>
   </si>
   <si>
-    <t>PYPL</t>
-  </si>
-  <si>
     <t>META</t>
   </si>
   <si>
+    <t>ISRG</t>
+  </si>
+  <si>
+    <t>QCOM</t>
+  </si>
+  <si>
+    <t>TXN</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
     <t>NVDA</t>
   </si>
   <si>
-    <t>INTC</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>TXN</t>
-  </si>
-  <si>
-    <t>QCOM</t>
-  </si>
-  <si>
-    <t>ISRG</t>
-  </si>
-  <si>
     <t>paper_trade</t>
   </si>
   <si>
     <t>initial</t>
   </si>
   <si>
+    <t>2026-10-14_26ca0548a178a1891287462eabd2327f</t>
+  </si>
+  <si>
+    <t>2026-10-14_12c67069830168f19e8792721e813c67</t>
+  </si>
+  <si>
+    <t>2026-10-13_72df83729c3b83b5284ef41028e4c952</t>
+  </si>
+  <si>
+    <t>2026-10-13_572bd3499a20b8e64a30af391461ef95</t>
+  </si>
+  <si>
+    <t>2026-10-09_cbfa34b7b92b8c9ddd53b2ba7394c363</t>
+  </si>
+  <si>
+    <t>2026-10-09_a65360c396f5991e9fa841dde59b8684</t>
+  </si>
+  <si>
+    <t>2026-10-09_603d3f285d1e0ad7f8d04d423ef9ecc5</t>
+  </si>
+  <si>
     <t>2026-10-09_4c574a6fffe0157d7c23fe8d2682dfb9</t>
   </si>
   <si>
-    <t>2026-10-09_603d3f285d1e0ad7f8d04d423ef9ecc5</t>
-  </si>
-  <si>
-    <t>2026-10-09_a65360c396f5991e9fa841dde59b8684</t>
-  </si>
-  <si>
-    <t>2026-10-09_cbfa34b7b92b8c9ddd53b2ba7394c363</t>
-  </si>
-  <si>
     <t>2026-10-07_dc7e32e4c69a2eb8b2d77f7cc32b45cf</t>
   </si>
   <si>
     <t>2026-10-06_53d2d3c2d4f2ff367a516a1f406e1bbb</t>
   </si>
   <si>
+    <t>2026-10-05_012c952fa1db120c5531512fa2448109</t>
+  </si>
+  <si>
     <t>2026-10-05_59e0a8bb4acd7dbfa1963226e5a0766c</t>
   </si>
   <si>
-    <t>2026-10-05_012c952fa1db120c5531512fa2448109</t>
-  </si>
-  <si>
     <t>2026-10-02_4cd245c09bc16a9a0ea92b28c74e67fc</t>
   </si>
   <si>
+    <t>2026-10-02_16129b154d393f9ae572f8ee04a0bdd7</t>
+  </si>
+  <si>
+    <t>2026-10-02_550f777fdf4defe6e05eb6aaa433e1f6</t>
+  </si>
+  <si>
+    <t>2026-10-02_49d5d47fa7cf3284a8706a7cac2b06ce</t>
+  </si>
+  <si>
+    <t>2026-10-02_087e2d99b729010b96e6f4995922a10e</t>
+  </si>
+  <si>
+    <t>2026-10-02_374e5bf40407d1d5c6e8be83ecfa25e0</t>
+  </si>
+  <si>
     <t>2026-10-02_0ef6ea276d632b306bbc10bc95cbf29d</t>
-  </si>
-  <si>
-    <t>2026-10-02_374e5bf40407d1d5c6e8be83ecfa25e0</t>
-  </si>
-  <si>
-    <t>2026-10-02_087e2d99b729010b96e6f4995922a10e</t>
-  </si>
-  <si>
-    <t>2026-10-02_49d5d47fa7cf3284a8706a7cac2b06ce</t>
-  </si>
-  <si>
-    <t>2026-10-02_550f777fdf4defe6e05eb6aaa433e1f6</t>
-  </si>
-  <si>
-    <t>2026-10-02_16129b154d393f9ae572f8ee04a0bdd7</t>
   </si>
   <si>
     <t>2026-09-29_6ee3325c3a5f92372b30d30b7a1c628c</t>
@@ -1251,7 +1275,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>9805</v>
+        <v>9600</v>
       </c>
       <c r="C2" s="2">
         <v>100</v>
@@ -1275,7 +1299,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>9805</v>
+        <v>9600</v>
       </c>
       <c r="C4" s="2">
         <v>100</v>
@@ -1346,7 +1370,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
@@ -1392,19 +1416,19 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2">
-        <v>-528.2349853515625</v>
+        <v>25</v>
+      </c>
+      <c r="F2">
+        <v>454.15</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1415,88 +1439,88 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>-256.2999877929688</v>
+        <v>-301.6000061035156</v>
       </c>
       <c r="G3">
         <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4">
-        <v>-116.7699966430664</v>
+        <v>27</v>
+      </c>
+      <c r="F4">
+        <v>99.54000091552734</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>-8</v>
       </c>
       <c r="H4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>-945</v>
+        <v>-356.2999877929688</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>-378.3500061035156</v>
+        <v>-945</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1507,88 +1531,88 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>-546</v>
+        <v>-116.7699966430664</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>-332.7950134277344</v>
+        <v>-256.2999877929688</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E9">
-        <v>-52.58</v>
+        <v>-528.2349853515625</v>
       </c>
       <c r="G9">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E10">
-        <v>-733.2050170898438</v>
+        <v>-378.3500061035156</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1599,160 +1623,252 @@
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E11">
-        <v>-236.0549926757812</v>
+        <v>-546</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12">
-        <v>-124.1699981689453</v>
+        <v>-52.58</v>
       </c>
       <c r="G12">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J12" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13">
-        <v>-636.4500122070312</v>
+        <v>-332.7950134277344</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J13" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14">
-        <v>-290</v>
+        <v>-733.2050170898438</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J14" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15">
-        <v>-186.384994506836</v>
+        <v>-406.4700012207031</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H15" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J15" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E16">
-        <v>-406.4700012207031</v>
+        <v>-186.384994506836</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H16" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J16" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
       </c>
-      <c r="C17">
+      <c r="D17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17">
+        <v>-290</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+      <c r="H17" t="s">
+        <v>42</v>
+      </c>
+      <c r="J17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18">
+        <v>-636.4500122070312</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19">
+        <v>-124.1699981689453</v>
+      </c>
+      <c r="G19">
+        <v>8</v>
+      </c>
+      <c r="H19" t="s">
+        <v>42</v>
+      </c>
+      <c r="J19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20">
+        <v>-236.0549926757812</v>
+      </c>
+      <c r="G20">
+        <v>4</v>
+      </c>
+      <c r="H20" t="s">
+        <v>42</v>
+      </c>
+      <c r="J20" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21">
         <v>10000</v>
       </c>
-      <c r="H17" t="s">
-        <v>39</v>
-      </c>
-      <c r="J17" t="s">
-        <v>55</v>
+      <c r="H21" t="s">
+        <v>43</v>
+      </c>
+      <c r="J21" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B17">
+  <conditionalFormatting sqref="B2:B21">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>$B2="option"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C17">
+  <conditionalFormatting sqref="C2:C21">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1760,7 +1876,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E17">
+  <conditionalFormatting sqref="E2:E21">
     <cfRule type="cellIs" dxfId="4" priority="4" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1768,7 +1884,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F17">
+  <conditionalFormatting sqref="F2:F21">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1776,7 +1892,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G17">
+  <conditionalFormatting sqref="G2:G21">
     <cfRule type="cellIs" dxfId="4" priority="8" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1790,7 +1906,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:GA7"/>
+  <dimension ref="A1:GA9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
@@ -1798,10 +1914,10 @@
   <sheetData>
     <row r="1" spans="1:183">
       <c r="A1" s="3" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>3</v>
@@ -1810,541 +1926,541 @@
         <v>8</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AL1" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="BE1" s="3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="BF1" s="3" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="BL1" s="3" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="BM1" s="3" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="BN1" s="3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="BO1" s="3" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="BP1" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="BQ1" s="3" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="BR1" s="3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="BS1" s="3" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="BT1" s="3" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="BU1" s="3" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="BV1" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="BW1" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="BX1" s="3" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="BY1" s="3" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="BZ1" s="3" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="CA1" s="3" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="CB1" s="3" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="CC1" s="3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="CD1" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="CE1" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="CF1" s="3" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="CH1" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="CI1" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="CJ1" s="3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="CK1" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="CL1" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="CM1" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="CN1" s="3" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="CO1" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="CP1" s="3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="CQ1" s="3" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="CR1" s="3" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="CS1" s="3" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="CT1" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="CU1" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="CV1" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="CW1" s="3" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="CX1" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="CY1" s="3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="CZ1" s="3" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="DA1" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="DB1" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="DC1" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="DD1" s="3" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="DE1" s="3" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="DF1" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="DG1" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="DH1" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="DI1" s="3" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="DJ1" s="3" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="DK1" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="DL1" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="DM1" s="3" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="DN1" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="DO1" s="3" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="DP1" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="DQ1" s="3" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="DR1" s="3" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="DS1" s="3" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="DT1" s="3" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="DU1" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="DV1" s="3" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="DW1" s="3" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="DX1" s="3" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="DY1" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="DZ1" s="3" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="EA1" s="3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="EB1" s="3" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="EC1" s="3" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="ED1" s="3" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="EE1" s="3" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="EF1" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="EG1" s="3" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="EH1" s="3" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="EI1" s="3" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="EJ1" s="3" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="EK1" s="3" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="EL1" s="3" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="EM1" s="3" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="EN1" s="3" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="EO1" s="3" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="EP1" s="3" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="EQ1" s="3" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="ER1" s="3" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="ES1" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="ET1" s="3" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="EU1" s="3" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="EV1" s="3" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="EW1" s="3" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="EX1" s="3" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="EY1" s="3" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="EZ1" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="FA1" s="3" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="FB1" s="3" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="FC1" s="3" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="FD1" s="3" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="FE1" s="3" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="FF1" s="3" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="FG1" s="3" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="FH1" s="3" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="FI1" s="3" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="FJ1" s="3" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="FK1" s="3" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="FL1" s="3" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="FM1" s="3" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="FN1" s="3" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="FO1" s="3" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="FP1" s="3" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="FQ1" s="3" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="FR1" s="3" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="FS1" s="3" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="FT1" s="3" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="FU1" s="3" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="FV1" s="3" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="FW1" s="3" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="FX1" s="3" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="FY1" s="3" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="FZ1" s="3" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="GA1" s="3" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:183">
@@ -2352,31 +2468,31 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>9804.852986706146</v>
+        <v>9600.492880668853</v>
       </c>
       <c r="C2">
-        <v>-2014.926890002838</v>
+        <v>-2382.287057075287</v>
       </c>
       <c r="D2">
-        <v>-3176.771366113281</v>
+        <v>-450.8538608132935</v>
       </c>
       <c r="E2">
         <v>10000</v>
       </c>
       <c r="F2">
-        <v>-0.01951470132938538</v>
+        <v>-0.03995071193311472</v>
       </c>
       <c r="G2">
-        <v>-3.204202502441404</v>
+        <v>-5.498600756835939</v>
       </c>
       <c r="H2">
-        <v>-0.009051351127888043</v>
+        <v>-0.01252882053325666</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>336.6400146484375</v>
+        <v>342.9599914550781</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2385,67 +2501,70 @@
         <v>2</v>
       </c>
       <c r="N2">
-        <v>3.845001220703125</v>
+        <v>10.16497802734375</v>
       </c>
       <c r="O2">
-        <v>0.01155366236140454</v>
+        <v>0.03054426183447312</v>
       </c>
       <c r="P2">
         <v>1</v>
       </c>
-      <c r="Q2">
-        <v>-528.2349853515625</v>
-      </c>
       <c r="R2">
-        <v>535.0700073242188</v>
+        <v>533.6900024414062</v>
       </c>
       <c r="S2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>6.83502197265625</v>
+        <v>5.45501708984375</v>
       </c>
       <c r="V2">
-        <v>0.01293935873654273</v>
+        <v>0.0103268758054964</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>347.6400146484375</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AB2">
+        <v>-8.65997314453125</v>
+      </c>
+      <c r="AC2">
+        <v>-0.02430528611065574</v>
       </c>
       <c r="AD2">
         <v>1</v>
       </c>
-      <c r="AE2">
-        <v>-256.2999877929688</v>
-      </c>
       <c r="AF2">
-        <v>262.4299926757812</v>
+        <v>254.0800018310547</v>
       </c>
       <c r="AG2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH2">
         <v>3</v>
       </c>
       <c r="AI2">
-        <v>6.1300048828125</v>
+        <v>-2.219985961914062</v>
       </c>
       <c r="AJ2">
-        <v>0.02391730462259778</v>
+        <v>-0.008661670182002923</v>
       </c>
       <c r="AK2">
         <v>1</v>
       </c>
       <c r="AM2">
-        <v>718.6699829101562</v>
+        <v>737.5399780273438</v>
       </c>
       <c r="AN2">
         <v>0</v>
@@ -2454,16 +2573,16 @@
         <v>1</v>
       </c>
       <c r="AP2">
-        <v>-14.5350341796875</v>
+        <v>4.3349609375</v>
       </c>
       <c r="AQ2">
-        <v>-0.01982396988686519</v>
+        <v>0.005912344891890964</v>
       </c>
       <c r="AR2">
         <v>1</v>
       </c>
       <c r="AT2">
-        <v>382.7000122070313</v>
+        <v>367.1600036621094</v>
       </c>
       <c r="AU2">
         <v>0</v>
@@ -2472,16 +2591,16 @@
         <v>2</v>
       </c>
       <c r="AW2">
-        <v>4.350006103515682</v>
+        <v>-11.19000244140625</v>
       </c>
       <c r="AX2">
-        <v>0.01149730681469996</v>
+        <v>-0.02957579558844958</v>
       </c>
       <c r="AY2">
         <v>1</v>
       </c>
       <c r="BA2">
-        <v>229.2799987792969</v>
+        <v>221.3000030517578</v>
       </c>
       <c r="BB2">
         <v>0</v>
@@ -2490,10 +2609,10 @@
         <v>4</v>
       </c>
       <c r="BD2">
-        <v>-6.774993896484375</v>
+        <v>-14.75498962402344</v>
       </c>
       <c r="BE2">
-        <v>-0.02870091337483271</v>
+        <v>-0.06250657720376729</v>
       </c>
       <c r="BF2">
         <v>0</v>
@@ -2508,7 +2627,7 @@
         <v>1</v>
       </c>
       <c r="BO2">
-        <v>55.52999877929688</v>
+        <v>56.09999847412109</v>
       </c>
       <c r="BP2">
         <v>0</v>
@@ -2517,10 +2636,10 @@
         <v>18</v>
       </c>
       <c r="BR2">
-        <v>2.949998779296884</v>
+        <v>3.519998474121088</v>
       </c>
       <c r="BS2">
-        <v>0.0561049596671146</v>
+        <v>0.06694557767442166</v>
       </c>
       <c r="BT2">
         <v>0</v>
@@ -2541,64 +2660,49 @@
         <v>0</v>
       </c>
       <c r="CH2">
-        <v>1</v>
-      </c>
-      <c r="CJ2">
-        <v>104.6999969482422</v>
+        <v>0</v>
       </c>
       <c r="CK2">
         <v>0</v>
       </c>
       <c r="CL2">
-        <v>8</v>
-      </c>
-      <c r="CM2">
-        <v>-19.47000122070312</v>
-      </c>
-      <c r="CN2">
-        <v>-0.1568011718435584</v>
+        <v>0</v>
       </c>
       <c r="CO2">
         <v>1</v>
       </c>
-      <c r="CP2">
-        <v>-116.7699966430664</v>
-      </c>
       <c r="CQ2">
-        <v>118.3899993896484</v>
+        <v>113.6399993896484</v>
       </c>
       <c r="CR2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CS2">
         <v>8</v>
       </c>
       <c r="CT2">
-        <v>1.620002746582031</v>
+        <v>-3.129997253417969</v>
       </c>
       <c r="CU2">
-        <v>0.01387345031390153</v>
+        <v>-0.0268048072570003</v>
       </c>
       <c r="CV2">
         <v>1</v>
       </c>
-      <c r="CW2">
-        <v>-945</v>
-      </c>
       <c r="CX2">
-        <v>946.9199829101562</v>
+        <v>982</v>
       </c>
       <c r="CY2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CZ2">
         <v>1</v>
       </c>
       <c r="DA2">
-        <v>1.91998291015625</v>
+        <v>37</v>
       </c>
       <c r="DB2">
-        <v>0.002031727947255257</v>
+        <v>0.03915343915343916</v>
       </c>
       <c r="DC2">
         <v>0</v>
@@ -2631,7 +2735,7 @@
         <v>1</v>
       </c>
       <c r="DZ2">
-        <v>608.0999755859375</v>
+        <v>570.8200073242188</v>
       </c>
       <c r="EA2">
         <v>0</v>
@@ -2640,16 +2744,16 @@
         <v>1</v>
       </c>
       <c r="EC2">
-        <v>-28.35003662109375</v>
+        <v>-65.6300048828125</v>
       </c>
       <c r="ED2">
-        <v>-0.04454401143427389</v>
+        <v>-0.1031188681342403</v>
       </c>
       <c r="EE2">
         <v>1</v>
       </c>
       <c r="EG2">
-        <v>283.739990234375</v>
+        <v>280.6499938964844</v>
       </c>
       <c r="EH2">
         <v>0</v>
@@ -2658,19 +2762,31 @@
         <v>3</v>
       </c>
       <c r="EJ2">
-        <v>-6.260009765625</v>
+        <v>-9.350006103515625</v>
       </c>
       <c r="EK2">
-        <v>-0.02158624057112069</v>
+        <v>-0.03224140035695044</v>
       </c>
       <c r="EL2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="EM2">
+        <v>-301.6000061035156</v>
+      </c>
+      <c r="EN2">
+        <v>310.4400024414062</v>
       </c>
       <c r="EO2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="EP2">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="EQ2">
+        <v>8.839996337890625</v>
+      </c>
+      <c r="ER2">
+        <v>0.02931033209215705</v>
       </c>
       <c r="ES2">
         <v>0</v>
@@ -2685,7 +2801,7 @@
         <v>1</v>
       </c>
       <c r="FB2">
-        <v>175.5</v>
+        <v>172.6199951171875</v>
       </c>
       <c r="FC2">
         <v>0</v>
@@ -2694,16 +2810,16 @@
         <v>5</v>
       </c>
       <c r="FE2">
-        <v>-10.88499450683597</v>
+        <v>-13.76499938964847</v>
       </c>
       <c r="FF2">
-        <v>-0.05840059461673419</v>
+        <v>-0.07385250849227354</v>
       </c>
       <c r="FG2">
         <v>1</v>
       </c>
       <c r="FI2">
-        <v>423.9599914550781</v>
+        <v>420.239990234375</v>
       </c>
       <c r="FJ2">
         <v>0</v>
@@ -2712,10 +2828,10 @@
         <v>2</v>
       </c>
       <c r="FL2">
-        <v>17.489990234375</v>
+        <v>13.76998901367188</v>
       </c>
       <c r="FM2">
-        <v>0.04302898167601388</v>
+        <v>0.03387701176548852</v>
       </c>
       <c r="FN2">
         <v>0</v>
@@ -2727,22 +2843,22 @@
         <v>0</v>
       </c>
       <c r="FU2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FW2">
-        <v>507.0299987792969</v>
+        <v>454.15</v>
       </c>
       <c r="FX2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="FY2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FZ2">
-        <v>-38.97000122070312</v>
+        <v>-91.85000000000002</v>
       </c>
       <c r="GA2">
-        <v>-0.07137362860934637</v>
+        <v>-0.1682234432234433</v>
       </c>
     </row>
     <row r="3" spans="1:183">
@@ -2750,19 +2866,25 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>9904.144532567963</v>
+        <v>9752.886795803435</v>
       </c>
       <c r="C3">
-        <v>1161.844476110443</v>
+        <v>-1931.433196261994</v>
       </c>
       <c r="D3">
-        <v>-756.8135172088623</v>
+        <v>83.49369374084472</v>
       </c>
       <c r="E3">
         <v>10000</v>
       </c>
       <c r="F3">
-        <v>-0.009585546743203666</v>
+        <v>-0.02471132041965651</v>
+      </c>
+      <c r="G3">
+        <v>-0.9851998901367194</v>
+      </c>
+      <c r="H3">
+        <v>-0.007934282875612668</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -2774,31 +2896,34 @@
         <v>2</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X3">
+        <v>-356.2999877929688</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3">
         <v>0</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK3">
         <v>1</v>
@@ -2812,11 +2937,8 @@
       <c r="AR3">
         <v>1</v>
       </c>
-      <c r="AS3">
-        <v>-378.3500061035156</v>
-      </c>
       <c r="AU3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV3">
         <v>2</v>
@@ -2867,31 +2989,40 @@
         <v>0</v>
       </c>
       <c r="CH3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="CJ3">
+        <v>99.54000091552734</v>
       </c>
       <c r="CK3">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="CL3">
+        <v>0</v>
+      </c>
+      <c r="CM3">
+        <v>-24.62999725341798</v>
+      </c>
+      <c r="CN3">
+        <v>-0.1983570718903167</v>
+      </c>
+      <c r="CO3">
+        <v>1</v>
+      </c>
+      <c r="CR3">
+        <v>0</v>
+      </c>
+      <c r="CS3">
         <v>8</v>
       </c>
-      <c r="CO3">
-        <v>0</v>
-      </c>
-      <c r="CR3">
-        <v>0</v>
-      </c>
-      <c r="CS3">
-        <v>0</v>
-      </c>
       <c r="CV3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY3">
         <v>0</v>
       </c>
       <c r="CZ3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC3">
         <v>0</v>
@@ -2998,19 +3129,19 @@
         <v>19</v>
       </c>
       <c r="B4">
-        <v>9950.788089754853</v>
+        <v>9804.852986706146</v>
       </c>
       <c r="C4">
-        <v>1918.657993319305</v>
+        <v>-2014.926890002838</v>
       </c>
       <c r="D4">
-        <v>-546.0819</v>
+        <v>-3176.771366113281</v>
       </c>
       <c r="E4">
         <v>10000</v>
       </c>
       <c r="F4">
-        <v>-0.004921191024514715</v>
+        <v>-0.01951470132938538</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -3022,13 +3153,16 @@
         <v>2</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>-528.2349853515625</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4">
         <v>0</v>
@@ -3040,13 +3174,16 @@
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AE4">
+        <v>-256.2999877929688</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK4">
         <v>1</v>
@@ -3058,13 +3195,13 @@
         <v>1</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU4">
         <v>0</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY4">
         <v>1</v>
@@ -3121,22 +3258,28 @@
         <v>8</v>
       </c>
       <c r="CO4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CP4">
+        <v>-116.7699966430664</v>
       </c>
       <c r="CR4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CS4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CV4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CW4">
+        <v>-945</v>
       </c>
       <c r="CY4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CZ4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC4">
         <v>0</v>
@@ -3231,11 +3374,8 @@
       <c r="FU4">
         <v>1</v>
       </c>
-      <c r="FV4">
-        <v>-546</v>
-      </c>
       <c r="FX4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FY4">
         <v>1</v>
@@ -3246,28 +3386,25 @@
         <v>20</v>
       </c>
       <c r="B5">
-        <v>9970.279909493622</v>
+        <v>9904.144532567963</v>
       </c>
       <c r="C5">
-        <v>2464.739893319305</v>
+        <v>1161.844476110443</v>
       </c>
       <c r="D5">
-        <v>-1612.271831359497</v>
+        <v>-756.8135172088623</v>
       </c>
       <c r="E5">
         <v>10000</v>
       </c>
       <c r="F5">
-        <v>-0.00297200905063788</v>
+        <v>-0.009585546743203666</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
-      <c r="J5">
-        <v>-332.7950134277344</v>
-      </c>
       <c r="L5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5">
         <v>2</v>
@@ -3309,13 +3446,16 @@
         <v>1</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AS5">
+        <v>-378.3500061035156</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY5">
         <v>1</v>
@@ -3338,11 +3478,8 @@
       <c r="BM5">
         <v>1</v>
       </c>
-      <c r="BN5">
-        <v>-52.58</v>
-      </c>
       <c r="BP5">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BQ5">
         <v>18</v>
@@ -3483,13 +3620,13 @@
         <v>0</v>
       </c>
       <c r="FU5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FX5">
         <v>0</v>
       </c>
       <c r="FY5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:183">
@@ -3497,28 +3634,28 @@
         <v>21</v>
       </c>
       <c r="B6">
-        <v>9919.091680733491</v>
+        <v>9950.788089754853</v>
       </c>
       <c r="C6">
-        <v>4077.011724678802</v>
+        <v>1918.657993319305</v>
       </c>
       <c r="D6">
-        <v>-5922.988275321198</v>
+        <v>-546.0819</v>
       </c>
       <c r="E6">
         <v>10000</v>
       </c>
       <c r="F6">
-        <v>-0.008090831926650943</v>
+        <v>-0.004921191024514715</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -3550,11 +3687,8 @@
       <c r="AK6">
         <v>1</v>
       </c>
-      <c r="AL6">
-        <v>-733.2050170898438</v>
-      </c>
       <c r="AN6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO6">
         <v>1</v>
@@ -3571,11 +3705,8 @@
       <c r="AY6">
         <v>1</v>
       </c>
-      <c r="AZ6">
-        <v>-236.0549926757812</v>
-      </c>
       <c r="BB6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BC6">
         <v>4</v>
@@ -3590,13 +3721,13 @@
         <v>0</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP6">
         <v>0</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BT6">
         <v>0</v>
@@ -3619,11 +3750,8 @@
       <c r="CH6">
         <v>1</v>
       </c>
-      <c r="CI6">
-        <v>-124.1699981689453</v>
-      </c>
       <c r="CK6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CL6">
         <v>8</v>
@@ -3676,11 +3804,8 @@
       <c r="DX6">
         <v>1</v>
       </c>
-      <c r="DY6">
-        <v>-636.4500122070312</v>
-      </c>
       <c r="EA6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB6">
         <v>1</v>
@@ -3688,11 +3813,8 @@
       <c r="EE6">
         <v>1</v>
       </c>
-      <c r="EF6">
-        <v>-290</v>
-      </c>
       <c r="EH6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="EI6">
         <v>3</v>
@@ -3718,11 +3840,8 @@
       <c r="EZ6">
         <v>1</v>
       </c>
-      <c r="FA6">
-        <v>-186.384994506836</v>
-      </c>
       <c r="FC6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="FD6">
         <v>5</v>
@@ -3730,11 +3849,8 @@
       <c r="FG6">
         <v>1</v>
       </c>
-      <c r="FH6">
-        <v>-406.4700012207031</v>
-      </c>
       <c r="FJ6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="FK6">
         <v>2</v>
@@ -3749,13 +3865,16 @@
         <v>0</v>
       </c>
       <c r="FU6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FV6">
+        <v>-546</v>
       </c>
       <c r="FX6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FY6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:183">
@@ -3763,28 +3882,31 @@
         <v>22</v>
       </c>
       <c r="B7">
-        <v>10000</v>
+        <v>9970.279909493622</v>
       </c>
       <c r="C7">
-        <v>10000</v>
+        <v>2464.739893319305</v>
       </c>
       <c r="D7">
-        <v>10000</v>
+        <v>-1612.271831359497</v>
       </c>
       <c r="E7">
         <v>10000</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>-0.00297200905063788</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>-332.7950134277344</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -3814,13 +3936,13 @@
         <v>0</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN7">
         <v>0</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3832,13 +3954,13 @@
         <v>0</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB7">
         <v>0</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF7">
         <v>0</v>
@@ -3850,13 +3972,16 @@
         <v>0</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BN7">
+        <v>-52.58</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BT7">
         <v>0</v>
@@ -3877,13 +4002,13 @@
         <v>0</v>
       </c>
       <c r="CH7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CK7">
         <v>0</v>
       </c>
       <c r="CL7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CO7">
         <v>0</v>
@@ -3931,22 +4056,22 @@
         <v>0</v>
       </c>
       <c r="DX7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EA7">
         <v>0</v>
       </c>
       <c r="EB7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EE7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EH7">
         <v>0</v>
       </c>
       <c r="EI7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="EL7">
         <v>0</v>
@@ -3967,22 +4092,22 @@
         <v>0</v>
       </c>
       <c r="EZ7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FC7">
         <v>0</v>
       </c>
       <c r="FD7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="FG7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FJ7">
         <v>0</v>
       </c>
       <c r="FK7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="FN7">
         <v>0</v>
@@ -4000,11 +4125,522 @@
         <v>0</v>
       </c>
       <c r="FY7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:183">
+      <c r="A8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
+        <v>9919.091680733491</v>
+      </c>
+      <c r="C8">
+        <v>4077.011724678802</v>
+      </c>
+      <c r="D8">
+        <v>-5922.988275321198</v>
+      </c>
+      <c r="E8">
+        <v>10000</v>
+      </c>
+      <c r="F8">
+        <v>-0.008090831926650943</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <v>-733.2050170898438</v>
+      </c>
+      <c r="AN8">
+        <v>1</v>
+      </c>
+      <c r="AO8">
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>1</v>
+      </c>
+      <c r="AZ8">
+        <v>-236.0549926757812</v>
+      </c>
+      <c r="BB8">
+        <v>4</v>
+      </c>
+      <c r="BC8">
+        <v>4</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CD8">
+        <v>0</v>
+      </c>
+      <c r="CE8">
+        <v>0</v>
+      </c>
+      <c r="CH8">
+        <v>1</v>
+      </c>
+      <c r="CI8">
+        <v>-124.1699981689453</v>
+      </c>
+      <c r="CK8">
+        <v>8</v>
+      </c>
+      <c r="CL8">
+        <v>8</v>
+      </c>
+      <c r="CO8">
+        <v>0</v>
+      </c>
+      <c r="CR8">
+        <v>0</v>
+      </c>
+      <c r="CS8">
+        <v>0</v>
+      </c>
+      <c r="CV8">
+        <v>0</v>
+      </c>
+      <c r="CY8">
+        <v>0</v>
+      </c>
+      <c r="CZ8">
+        <v>0</v>
+      </c>
+      <c r="DC8">
+        <v>0</v>
+      </c>
+      <c r="DF8">
+        <v>0</v>
+      </c>
+      <c r="DG8">
+        <v>0</v>
+      </c>
+      <c r="DJ8">
+        <v>0</v>
+      </c>
+      <c r="DM8">
+        <v>0</v>
+      </c>
+      <c r="DN8">
+        <v>0</v>
+      </c>
+      <c r="DQ8">
+        <v>0</v>
+      </c>
+      <c r="DT8">
+        <v>0</v>
+      </c>
+      <c r="DU8">
+        <v>0</v>
+      </c>
+      <c r="DX8">
+        <v>1</v>
+      </c>
+      <c r="DY8">
+        <v>-636.4500122070312</v>
+      </c>
+      <c r="EA8">
+        <v>1</v>
+      </c>
+      <c r="EB8">
+        <v>1</v>
+      </c>
+      <c r="EE8">
+        <v>1</v>
+      </c>
+      <c r="EF8">
+        <v>-290</v>
+      </c>
+      <c r="EH8">
+        <v>3</v>
+      </c>
+      <c r="EI8">
+        <v>3</v>
+      </c>
+      <c r="EL8">
+        <v>0</v>
+      </c>
+      <c r="EO8">
+        <v>0</v>
+      </c>
+      <c r="EP8">
+        <v>0</v>
+      </c>
+      <c r="ES8">
+        <v>0</v>
+      </c>
+      <c r="EV8">
+        <v>0</v>
+      </c>
+      <c r="EW8">
+        <v>0</v>
+      </c>
+      <c r="EZ8">
+        <v>1</v>
+      </c>
+      <c r="FA8">
+        <v>-186.384994506836</v>
+      </c>
+      <c r="FC8">
+        <v>5</v>
+      </c>
+      <c r="FD8">
+        <v>5</v>
+      </c>
+      <c r="FG8">
+        <v>1</v>
+      </c>
+      <c r="FH8">
+        <v>-406.4700012207031</v>
+      </c>
+      <c r="FJ8">
+        <v>2</v>
+      </c>
+      <c r="FK8">
+        <v>2</v>
+      </c>
+      <c r="FN8">
+        <v>0</v>
+      </c>
+      <c r="FQ8">
+        <v>0</v>
+      </c>
+      <c r="FR8">
+        <v>0</v>
+      </c>
+      <c r="FU8">
+        <v>0</v>
+      </c>
+      <c r="FX8">
+        <v>0</v>
+      </c>
+      <c r="FY8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:183">
+      <c r="A9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
+        <v>10000</v>
+      </c>
+      <c r="C9">
+        <v>10000</v>
+      </c>
+      <c r="D9">
+        <v>10000</v>
+      </c>
+      <c r="E9">
+        <v>10000</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CD9">
+        <v>0</v>
+      </c>
+      <c r="CE9">
+        <v>0</v>
+      </c>
+      <c r="CH9">
+        <v>0</v>
+      </c>
+      <c r="CK9">
+        <v>0</v>
+      </c>
+      <c r="CL9">
+        <v>0</v>
+      </c>
+      <c r="CO9">
+        <v>0</v>
+      </c>
+      <c r="CR9">
+        <v>0</v>
+      </c>
+      <c r="CS9">
+        <v>0</v>
+      </c>
+      <c r="CV9">
+        <v>0</v>
+      </c>
+      <c r="CY9">
+        <v>0</v>
+      </c>
+      <c r="CZ9">
+        <v>0</v>
+      </c>
+      <c r="DC9">
+        <v>0</v>
+      </c>
+      <c r="DF9">
+        <v>0</v>
+      </c>
+      <c r="DG9">
+        <v>0</v>
+      </c>
+      <c r="DJ9">
+        <v>0</v>
+      </c>
+      <c r="DM9">
+        <v>0</v>
+      </c>
+      <c r="DN9">
+        <v>0</v>
+      </c>
+      <c r="DQ9">
+        <v>0</v>
+      </c>
+      <c r="DT9">
+        <v>0</v>
+      </c>
+      <c r="DU9">
+        <v>0</v>
+      </c>
+      <c r="DX9">
+        <v>0</v>
+      </c>
+      <c r="EA9">
+        <v>0</v>
+      </c>
+      <c r="EB9">
+        <v>0</v>
+      </c>
+      <c r="EE9">
+        <v>0</v>
+      </c>
+      <c r="EH9">
+        <v>0</v>
+      </c>
+      <c r="EI9">
+        <v>0</v>
+      </c>
+      <c r="EL9">
+        <v>0</v>
+      </c>
+      <c r="EO9">
+        <v>0</v>
+      </c>
+      <c r="EP9">
+        <v>0</v>
+      </c>
+      <c r="ES9">
+        <v>0</v>
+      </c>
+      <c r="EV9">
+        <v>0</v>
+      </c>
+      <c r="EW9">
+        <v>0</v>
+      </c>
+      <c r="EZ9">
+        <v>0</v>
+      </c>
+      <c r="FC9">
+        <v>0</v>
+      </c>
+      <c r="FD9">
+        <v>0</v>
+      </c>
+      <c r="FG9">
+        <v>0</v>
+      </c>
+      <c r="FJ9">
+        <v>0</v>
+      </c>
+      <c r="FK9">
+        <v>0</v>
+      </c>
+      <c r="FN9">
+        <v>0</v>
+      </c>
+      <c r="FQ9">
+        <v>0</v>
+      </c>
+      <c r="FR9">
+        <v>0</v>
+      </c>
+      <c r="FU9">
+        <v>0</v>
+      </c>
+      <c r="FX9">
+        <v>0</v>
+      </c>
+      <c r="FY9">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AA2:AA7">
+  <conditionalFormatting sqref="AA2:AA9">
     <cfRule type="cellIs" dxfId="4" priority="25" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4012,7 +4648,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE2:AE7">
+  <conditionalFormatting sqref="AE2:AE9">
     <cfRule type="cellIs" dxfId="4" priority="27" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4020,7 +4656,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF2:AF7">
+  <conditionalFormatting sqref="AF2:AF9">
     <cfRule type="cellIs" dxfId="4" priority="29" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4028,7 +4664,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG2:AG7">
+  <conditionalFormatting sqref="AG2:AG9">
     <cfRule type="cellIs" dxfId="4" priority="31" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4036,7 +4672,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH2:AH7">
+  <conditionalFormatting sqref="AH2:AH9">
     <cfRule type="cellIs" dxfId="4" priority="33" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4044,7 +4680,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL2:AL7">
+  <conditionalFormatting sqref="AL2:AL9">
     <cfRule type="cellIs" dxfId="4" priority="35" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4052,7 +4688,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM2:AM7">
+  <conditionalFormatting sqref="AM2:AM9">
     <cfRule type="cellIs" dxfId="4" priority="37" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4060,7 +4696,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AN2:AN7">
+  <conditionalFormatting sqref="AN2:AN9">
     <cfRule type="cellIs" dxfId="4" priority="39" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4068,7 +4704,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AO2:AO7">
+  <conditionalFormatting sqref="AO2:AO9">
     <cfRule type="cellIs" dxfId="4" priority="41" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4076,7 +4712,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AS2:AS7">
+  <conditionalFormatting sqref="AS2:AS9">
     <cfRule type="cellIs" dxfId="4" priority="43" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4084,7 +4720,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AT2:AT7">
+  <conditionalFormatting sqref="AT2:AT9">
     <cfRule type="cellIs" dxfId="4" priority="45" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4092,7 +4728,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU2:AU7">
+  <conditionalFormatting sqref="AU2:AU9">
     <cfRule type="cellIs" dxfId="4" priority="47" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4100,7 +4736,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AV2:AV7">
+  <conditionalFormatting sqref="AV2:AV9">
     <cfRule type="cellIs" dxfId="4" priority="49" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4108,7 +4744,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AZ2:AZ7">
+  <conditionalFormatting sqref="AZ2:AZ9">
     <cfRule type="cellIs" dxfId="4" priority="51" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4116,7 +4752,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BA2:BA7">
+  <conditionalFormatting sqref="BA2:BA9">
     <cfRule type="cellIs" dxfId="4" priority="53" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4124,7 +4760,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB2:BB7">
+  <conditionalFormatting sqref="BB2:BB9">
     <cfRule type="cellIs" dxfId="4" priority="55" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4132,7 +4768,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BC2:BC7">
+  <conditionalFormatting sqref="BC2:BC9">
     <cfRule type="cellIs" dxfId="4" priority="57" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4140,7 +4776,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BG2:BG7">
+  <conditionalFormatting sqref="BG2:BG9">
     <cfRule type="cellIs" dxfId="4" priority="59" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4148,7 +4784,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BH2:BH7">
+  <conditionalFormatting sqref="BH2:BH9">
     <cfRule type="cellIs" dxfId="4" priority="61" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4156,7 +4792,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BI2:BI7">
+  <conditionalFormatting sqref="BI2:BI9">
     <cfRule type="cellIs" dxfId="4" priority="63" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4164,7 +4800,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BJ2:BJ7">
+  <conditionalFormatting sqref="BJ2:BJ9">
     <cfRule type="cellIs" dxfId="4" priority="65" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4172,7 +4808,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BN2:BN7">
+  <conditionalFormatting sqref="BN2:BN9">
     <cfRule type="cellIs" dxfId="4" priority="67" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4180,7 +4816,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BO2:BO7">
+  <conditionalFormatting sqref="BO2:BO9">
     <cfRule type="cellIs" dxfId="4" priority="69" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4188,7 +4824,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BP2:BP7">
+  <conditionalFormatting sqref="BP2:BP9">
     <cfRule type="cellIs" dxfId="4" priority="71" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4196,7 +4832,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BQ2:BQ7">
+  <conditionalFormatting sqref="BQ2:BQ9">
     <cfRule type="cellIs" dxfId="4" priority="73" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4204,7 +4840,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BU2:BU7">
+  <conditionalFormatting sqref="BU2:BU9">
     <cfRule type="cellIs" dxfId="4" priority="75" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4212,7 +4848,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BV2:BV7">
+  <conditionalFormatting sqref="BV2:BV9">
     <cfRule type="cellIs" dxfId="4" priority="77" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4220,7 +4856,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BW2:BW7">
+  <conditionalFormatting sqref="BW2:BW9">
     <cfRule type="cellIs" dxfId="4" priority="79" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4228,7 +4864,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BX2:BX7">
+  <conditionalFormatting sqref="BX2:BX9">
     <cfRule type="cellIs" dxfId="4" priority="81" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4236,7 +4872,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CB2:CB7">
+  <conditionalFormatting sqref="CB2:CB9">
     <cfRule type="cellIs" dxfId="4" priority="83" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4244,7 +4880,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CC2:CC7">
+  <conditionalFormatting sqref="CC2:CC9">
     <cfRule type="cellIs" dxfId="4" priority="85" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4252,7 +4888,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CD2:CD7">
+  <conditionalFormatting sqref="CD2:CD9">
     <cfRule type="cellIs" dxfId="4" priority="87" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4260,7 +4896,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CE2:CE7">
+  <conditionalFormatting sqref="CE2:CE9">
     <cfRule type="cellIs" dxfId="4" priority="89" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4268,7 +4904,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CI2:CI7">
+  <conditionalFormatting sqref="CI2:CI9">
     <cfRule type="cellIs" dxfId="4" priority="91" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4276,7 +4912,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CJ2:CJ7">
+  <conditionalFormatting sqref="CJ2:CJ9">
     <cfRule type="cellIs" dxfId="4" priority="93" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4284,7 +4920,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CK2:CK7">
+  <conditionalFormatting sqref="CK2:CK9">
     <cfRule type="cellIs" dxfId="4" priority="95" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4292,7 +4928,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CL2:CL7">
+  <conditionalFormatting sqref="CL2:CL9">
     <cfRule type="cellIs" dxfId="4" priority="97" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4300,7 +4936,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CP2:CP7">
+  <conditionalFormatting sqref="CP2:CP9">
     <cfRule type="cellIs" dxfId="4" priority="99" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4308,7 +4944,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CQ2:CQ7">
+  <conditionalFormatting sqref="CQ2:CQ9">
     <cfRule type="cellIs" dxfId="4" priority="101" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4316,7 +4952,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CR2:CR7">
+  <conditionalFormatting sqref="CR2:CR9">
     <cfRule type="cellIs" dxfId="4" priority="103" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4324,7 +4960,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CS2:CS7">
+  <conditionalFormatting sqref="CS2:CS9">
     <cfRule type="cellIs" dxfId="4" priority="105" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4332,7 +4968,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CW2:CW7">
+  <conditionalFormatting sqref="CW2:CW9">
     <cfRule type="cellIs" dxfId="4" priority="107" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4340,7 +4976,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CX2:CX7">
+  <conditionalFormatting sqref="CX2:CX9">
     <cfRule type="cellIs" dxfId="4" priority="109" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4348,7 +4984,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CY2:CY7">
+  <conditionalFormatting sqref="CY2:CY9">
     <cfRule type="cellIs" dxfId="4" priority="111" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4356,7 +4992,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CZ2:CZ7">
+  <conditionalFormatting sqref="CZ2:CZ9">
     <cfRule type="cellIs" dxfId="4" priority="113" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4364,7 +5000,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D2:D9">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4372,7 +5008,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DD2:DD7">
+  <conditionalFormatting sqref="DD2:DD9">
     <cfRule type="cellIs" dxfId="4" priority="115" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4380,7 +5016,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DE2:DE7">
+  <conditionalFormatting sqref="DE2:DE9">
     <cfRule type="cellIs" dxfId="4" priority="117" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4388,7 +5024,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DF2:DF7">
+  <conditionalFormatting sqref="DF2:DF9">
     <cfRule type="cellIs" dxfId="4" priority="119" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4396,7 +5032,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DG2:DG7">
+  <conditionalFormatting sqref="DG2:DG9">
     <cfRule type="cellIs" dxfId="4" priority="121" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4404,7 +5040,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DK2:DK7">
+  <conditionalFormatting sqref="DK2:DK9">
     <cfRule type="cellIs" dxfId="4" priority="123" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4412,7 +5048,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DL2:DL7">
+  <conditionalFormatting sqref="DL2:DL9">
     <cfRule type="cellIs" dxfId="4" priority="125" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4420,7 +5056,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DM2:DM7">
+  <conditionalFormatting sqref="DM2:DM9">
     <cfRule type="cellIs" dxfId="4" priority="127" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4428,7 +5064,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DN2:DN7">
+  <conditionalFormatting sqref="DN2:DN9">
     <cfRule type="cellIs" dxfId="4" priority="129" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4436,7 +5072,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DR2:DR7">
+  <conditionalFormatting sqref="DR2:DR9">
     <cfRule type="cellIs" dxfId="4" priority="131" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4444,7 +5080,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DS2:DS7">
+  <conditionalFormatting sqref="DS2:DS9">
     <cfRule type="cellIs" dxfId="4" priority="133" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4452,7 +5088,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DT2:DT7">
+  <conditionalFormatting sqref="DT2:DT9">
     <cfRule type="cellIs" dxfId="4" priority="135" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4460,7 +5096,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DU2:DU7">
+  <conditionalFormatting sqref="DU2:DU9">
     <cfRule type="cellIs" dxfId="4" priority="137" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4468,7 +5104,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DY2:DY7">
+  <conditionalFormatting sqref="DY2:DY9">
     <cfRule type="cellIs" dxfId="4" priority="139" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4476,7 +5112,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DZ2:DZ7">
+  <conditionalFormatting sqref="DZ2:DZ9">
     <cfRule type="cellIs" dxfId="4" priority="141" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4484,7 +5120,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EA2:EA7">
+  <conditionalFormatting sqref="EA2:EA9">
     <cfRule type="cellIs" dxfId="4" priority="143" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4492,7 +5128,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EB2:EB7">
+  <conditionalFormatting sqref="EB2:EB9">
     <cfRule type="cellIs" dxfId="4" priority="145" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4500,7 +5136,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EF2:EF7">
+  <conditionalFormatting sqref="EF2:EF9">
     <cfRule type="cellIs" dxfId="4" priority="147" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4508,7 +5144,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EG2:EG7">
+  <conditionalFormatting sqref="EG2:EG9">
     <cfRule type="cellIs" dxfId="4" priority="149" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4516,7 +5152,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EH2:EH7">
+  <conditionalFormatting sqref="EH2:EH9">
     <cfRule type="cellIs" dxfId="4" priority="151" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4524,7 +5160,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EI2:EI7">
+  <conditionalFormatting sqref="EI2:EI9">
     <cfRule type="cellIs" dxfId="4" priority="153" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4532,7 +5168,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EM2:EM7">
+  <conditionalFormatting sqref="EM2:EM9">
     <cfRule type="cellIs" dxfId="4" priority="155" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4540,7 +5176,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EN2:EN7">
+  <conditionalFormatting sqref="EN2:EN9">
     <cfRule type="cellIs" dxfId="4" priority="157" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4548,7 +5184,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EO2:EO7">
+  <conditionalFormatting sqref="EO2:EO9">
     <cfRule type="cellIs" dxfId="4" priority="159" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4556,7 +5192,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EP2:EP7">
+  <conditionalFormatting sqref="EP2:EP9">
     <cfRule type="cellIs" dxfId="4" priority="161" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4564,7 +5200,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="ET2:ET7">
+  <conditionalFormatting sqref="ET2:ET9">
     <cfRule type="cellIs" dxfId="4" priority="163" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4572,7 +5208,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EU2:EU7">
+  <conditionalFormatting sqref="EU2:EU9">
     <cfRule type="cellIs" dxfId="4" priority="165" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4580,7 +5216,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EV2:EV7">
+  <conditionalFormatting sqref="EV2:EV9">
     <cfRule type="cellIs" dxfId="4" priority="167" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4588,7 +5224,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EW2:EW7">
+  <conditionalFormatting sqref="EW2:EW9">
     <cfRule type="cellIs" dxfId="4" priority="169" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4596,7 +5232,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FA2:FA7">
+  <conditionalFormatting sqref="FA2:FA9">
     <cfRule type="cellIs" dxfId="4" priority="171" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4604,7 +5240,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FB2:FB7">
+  <conditionalFormatting sqref="FB2:FB9">
     <cfRule type="cellIs" dxfId="4" priority="173" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4612,7 +5248,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FC2:FC7">
+  <conditionalFormatting sqref="FC2:FC9">
     <cfRule type="cellIs" dxfId="4" priority="175" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4620,7 +5256,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FD2:FD7">
+  <conditionalFormatting sqref="FD2:FD9">
     <cfRule type="cellIs" dxfId="4" priority="177" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4628,7 +5264,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FH2:FH7">
+  <conditionalFormatting sqref="FH2:FH9">
     <cfRule type="cellIs" dxfId="4" priority="179" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4636,7 +5272,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FI2:FI7">
+  <conditionalFormatting sqref="FI2:FI9">
     <cfRule type="cellIs" dxfId="4" priority="181" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4644,7 +5280,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FJ2:FJ7">
+  <conditionalFormatting sqref="FJ2:FJ9">
     <cfRule type="cellIs" dxfId="4" priority="183" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4652,7 +5288,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FK2:FK7">
+  <conditionalFormatting sqref="FK2:FK9">
     <cfRule type="cellIs" dxfId="4" priority="185" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4660,7 +5296,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FO2:FO7">
+  <conditionalFormatting sqref="FO2:FO9">
     <cfRule type="cellIs" dxfId="4" priority="187" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4668,7 +5304,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FP2:FP7">
+  <conditionalFormatting sqref="FP2:FP9">
     <cfRule type="cellIs" dxfId="4" priority="189" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4676,7 +5312,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FQ2:FQ7">
+  <conditionalFormatting sqref="FQ2:FQ9">
     <cfRule type="cellIs" dxfId="4" priority="191" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4684,7 +5320,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FR2:FR7">
+  <conditionalFormatting sqref="FR2:FR9">
     <cfRule type="cellIs" dxfId="4" priority="193" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4692,7 +5328,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FV2:FV7">
+  <conditionalFormatting sqref="FV2:FV9">
     <cfRule type="cellIs" dxfId="4" priority="195" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4700,7 +5336,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FW2:FW7">
+  <conditionalFormatting sqref="FW2:FW9">
     <cfRule type="cellIs" dxfId="4" priority="197" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4708,7 +5344,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FX2:FX7">
+  <conditionalFormatting sqref="FX2:FX9">
     <cfRule type="cellIs" dxfId="4" priority="199" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4716,7 +5352,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FY2:FY7">
+  <conditionalFormatting sqref="FY2:FY9">
     <cfRule type="cellIs" dxfId="4" priority="201" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4724,7 +5360,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J7">
+  <conditionalFormatting sqref="J2:J9">
     <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4732,7 +5368,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K7">
+  <conditionalFormatting sqref="K2:K9">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4740,7 +5376,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L7">
+  <conditionalFormatting sqref="L2:L9">
     <cfRule type="cellIs" dxfId="4" priority="7" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4748,7 +5384,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M7">
+  <conditionalFormatting sqref="M2:M9">
     <cfRule type="cellIs" dxfId="4" priority="9" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4756,7 +5392,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q7">
+  <conditionalFormatting sqref="Q2:Q9">
     <cfRule type="cellIs" dxfId="4" priority="11" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4764,7 +5400,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R7">
+  <conditionalFormatting sqref="R2:R9">
     <cfRule type="cellIs" dxfId="4" priority="13" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4772,7 +5408,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S7">
+  <conditionalFormatting sqref="S2:S9">
     <cfRule type="cellIs" dxfId="4" priority="15" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4780,7 +5416,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T7">
+  <conditionalFormatting sqref="T2:T9">
     <cfRule type="cellIs" dxfId="4" priority="17" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4788,7 +5424,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X7">
+  <conditionalFormatting sqref="X2:X9">
     <cfRule type="cellIs" dxfId="4" priority="19" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4796,7 +5432,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y7">
+  <conditionalFormatting sqref="Y2:Y9">
     <cfRule type="cellIs" dxfId="4" priority="21" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4804,7 +5440,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:Z7">
+  <conditionalFormatting sqref="Z2:Z9">
     <cfRule type="cellIs" dxfId="4" priority="23" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>

--- a/reports/paper_trade_trx.xlsx
+++ b/reports/paper_trade_trx.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="248">
   <si>
     <t>NAV</t>
   </si>
@@ -36,7 +36,7 @@
     <t>last_updated</t>
   </si>
   <si>
-    <t>2026-10-14 18:01:25</t>
+    <t>2026-10-15 18:01:13</t>
   </si>
   <si>
     <t>pf_id</t>
@@ -69,6 +69,9 @@
     <t>date</t>
   </si>
   <si>
+    <t>2026-10-15</t>
+  </si>
+  <si>
     <t>2026-10-14</t>
   </si>
   <si>
@@ -93,6 +96,12 @@
     <t>2026-09-29</t>
   </si>
   <si>
+    <t>QCOM</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
     <t>AMAT</t>
   </si>
   <si>
@@ -105,6 +114,9 @@
     <t>GOOGL</t>
   </si>
   <si>
+    <t>MSFT</t>
+  </si>
+  <si>
     <t>COST</t>
   </si>
   <si>
@@ -114,9 +126,6 @@
     <t>AMZN</t>
   </si>
   <si>
-    <t>MSFT</t>
-  </si>
-  <si>
     <t>TSLA</t>
   </si>
   <si>
@@ -132,15 +141,9 @@
     <t>ISRG</t>
   </si>
   <si>
-    <t>QCOM</t>
-  </si>
-  <si>
     <t>TXN</t>
   </si>
   <si>
-    <t>AMD</t>
-  </si>
-  <si>
     <t>NVDA</t>
   </si>
   <si>
@@ -150,6 +153,12 @@
     <t>initial</t>
   </si>
   <si>
+    <t>2026-10-15_b2113621636a6c54be0246381e6e8245</t>
+  </si>
+  <si>
+    <t>2026-10-15_93ec2b62647208f53b9f38380631ec06</t>
+  </si>
+  <si>
     <t>2026-10-14_26ca0548a178a1891287462eabd2327f</t>
   </si>
   <si>
@@ -162,6 +171,9 @@
     <t>2026-10-13_572bd3499a20b8e64a30af391461ef95</t>
   </si>
   <si>
+    <t>2026-10-09_4c574a6fffe0157d7c23fe8d2682dfb9</t>
+  </si>
+  <si>
     <t>2026-10-09_cbfa34b7b92b8c9ddd53b2ba7394c363</t>
   </si>
   <si>
@@ -169,9 +181,6 @@
   </si>
   <si>
     <t>2026-10-09_603d3f285d1e0ad7f8d04d423ef9ecc5</t>
-  </si>
-  <si>
-    <t>2026-10-09_4c574a6fffe0157d7c23fe8d2682dfb9</t>
   </si>
   <si>
     <t>2026-10-07_dc7e32e4c69a2eb8b2d77f7cc32b45cf</t>
@@ -1275,7 +1284,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>9600</v>
+        <v>9590</v>
       </c>
       <c r="C2" s="2">
         <v>100</v>
@@ -1299,7 +1308,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>9600</v>
+        <v>9590</v>
       </c>
       <c r="C4" s="2">
         <v>100</v>
@@ -1370,7 +1379,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
@@ -1416,19 +1425,19 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>454.15</v>
+        <v>169.3099975585938</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="H2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1439,19 +1448,19 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3">
-        <v>-301.6000061035156</v>
+        <v>27</v>
+      </c>
+      <c r="F3">
+        <v>539.6199951171875</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="H3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1462,19 +1471,19 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4">
-        <v>99.54000091552734</v>
+        <v>454.15</v>
       </c>
       <c r="G4">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="H4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1485,19 +1494,19 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>-356.2999877929688</v>
+        <v>-301.6000061035156</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1508,19 +1517,19 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6">
-        <v>-945</v>
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>99.54000091552734</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="H6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1531,65 +1540,65 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>-116.7699966430664</v>
+        <v>-356.2999877929688</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8">
-        <v>-256.2999877929688</v>
+        <v>-528.2349853515625</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9">
-        <v>-528.2349853515625</v>
+        <v>-945</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1600,65 +1609,65 @@
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E10">
-        <v>-378.3500061035156</v>
+        <v>-116.7699966430664</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E11">
-        <v>-546</v>
+        <v>-256.2999877929688</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E12">
-        <v>-52.58</v>
+        <v>-378.3500061035156</v>
       </c>
       <c r="G12">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1669,19 +1678,19 @@
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E13">
-        <v>-332.7950134277344</v>
+        <v>-546</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1692,19 +1701,19 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14">
-        <v>-733.2050170898438</v>
+        <v>-52.58</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1715,134 +1724,134 @@
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E15">
-        <v>-406.4700012207031</v>
+        <v>-332.7950134277344</v>
       </c>
       <c r="G15">
         <v>2</v>
       </c>
       <c r="H15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E16">
-        <v>-186.384994506836</v>
+        <v>-733.2050170898438</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E17">
-        <v>-290</v>
+        <v>-406.4700012207031</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E18">
-        <v>-636.4500122070312</v>
+        <v>-186.384994506836</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E19">
-        <v>-124.1699981689453</v>
+        <v>-290</v>
       </c>
       <c r="G19">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E20">
-        <v>-236.0549926757812</v>
+        <v>-636.4500122070312</v>
       </c>
       <c r="G20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1852,23 +1861,69 @@
       <c r="B21" t="s">
         <v>2</v>
       </c>
-      <c r="C21">
-        <v>10000</v>
+      <c r="D21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21">
+        <v>-124.1699981689453</v>
+      </c>
+      <c r="G21">
+        <v>8</v>
       </c>
       <c r="H21" t="s">
         <v>43</v>
       </c>
       <c r="J21" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22">
+        <v>-236.0549926757812</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>10000</v>
+      </c>
+      <c r="H23" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B21">
+  <conditionalFormatting sqref="B2:B23">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>$B2="option"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C21">
+  <conditionalFormatting sqref="C2:C23">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1876,7 +1931,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E21">
+  <conditionalFormatting sqref="E2:E23">
     <cfRule type="cellIs" dxfId="4" priority="4" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1884,7 +1939,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F21">
+  <conditionalFormatting sqref="F2:F23">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1892,7 +1947,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G21">
+  <conditionalFormatting sqref="G2:G23">
     <cfRule type="cellIs" dxfId="4" priority="8" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1906,7 +1961,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:GA9"/>
+  <dimension ref="A1:GA10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
@@ -1914,10 +1969,10 @@
   <sheetData>
     <row r="1" spans="1:183">
       <c r="A1" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>3</v>
@@ -1926,541 +1981,541 @@
         <v>8</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AL1" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="BE1" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="BF1" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="BL1" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="BM1" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="BN1" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="BO1" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="BP1" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="BQ1" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="BR1" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="BS1" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="BT1" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="BU1" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="BV1" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="BW1" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BX1" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="BY1" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="BZ1" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="CA1" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="CB1" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="CC1" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="CD1" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="CE1" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="CF1" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="CH1" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="CI1" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="CJ1" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="CK1" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="CL1" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="CM1" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="CN1" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="CO1" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="CP1" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="CQ1" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="CR1" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="CS1" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="CT1" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="CU1" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="CV1" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="CW1" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="CX1" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="CY1" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="CZ1" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="DA1" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="DB1" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="DC1" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="DD1" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="DE1" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="DF1" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="DG1" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="DH1" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="DI1" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="DJ1" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="DK1" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="DL1" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="DM1" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="DN1" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="DO1" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="DP1" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="DQ1" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="DR1" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="DS1" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DT1" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="DU1" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="DV1" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="DW1" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="DX1" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="DY1" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="DZ1" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="EA1" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="EB1" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="EC1" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="ED1" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="EE1" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="EF1" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="EG1" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="EH1" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="EI1" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="EJ1" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="EK1" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="EL1" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="EM1" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="EN1" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="EO1" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="EP1" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="EQ1" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="ER1" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="ES1" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="ET1" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="EU1" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="EV1" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="EW1" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="EX1" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="EY1" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="EZ1" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="FA1" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="FB1" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="FC1" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="FD1" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="FE1" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="FF1" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="FG1" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="FH1" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="FI1" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="FJ1" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="FK1" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="FL1" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="FM1" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="FN1" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="FO1" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="FP1" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="FQ1" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="FR1" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="FS1" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="FT1" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="FU1" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="FV1" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="FW1" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="FX1" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="FY1" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="FZ1" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="GA1" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:183">
@@ -2468,31 +2523,31 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>9600.492880668853</v>
+        <v>9589.634938386749</v>
       </c>
       <c r="C2">
-        <v>-2382.287057075287</v>
+        <v>-996.3249996625673</v>
       </c>
       <c r="D2">
-        <v>-450.8538608132935</v>
+        <v>1385.96205741272</v>
       </c>
       <c r="E2">
         <v>10000</v>
       </c>
       <c r="F2">
-        <v>-0.03995071193311472</v>
+        <v>-0.04103650616132504</v>
       </c>
       <c r="G2">
-        <v>-5.498600756835939</v>
+        <v>-2.543401568603515</v>
       </c>
       <c r="H2">
-        <v>-0.01252882053325666</v>
+        <v>-0.006606232173333065</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>342.9599914550781</v>
+        <v>342</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2501,16 +2556,16 @@
         <v>2</v>
       </c>
       <c r="N2">
-        <v>10.16497802734375</v>
+        <v>9.204986572265625</v>
       </c>
       <c r="O2">
-        <v>0.03054426183447312</v>
+        <v>0.02765962890325713</v>
       </c>
       <c r="P2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>533.6900024414062</v>
+        <v>539.4400024414062</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -2519,16 +2574,16 @@
         <v>1</v>
       </c>
       <c r="U2">
-        <v>5.45501708984375</v>
+        <v>11.20501708984375</v>
       </c>
       <c r="V2">
-        <v>0.0103268758054964</v>
+        <v>0.0212121828363685</v>
       </c>
       <c r="W2">
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>347.6400146484375</v>
+        <v>349.2200012207031</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2537,16 +2592,16 @@
         <v>2</v>
       </c>
       <c r="AB2">
-        <v>-8.65997314453125</v>
+        <v>-7.079986572265625</v>
       </c>
       <c r="AC2">
-        <v>-0.02430528611065574</v>
+        <v>-0.01987085830712831</v>
       </c>
       <c r="AD2">
         <v>1</v>
       </c>
       <c r="AF2">
-        <v>254.0800018310547</v>
+        <v>254.759994506836</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -2555,16 +2610,16 @@
         <v>3</v>
       </c>
       <c r="AI2">
-        <v>-2.219985961914062</v>
+        <v>-1.539993286132784</v>
       </c>
       <c r="AJ2">
-        <v>-0.008661670182002923</v>
+        <v>-0.006008557781815971</v>
       </c>
       <c r="AK2">
         <v>1</v>
       </c>
       <c r="AM2">
-        <v>737.5399780273438</v>
+        <v>736.719970703125</v>
       </c>
       <c r="AN2">
         <v>0</v>
@@ -2573,16 +2628,16 @@
         <v>1</v>
       </c>
       <c r="AP2">
-        <v>4.3349609375</v>
+        <v>3.51495361328125</v>
       </c>
       <c r="AQ2">
-        <v>0.005912344891890964</v>
+        <v>0.00479395739438937</v>
       </c>
       <c r="AR2">
         <v>1</v>
       </c>
       <c r="AT2">
-        <v>367.1600036621094</v>
+        <v>362.4400024414063</v>
       </c>
       <c r="AU2">
         <v>0</v>
@@ -2591,16 +2646,16 @@
         <v>2</v>
       </c>
       <c r="AW2">
-        <v>-11.19000244140625</v>
+        <v>-15.91000366210932</v>
       </c>
       <c r="AX2">
-        <v>-0.02957579558844958</v>
+        <v>-0.04205101996947336</v>
       </c>
       <c r="AY2">
         <v>1</v>
       </c>
       <c r="BA2">
-        <v>221.3000030517578</v>
+        <v>217.229995727539</v>
       </c>
       <c r="BB2">
         <v>0</v>
@@ -2609,10 +2664,10 @@
         <v>4</v>
       </c>
       <c r="BD2">
-        <v>-14.75498962402344</v>
+        <v>-18.82499694824222</v>
       </c>
       <c r="BE2">
-        <v>-0.06250657720376729</v>
+        <v>-0.07974835327502738</v>
       </c>
       <c r="BF2">
         <v>0</v>
@@ -2627,7 +2682,7 @@
         <v>1</v>
       </c>
       <c r="BO2">
-        <v>56.09999847412109</v>
+        <v>57.15999984741211</v>
       </c>
       <c r="BP2">
         <v>0</v>
@@ -2636,10 +2691,10 @@
         <v>18</v>
       </c>
       <c r="BR2">
-        <v>3.519998474121088</v>
+        <v>4.579999847412111</v>
       </c>
       <c r="BS2">
-        <v>0.06694557767442166</v>
+        <v>0.08710536035397709</v>
       </c>
       <c r="BT2">
         <v>0</v>
@@ -2672,7 +2727,7 @@
         <v>1</v>
       </c>
       <c r="CQ2">
-        <v>113.6399993896484</v>
+        <v>109.8499984741211</v>
       </c>
       <c r="CR2">
         <v>0</v>
@@ -2681,16 +2736,16 @@
         <v>8</v>
       </c>
       <c r="CT2">
-        <v>-3.129997253417969</v>
+        <v>-6.919998168945312</v>
       </c>
       <c r="CU2">
-        <v>-0.0268048072570003</v>
+        <v>-0.05926178271716354</v>
       </c>
       <c r="CV2">
         <v>1</v>
       </c>
       <c r="CX2">
-        <v>982</v>
+        <v>978.010009765625</v>
       </c>
       <c r="CY2">
         <v>0</v>
@@ -2699,10 +2754,10 @@
         <v>1</v>
       </c>
       <c r="DA2">
-        <v>37</v>
+        <v>33.010009765625</v>
       </c>
       <c r="DB2">
-        <v>0.03915343915343916</v>
+        <v>0.03493122726521158</v>
       </c>
       <c r="DC2">
         <v>0</v>
@@ -2732,28 +2787,28 @@
         <v>0</v>
       </c>
       <c r="DX2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DZ2">
-        <v>570.8200073242188</v>
+        <v>539.6199951171875</v>
       </c>
       <c r="EA2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="EB2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC2">
-        <v>-65.6300048828125</v>
+        <v>-96.83001708984375</v>
       </c>
       <c r="ED2">
-        <v>-0.1031188681342403</v>
+        <v>-0.1521408048278046</v>
       </c>
       <c r="EE2">
         <v>1</v>
       </c>
       <c r="EG2">
-        <v>280.6499938964844</v>
+        <v>279.1199951171875</v>
       </c>
       <c r="EH2">
         <v>0</v>
@@ -2762,31 +2817,28 @@
         <v>3</v>
       </c>
       <c r="EJ2">
-        <v>-9.350006103515625</v>
+        <v>-10.8800048828125</v>
       </c>
       <c r="EK2">
-        <v>-0.03224140035695044</v>
+        <v>-0.0375172582165948</v>
       </c>
       <c r="EL2">
         <v>1</v>
       </c>
-      <c r="EM2">
-        <v>-301.6000061035156</v>
-      </c>
       <c r="EN2">
-        <v>310.4400024414062</v>
+        <v>330.1700134277344</v>
       </c>
       <c r="EO2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="EP2">
         <v>3</v>
       </c>
       <c r="EQ2">
-        <v>8.839996337890625</v>
+        <v>28.57000732421875</v>
       </c>
       <c r="ER2">
-        <v>0.02931033209215705</v>
+        <v>0.09472813907839539</v>
       </c>
       <c r="ES2">
         <v>0</v>
@@ -2798,28 +2850,28 @@
         <v>0</v>
       </c>
       <c r="EZ2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FB2">
-        <v>172.6199951171875</v>
+        <v>169.3099975585938</v>
       </c>
       <c r="FC2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="FD2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="FE2">
-        <v>-13.76499938964847</v>
+        <v>-17.07499694824222</v>
       </c>
       <c r="FF2">
-        <v>-0.07385250849227354</v>
+        <v>-0.09161143574578889</v>
       </c>
       <c r="FG2">
         <v>1</v>
       </c>
       <c r="FI2">
-        <v>420.239990234375</v>
+        <v>427.8599853515625</v>
       </c>
       <c r="FJ2">
         <v>0</v>
@@ -2828,10 +2880,10 @@
         <v>2</v>
       </c>
       <c r="FL2">
-        <v>13.76998901367188</v>
+        <v>21.38998413085938</v>
       </c>
       <c r="FM2">
-        <v>0.03387701176548852</v>
+        <v>0.05262377067587121</v>
       </c>
       <c r="FN2">
         <v>0</v>
@@ -2845,20 +2897,11 @@
       <c r="FU2">
         <v>0</v>
       </c>
-      <c r="FW2">
-        <v>454.15</v>
-      </c>
       <c r="FX2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="FY2">
         <v>0</v>
-      </c>
-      <c r="FZ2">
-        <v>-91.85000000000002</v>
-      </c>
-      <c r="GA2">
-        <v>-0.1682234432234433</v>
       </c>
     </row>
     <row r="3" spans="1:183">
@@ -2866,25 +2909,25 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>9752.886795803435</v>
+        <v>9600.492880668853</v>
       </c>
       <c r="C3">
-        <v>-1931.433196261994</v>
+        <v>-2382.287057075287</v>
       </c>
       <c r="D3">
-        <v>83.49369374084472</v>
+        <v>-450.8538608132935</v>
       </c>
       <c r="E3">
         <v>10000</v>
       </c>
       <c r="F3">
-        <v>-0.02471132041965651</v>
+        <v>-0.03995071193311472</v>
       </c>
       <c r="G3">
-        <v>-0.9851998901367194</v>
+        <v>-3.674000000000001</v>
       </c>
       <c r="H3">
-        <v>-0.007934282875612668</v>
+        <v>-0.006728937728937732</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -2907,11 +2950,8 @@
       <c r="W3">
         <v>1</v>
       </c>
-      <c r="X3">
-        <v>-356.2999877929688</v>
-      </c>
       <c r="Z3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA3">
         <v>2</v>
@@ -2991,20 +3031,11 @@
       <c r="CH3">
         <v>0</v>
       </c>
-      <c r="CJ3">
-        <v>99.54000091552734</v>
-      </c>
       <c r="CK3">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="CL3">
         <v>0</v>
-      </c>
-      <c r="CM3">
-        <v>-24.62999725341798</v>
-      </c>
-      <c r="CN3">
-        <v>-0.1983570718903167</v>
       </c>
       <c r="CO3">
         <v>1</v>
@@ -3070,13 +3101,16 @@
         <v>3</v>
       </c>
       <c r="EL3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="EM3">
+        <v>-301.6000061035156</v>
       </c>
       <c r="EO3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="EP3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="ES3">
         <v>0</v>
@@ -3115,13 +3149,22 @@
         <v>0</v>
       </c>
       <c r="FU3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="FW3">
+        <v>454.15</v>
       </c>
       <c r="FX3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="FY3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="FZ3">
+        <v>-91.85000000000002</v>
+      </c>
+      <c r="GA3">
+        <v>-0.1682234432234433</v>
       </c>
     </row>
     <row r="4" spans="1:183">
@@ -3129,19 +3172,25 @@
         <v>19</v>
       </c>
       <c r="B4">
-        <v>9804.852986706146</v>
+        <v>9752.886795803435</v>
       </c>
       <c r="C4">
-        <v>-2014.926890002838</v>
+        <v>-1931.433196261994</v>
       </c>
       <c r="D4">
-        <v>-3176.771366113281</v>
+        <v>83.49369374084472</v>
       </c>
       <c r="E4">
         <v>10000</v>
       </c>
       <c r="F4">
-        <v>-0.01951470132938538</v>
+        <v>-0.02471132041965651</v>
+      </c>
+      <c r="G4">
+        <v>-0.9851998901367194</v>
+      </c>
+      <c r="H4">
+        <v>-0.007934282875612668</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -3155,32 +3204,29 @@
       <c r="P4">
         <v>1</v>
       </c>
-      <c r="Q4">
-        <v>-528.2349853515625</v>
-      </c>
       <c r="S4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4">
         <v>1</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X4">
+        <v>-356.2999877929688</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD4">
         <v>1</v>
       </c>
-      <c r="AE4">
-        <v>-256.2999877929688</v>
-      </c>
       <c r="AG4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH4">
         <v>3</v>
@@ -3249,22 +3295,28 @@
         <v>0</v>
       </c>
       <c r="CH4">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="CJ4">
+        <v>99.54000091552734</v>
       </c>
       <c r="CK4">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="CL4">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="CM4">
+        <v>-24.62999725341798</v>
+      </c>
+      <c r="CN4">
+        <v>-0.1983570718903167</v>
       </c>
       <c r="CO4">
         <v>1</v>
       </c>
-      <c r="CP4">
-        <v>-116.7699966430664</v>
-      </c>
       <c r="CR4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CS4">
         <v>8</v>
@@ -3272,11 +3324,8 @@
       <c r="CV4">
         <v>1</v>
       </c>
-      <c r="CW4">
-        <v>-945</v>
-      </c>
       <c r="CY4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CZ4">
         <v>1</v>
@@ -3386,19 +3435,19 @@
         <v>20</v>
       </c>
       <c r="B5">
-        <v>9904.144532567963</v>
+        <v>9804.852986706146</v>
       </c>
       <c r="C5">
-        <v>1161.844476110443</v>
+        <v>-2014.926890002838</v>
       </c>
       <c r="D5">
-        <v>-756.8135172088623</v>
+        <v>-3176.771366113281</v>
       </c>
       <c r="E5">
         <v>10000</v>
       </c>
       <c r="F5">
-        <v>-0.009585546743203666</v>
+        <v>-0.01951470132938538</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -3410,13 +3459,16 @@
         <v>2</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>-528.2349853515625</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5">
         <v>0</v>
@@ -3428,13 +3480,16 @@
         <v>0</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AE5">
+        <v>-256.2999877929688</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK5">
         <v>1</v>
@@ -3448,11 +3503,8 @@
       <c r="AR5">
         <v>1</v>
       </c>
-      <c r="AS5">
-        <v>-378.3500061035156</v>
-      </c>
       <c r="AU5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV5">
         <v>2</v>
@@ -3512,22 +3564,28 @@
         <v>8</v>
       </c>
       <c r="CO5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CP5">
+        <v>-116.7699966430664</v>
       </c>
       <c r="CR5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CS5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CV5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CW5">
+        <v>-945</v>
       </c>
       <c r="CY5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CZ5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC5">
         <v>0</v>
@@ -3634,19 +3692,19 @@
         <v>21</v>
       </c>
       <c r="B6">
-        <v>9950.788089754853</v>
+        <v>9904.144532567963</v>
       </c>
       <c r="C6">
-        <v>1918.657993319305</v>
+        <v>1161.844476110443</v>
       </c>
       <c r="D6">
-        <v>-546.0819</v>
+        <v>-756.8135172088623</v>
       </c>
       <c r="E6">
         <v>10000</v>
       </c>
       <c r="F6">
-        <v>-0.004921191024514715</v>
+        <v>-0.009585546743203666</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -3694,13 +3752,16 @@
         <v>1</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AS6">
+        <v>-378.3500061035156</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY6">
         <v>1</v>
@@ -3867,11 +3928,8 @@
       <c r="FU6">
         <v>1</v>
       </c>
-      <c r="FV6">
-        <v>-546</v>
-      </c>
       <c r="FX6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FY6">
         <v>1</v>
@@ -3882,28 +3940,25 @@
         <v>22</v>
       </c>
       <c r="B7">
-        <v>9970.279909493622</v>
+        <v>9950.788089754853</v>
       </c>
       <c r="C7">
-        <v>2464.739893319305</v>
+        <v>1918.657993319305</v>
       </c>
       <c r="D7">
-        <v>-1612.271831359497</v>
+        <v>-546.0819</v>
       </c>
       <c r="E7">
         <v>10000</v>
       </c>
       <c r="F7">
-        <v>-0.00297200905063788</v>
+        <v>-0.004921191024514715</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
-      <c r="J7">
-        <v>-332.7950134277344</v>
-      </c>
       <c r="L7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7">
         <v>2</v>
@@ -3974,11 +4029,8 @@
       <c r="BM7">
         <v>1</v>
       </c>
-      <c r="BN7">
-        <v>-52.58</v>
-      </c>
       <c r="BP7">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BQ7">
         <v>18</v>
@@ -4119,13 +4171,16 @@
         <v>0</v>
       </c>
       <c r="FU7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FV7">
+        <v>-546</v>
       </c>
       <c r="FX7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FY7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:183">
@@ -4133,28 +4188,31 @@
         <v>23</v>
       </c>
       <c r="B8">
-        <v>9919.091680733491</v>
+        <v>9970.279909493622</v>
       </c>
       <c r="C8">
-        <v>4077.011724678802</v>
+        <v>2464.739893319305</v>
       </c>
       <c r="D8">
-        <v>-5922.988275321198</v>
+        <v>-1612.271831359497</v>
       </c>
       <c r="E8">
         <v>10000</v>
       </c>
       <c r="F8">
-        <v>-0.008090831926650943</v>
+        <v>-0.00297200905063788</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>-332.7950134277344</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -4186,11 +4244,8 @@
       <c r="AK8">
         <v>1</v>
       </c>
-      <c r="AL8">
-        <v>-733.2050170898438</v>
-      </c>
       <c r="AN8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>1</v>
@@ -4207,11 +4262,8 @@
       <c r="AY8">
         <v>1</v>
       </c>
-      <c r="AZ8">
-        <v>-236.0549926757812</v>
-      </c>
       <c r="BB8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BC8">
         <v>4</v>
@@ -4226,13 +4278,16 @@
         <v>0</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BN8">
+        <v>-52.58</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BT8">
         <v>0</v>
@@ -4255,11 +4310,8 @@
       <c r="CH8">
         <v>1</v>
       </c>
-      <c r="CI8">
-        <v>-124.1699981689453</v>
-      </c>
       <c r="CK8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CL8">
         <v>8</v>
@@ -4312,11 +4364,8 @@
       <c r="DX8">
         <v>1</v>
       </c>
-      <c r="DY8">
-        <v>-636.4500122070312</v>
-      </c>
       <c r="EA8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB8">
         <v>1</v>
@@ -4324,11 +4373,8 @@
       <c r="EE8">
         <v>1</v>
       </c>
-      <c r="EF8">
-        <v>-290</v>
-      </c>
       <c r="EH8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="EI8">
         <v>3</v>
@@ -4354,11 +4400,8 @@
       <c r="EZ8">
         <v>1</v>
       </c>
-      <c r="FA8">
-        <v>-186.384994506836</v>
-      </c>
       <c r="FC8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="FD8">
         <v>5</v>
@@ -4366,11 +4409,8 @@
       <c r="FG8">
         <v>1</v>
       </c>
-      <c r="FH8">
-        <v>-406.4700012207031</v>
-      </c>
       <c r="FJ8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="FK8">
         <v>2</v>
@@ -4399,19 +4439,19 @@
         <v>24</v>
       </c>
       <c r="B9">
-        <v>10000</v>
+        <v>9919.091680733491</v>
       </c>
       <c r="C9">
-        <v>10000</v>
+        <v>4077.011724678802</v>
       </c>
       <c r="D9">
-        <v>10000</v>
+        <v>-5922.988275321198</v>
       </c>
       <c r="E9">
         <v>10000</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>-0.008090831926650943</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -4450,13 +4490,16 @@
         <v>0</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AL9">
+        <v>-733.2050170898438</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -4468,13 +4511,16 @@
         <v>0</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AZ9">
+        <v>-236.0549926757812</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF9">
         <v>0</v>
@@ -4513,13 +4559,16 @@
         <v>0</v>
       </c>
       <c r="CH9">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CI9">
+        <v>-124.1699981689453</v>
       </c>
       <c r="CK9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CL9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CO9">
         <v>0</v>
@@ -4567,22 +4616,28 @@
         <v>0</v>
       </c>
       <c r="DX9">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="DY9">
+        <v>-636.4500122070312</v>
       </c>
       <c r="EA9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EB9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EE9">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="EF9">
+        <v>-290</v>
       </c>
       <c r="EH9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="EI9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="EL9">
         <v>0</v>
@@ -4603,22 +4658,28 @@
         <v>0</v>
       </c>
       <c r="EZ9">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FA9">
+        <v>-186.384994506836</v>
       </c>
       <c r="FC9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="FD9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="FG9">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FH9">
+        <v>-406.4700012207031</v>
       </c>
       <c r="FJ9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="FK9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="FN9">
         <v>0</v>
@@ -4636,11 +4697,256 @@
         <v>0</v>
       </c>
       <c r="FY9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:183">
+      <c r="A10" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10">
+        <v>10000</v>
+      </c>
+      <c r="C10">
+        <v>10000</v>
+      </c>
+      <c r="D10">
+        <v>10000</v>
+      </c>
+      <c r="E10">
+        <v>10000</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CD10">
+        <v>0</v>
+      </c>
+      <c r="CE10">
+        <v>0</v>
+      </c>
+      <c r="CH10">
+        <v>0</v>
+      </c>
+      <c r="CK10">
+        <v>0</v>
+      </c>
+      <c r="CL10">
+        <v>0</v>
+      </c>
+      <c r="CO10">
+        <v>0</v>
+      </c>
+      <c r="CR10">
+        <v>0</v>
+      </c>
+      <c r="CS10">
+        <v>0</v>
+      </c>
+      <c r="CV10">
+        <v>0</v>
+      </c>
+      <c r="CY10">
+        <v>0</v>
+      </c>
+      <c r="CZ10">
+        <v>0</v>
+      </c>
+      <c r="DC10">
+        <v>0</v>
+      </c>
+      <c r="DF10">
+        <v>0</v>
+      </c>
+      <c r="DG10">
+        <v>0</v>
+      </c>
+      <c r="DJ10">
+        <v>0</v>
+      </c>
+      <c r="DM10">
+        <v>0</v>
+      </c>
+      <c r="DN10">
+        <v>0</v>
+      </c>
+      <c r="DQ10">
+        <v>0</v>
+      </c>
+      <c r="DT10">
+        <v>0</v>
+      </c>
+      <c r="DU10">
+        <v>0</v>
+      </c>
+      <c r="DX10">
+        <v>0</v>
+      </c>
+      <c r="EA10">
+        <v>0</v>
+      </c>
+      <c r="EB10">
+        <v>0</v>
+      </c>
+      <c r="EE10">
+        <v>0</v>
+      </c>
+      <c r="EH10">
+        <v>0</v>
+      </c>
+      <c r="EI10">
+        <v>0</v>
+      </c>
+      <c r="EL10">
+        <v>0</v>
+      </c>
+      <c r="EO10">
+        <v>0</v>
+      </c>
+      <c r="EP10">
+        <v>0</v>
+      </c>
+      <c r="ES10">
+        <v>0</v>
+      </c>
+      <c r="EV10">
+        <v>0</v>
+      </c>
+      <c r="EW10">
+        <v>0</v>
+      </c>
+      <c r="EZ10">
+        <v>0</v>
+      </c>
+      <c r="FC10">
+        <v>0</v>
+      </c>
+      <c r="FD10">
+        <v>0</v>
+      </c>
+      <c r="FG10">
+        <v>0</v>
+      </c>
+      <c r="FJ10">
+        <v>0</v>
+      </c>
+      <c r="FK10">
+        <v>0</v>
+      </c>
+      <c r="FN10">
+        <v>0</v>
+      </c>
+      <c r="FQ10">
+        <v>0</v>
+      </c>
+      <c r="FR10">
+        <v>0</v>
+      </c>
+      <c r="FU10">
+        <v>0</v>
+      </c>
+      <c r="FX10">
+        <v>0</v>
+      </c>
+      <c r="FY10">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AA2:AA9">
+  <conditionalFormatting sqref="AA2:AA10">
     <cfRule type="cellIs" dxfId="4" priority="25" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4648,7 +4954,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE2:AE9">
+  <conditionalFormatting sqref="AE2:AE10">
     <cfRule type="cellIs" dxfId="4" priority="27" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4656,7 +4962,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF2:AF9">
+  <conditionalFormatting sqref="AF2:AF10">
     <cfRule type="cellIs" dxfId="4" priority="29" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4664,7 +4970,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG2:AG9">
+  <conditionalFormatting sqref="AG2:AG10">
     <cfRule type="cellIs" dxfId="4" priority="31" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4672,7 +4978,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH2:AH9">
+  <conditionalFormatting sqref="AH2:AH10">
     <cfRule type="cellIs" dxfId="4" priority="33" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4680,7 +4986,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL2:AL9">
+  <conditionalFormatting sqref="AL2:AL10">
     <cfRule type="cellIs" dxfId="4" priority="35" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4688,7 +4994,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM2:AM9">
+  <conditionalFormatting sqref="AM2:AM10">
     <cfRule type="cellIs" dxfId="4" priority="37" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4696,7 +5002,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AN2:AN9">
+  <conditionalFormatting sqref="AN2:AN10">
     <cfRule type="cellIs" dxfId="4" priority="39" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4704,7 +5010,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AO2:AO9">
+  <conditionalFormatting sqref="AO2:AO10">
     <cfRule type="cellIs" dxfId="4" priority="41" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4712,7 +5018,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AS2:AS9">
+  <conditionalFormatting sqref="AS2:AS10">
     <cfRule type="cellIs" dxfId="4" priority="43" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4720,7 +5026,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AT2:AT9">
+  <conditionalFormatting sqref="AT2:AT10">
     <cfRule type="cellIs" dxfId="4" priority="45" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4728,7 +5034,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU2:AU9">
+  <conditionalFormatting sqref="AU2:AU10">
     <cfRule type="cellIs" dxfId="4" priority="47" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4736,7 +5042,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AV2:AV9">
+  <conditionalFormatting sqref="AV2:AV10">
     <cfRule type="cellIs" dxfId="4" priority="49" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4744,7 +5050,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AZ2:AZ9">
+  <conditionalFormatting sqref="AZ2:AZ10">
     <cfRule type="cellIs" dxfId="4" priority="51" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4752,7 +5058,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BA2:BA9">
+  <conditionalFormatting sqref="BA2:BA10">
     <cfRule type="cellIs" dxfId="4" priority="53" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4760,7 +5066,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB2:BB9">
+  <conditionalFormatting sqref="BB2:BB10">
     <cfRule type="cellIs" dxfId="4" priority="55" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4768,7 +5074,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BC2:BC9">
+  <conditionalFormatting sqref="BC2:BC10">
     <cfRule type="cellIs" dxfId="4" priority="57" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4776,7 +5082,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BG2:BG9">
+  <conditionalFormatting sqref="BG2:BG10">
     <cfRule type="cellIs" dxfId="4" priority="59" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4784,7 +5090,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BH2:BH9">
+  <conditionalFormatting sqref="BH2:BH10">
     <cfRule type="cellIs" dxfId="4" priority="61" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4792,7 +5098,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BI2:BI9">
+  <conditionalFormatting sqref="BI2:BI10">
     <cfRule type="cellIs" dxfId="4" priority="63" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4800,7 +5106,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BJ2:BJ9">
+  <conditionalFormatting sqref="BJ2:BJ10">
     <cfRule type="cellIs" dxfId="4" priority="65" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4808,7 +5114,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BN2:BN9">
+  <conditionalFormatting sqref="BN2:BN10">
     <cfRule type="cellIs" dxfId="4" priority="67" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4816,7 +5122,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BO2:BO9">
+  <conditionalFormatting sqref="BO2:BO10">
     <cfRule type="cellIs" dxfId="4" priority="69" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4824,7 +5130,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BP2:BP9">
+  <conditionalFormatting sqref="BP2:BP10">
     <cfRule type="cellIs" dxfId="4" priority="71" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4832,7 +5138,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BQ2:BQ9">
+  <conditionalFormatting sqref="BQ2:BQ10">
     <cfRule type="cellIs" dxfId="4" priority="73" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4840,7 +5146,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BU2:BU9">
+  <conditionalFormatting sqref="BU2:BU10">
     <cfRule type="cellIs" dxfId="4" priority="75" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4848,7 +5154,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BV2:BV9">
+  <conditionalFormatting sqref="BV2:BV10">
     <cfRule type="cellIs" dxfId="4" priority="77" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4856,7 +5162,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BW2:BW9">
+  <conditionalFormatting sqref="BW2:BW10">
     <cfRule type="cellIs" dxfId="4" priority="79" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4864,7 +5170,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BX2:BX9">
+  <conditionalFormatting sqref="BX2:BX10">
     <cfRule type="cellIs" dxfId="4" priority="81" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4872,7 +5178,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CB2:CB9">
+  <conditionalFormatting sqref="CB2:CB10">
     <cfRule type="cellIs" dxfId="4" priority="83" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4880,7 +5186,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CC2:CC9">
+  <conditionalFormatting sqref="CC2:CC10">
     <cfRule type="cellIs" dxfId="4" priority="85" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4888,7 +5194,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CD2:CD9">
+  <conditionalFormatting sqref="CD2:CD10">
     <cfRule type="cellIs" dxfId="4" priority="87" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4896,7 +5202,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CE2:CE9">
+  <conditionalFormatting sqref="CE2:CE10">
     <cfRule type="cellIs" dxfId="4" priority="89" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4904,7 +5210,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CI2:CI9">
+  <conditionalFormatting sqref="CI2:CI10">
     <cfRule type="cellIs" dxfId="4" priority="91" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4912,7 +5218,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CJ2:CJ9">
+  <conditionalFormatting sqref="CJ2:CJ10">
     <cfRule type="cellIs" dxfId="4" priority="93" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4920,7 +5226,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CK2:CK9">
+  <conditionalFormatting sqref="CK2:CK10">
     <cfRule type="cellIs" dxfId="4" priority="95" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4928,7 +5234,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CL2:CL9">
+  <conditionalFormatting sqref="CL2:CL10">
     <cfRule type="cellIs" dxfId="4" priority="97" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4936,7 +5242,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CP2:CP9">
+  <conditionalFormatting sqref="CP2:CP10">
     <cfRule type="cellIs" dxfId="4" priority="99" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4944,7 +5250,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CQ2:CQ9">
+  <conditionalFormatting sqref="CQ2:CQ10">
     <cfRule type="cellIs" dxfId="4" priority="101" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4952,7 +5258,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CR2:CR9">
+  <conditionalFormatting sqref="CR2:CR10">
     <cfRule type="cellIs" dxfId="4" priority="103" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4960,7 +5266,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CS2:CS9">
+  <conditionalFormatting sqref="CS2:CS10">
     <cfRule type="cellIs" dxfId="4" priority="105" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4968,7 +5274,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CW2:CW9">
+  <conditionalFormatting sqref="CW2:CW10">
     <cfRule type="cellIs" dxfId="4" priority="107" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4976,7 +5282,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CX2:CX9">
+  <conditionalFormatting sqref="CX2:CX10">
     <cfRule type="cellIs" dxfId="4" priority="109" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4984,7 +5290,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CY2:CY9">
+  <conditionalFormatting sqref="CY2:CY10">
     <cfRule type="cellIs" dxfId="4" priority="111" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4992,7 +5298,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CZ2:CZ9">
+  <conditionalFormatting sqref="CZ2:CZ10">
     <cfRule type="cellIs" dxfId="4" priority="113" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5000,7 +5306,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="D2:D10">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5008,7 +5314,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DD2:DD9">
+  <conditionalFormatting sqref="DD2:DD10">
     <cfRule type="cellIs" dxfId="4" priority="115" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5016,7 +5322,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DE2:DE9">
+  <conditionalFormatting sqref="DE2:DE10">
     <cfRule type="cellIs" dxfId="4" priority="117" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5024,7 +5330,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DF2:DF9">
+  <conditionalFormatting sqref="DF2:DF10">
     <cfRule type="cellIs" dxfId="4" priority="119" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5032,7 +5338,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DG2:DG9">
+  <conditionalFormatting sqref="DG2:DG10">
     <cfRule type="cellIs" dxfId="4" priority="121" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5040,7 +5346,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DK2:DK9">
+  <conditionalFormatting sqref="DK2:DK10">
     <cfRule type="cellIs" dxfId="4" priority="123" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5048,7 +5354,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DL2:DL9">
+  <conditionalFormatting sqref="DL2:DL10">
     <cfRule type="cellIs" dxfId="4" priority="125" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5056,7 +5362,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DM2:DM9">
+  <conditionalFormatting sqref="DM2:DM10">
     <cfRule type="cellIs" dxfId="4" priority="127" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5064,7 +5370,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DN2:DN9">
+  <conditionalFormatting sqref="DN2:DN10">
     <cfRule type="cellIs" dxfId="4" priority="129" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5072,7 +5378,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DR2:DR9">
+  <conditionalFormatting sqref="DR2:DR10">
     <cfRule type="cellIs" dxfId="4" priority="131" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5080,7 +5386,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DS2:DS9">
+  <conditionalFormatting sqref="DS2:DS10">
     <cfRule type="cellIs" dxfId="4" priority="133" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5088,7 +5394,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DT2:DT9">
+  <conditionalFormatting sqref="DT2:DT10">
     <cfRule type="cellIs" dxfId="4" priority="135" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5096,7 +5402,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DU2:DU9">
+  <conditionalFormatting sqref="DU2:DU10">
     <cfRule type="cellIs" dxfId="4" priority="137" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5104,7 +5410,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DY2:DY9">
+  <conditionalFormatting sqref="DY2:DY10">
     <cfRule type="cellIs" dxfId="4" priority="139" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5112,7 +5418,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DZ2:DZ9">
+  <conditionalFormatting sqref="DZ2:DZ10">
     <cfRule type="cellIs" dxfId="4" priority="141" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5120,7 +5426,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EA2:EA9">
+  <conditionalFormatting sqref="EA2:EA10">
     <cfRule type="cellIs" dxfId="4" priority="143" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5128,7 +5434,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EB2:EB9">
+  <conditionalFormatting sqref="EB2:EB10">
     <cfRule type="cellIs" dxfId="4" priority="145" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5136,7 +5442,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EF2:EF9">
+  <conditionalFormatting sqref="EF2:EF10">
     <cfRule type="cellIs" dxfId="4" priority="147" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5144,7 +5450,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EG2:EG9">
+  <conditionalFormatting sqref="EG2:EG10">
     <cfRule type="cellIs" dxfId="4" priority="149" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5152,7 +5458,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EH2:EH9">
+  <conditionalFormatting sqref="EH2:EH10">
     <cfRule type="cellIs" dxfId="4" priority="151" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5160,7 +5466,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EI2:EI9">
+  <conditionalFormatting sqref="EI2:EI10">
     <cfRule type="cellIs" dxfId="4" priority="153" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5168,7 +5474,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EM2:EM9">
+  <conditionalFormatting sqref="EM2:EM10">
     <cfRule type="cellIs" dxfId="4" priority="155" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5176,7 +5482,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EN2:EN9">
+  <conditionalFormatting sqref="EN2:EN10">
     <cfRule type="cellIs" dxfId="4" priority="157" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5184,7 +5490,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EO2:EO9">
+  <conditionalFormatting sqref="EO2:EO10">
     <cfRule type="cellIs" dxfId="4" priority="159" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5192,7 +5498,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EP2:EP9">
+  <conditionalFormatting sqref="EP2:EP10">
     <cfRule type="cellIs" dxfId="4" priority="161" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5200,7 +5506,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="ET2:ET9">
+  <conditionalFormatting sqref="ET2:ET10">
     <cfRule type="cellIs" dxfId="4" priority="163" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5208,7 +5514,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EU2:EU9">
+  <conditionalFormatting sqref="EU2:EU10">
     <cfRule type="cellIs" dxfId="4" priority="165" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5216,7 +5522,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EV2:EV9">
+  <conditionalFormatting sqref="EV2:EV10">
     <cfRule type="cellIs" dxfId="4" priority="167" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5224,7 +5530,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EW2:EW9">
+  <conditionalFormatting sqref="EW2:EW10">
     <cfRule type="cellIs" dxfId="4" priority="169" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5232,7 +5538,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FA2:FA9">
+  <conditionalFormatting sqref="FA2:FA10">
     <cfRule type="cellIs" dxfId="4" priority="171" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5240,7 +5546,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FB2:FB9">
+  <conditionalFormatting sqref="FB2:FB10">
     <cfRule type="cellIs" dxfId="4" priority="173" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5248,7 +5554,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FC2:FC9">
+  <conditionalFormatting sqref="FC2:FC10">
     <cfRule type="cellIs" dxfId="4" priority="175" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5256,7 +5562,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FD2:FD9">
+  <conditionalFormatting sqref="FD2:FD10">
     <cfRule type="cellIs" dxfId="4" priority="177" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5264,7 +5570,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FH2:FH9">
+  <conditionalFormatting sqref="FH2:FH10">
     <cfRule type="cellIs" dxfId="4" priority="179" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5272,7 +5578,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FI2:FI9">
+  <conditionalFormatting sqref="FI2:FI10">
     <cfRule type="cellIs" dxfId="4" priority="181" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5280,7 +5586,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FJ2:FJ9">
+  <conditionalFormatting sqref="FJ2:FJ10">
     <cfRule type="cellIs" dxfId="4" priority="183" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5288,7 +5594,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FK2:FK9">
+  <conditionalFormatting sqref="FK2:FK10">
     <cfRule type="cellIs" dxfId="4" priority="185" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5296,7 +5602,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FO2:FO9">
+  <conditionalFormatting sqref="FO2:FO10">
     <cfRule type="cellIs" dxfId="4" priority="187" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5304,7 +5610,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FP2:FP9">
+  <conditionalFormatting sqref="FP2:FP10">
     <cfRule type="cellIs" dxfId="4" priority="189" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5312,7 +5618,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FQ2:FQ9">
+  <conditionalFormatting sqref="FQ2:FQ10">
     <cfRule type="cellIs" dxfId="4" priority="191" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5320,7 +5626,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FR2:FR9">
+  <conditionalFormatting sqref="FR2:FR10">
     <cfRule type="cellIs" dxfId="4" priority="193" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5328,7 +5634,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FV2:FV9">
+  <conditionalFormatting sqref="FV2:FV10">
     <cfRule type="cellIs" dxfId="4" priority="195" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5336,7 +5642,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FW2:FW9">
+  <conditionalFormatting sqref="FW2:FW10">
     <cfRule type="cellIs" dxfId="4" priority="197" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5344,7 +5650,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FX2:FX9">
+  <conditionalFormatting sqref="FX2:FX10">
     <cfRule type="cellIs" dxfId="4" priority="199" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5352,7 +5658,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FY2:FY9">
+  <conditionalFormatting sqref="FY2:FY10">
     <cfRule type="cellIs" dxfId="4" priority="201" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5360,7 +5666,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J9">
+  <conditionalFormatting sqref="J2:J10">
     <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5368,7 +5674,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K9">
+  <conditionalFormatting sqref="K2:K10">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5376,7 +5682,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L9">
+  <conditionalFormatting sqref="L2:L10">
     <cfRule type="cellIs" dxfId="4" priority="7" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5384,7 +5690,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M9">
+  <conditionalFormatting sqref="M2:M10">
     <cfRule type="cellIs" dxfId="4" priority="9" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5392,7 +5698,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q9">
+  <conditionalFormatting sqref="Q2:Q10">
     <cfRule type="cellIs" dxfId="4" priority="11" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5400,7 +5706,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R9">
+  <conditionalFormatting sqref="R2:R10">
     <cfRule type="cellIs" dxfId="4" priority="13" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5408,7 +5714,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S9">
+  <conditionalFormatting sqref="S2:S10">
     <cfRule type="cellIs" dxfId="4" priority="15" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5416,7 +5722,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T9">
+  <conditionalFormatting sqref="T2:T10">
     <cfRule type="cellIs" dxfId="4" priority="17" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5424,7 +5730,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X9">
+  <conditionalFormatting sqref="X2:X10">
     <cfRule type="cellIs" dxfId="4" priority="19" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5432,7 +5738,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y9">
+  <conditionalFormatting sqref="Y2:Y10">
     <cfRule type="cellIs" dxfId="4" priority="21" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5440,7 +5746,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:Z9">
+  <conditionalFormatting sqref="Z2:Z10">
     <cfRule type="cellIs" dxfId="4" priority="23" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>

--- a/reports/paper_trade_trx.xlsx
+++ b/reports/paper_trade_trx.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="251">
   <si>
     <t>NAV</t>
   </si>
@@ -36,7 +36,7 @@
     <t>last_updated</t>
   </si>
   <si>
-    <t>2026-10-15 18:01:13</t>
+    <t>2026-10-19 18:03:42</t>
   </si>
   <si>
     <t>pf_id</t>
@@ -69,6 +69,9 @@
     <t>date</t>
   </si>
   <si>
+    <t>2026-10-16</t>
+  </si>
+  <si>
     <t>2026-10-15</t>
   </si>
   <si>
@@ -96,6 +99,9 @@
     <t>2026-09-29</t>
   </si>
   <si>
+    <t>NVDA</t>
+  </si>
+  <si>
     <t>QCOM</t>
   </si>
   <si>
@@ -144,15 +150,15 @@
     <t>TXN</t>
   </si>
   <si>
-    <t>NVDA</t>
-  </si>
-  <si>
     <t>paper_trade</t>
   </si>
   <si>
     <t>initial</t>
   </si>
   <si>
+    <t>2026-10-16_5989af14de8535428a112c8e80fa9e27</t>
+  </si>
+  <si>
     <t>2026-10-15_b2113621636a6c54be0246381e6e8245</t>
   </si>
   <si>
@@ -760,6 +766,9 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>2026-10-19</t>
   </si>
 </sst>
 </file>
@@ -1284,7 +1293,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>9590</v>
+        <v>9543</v>
       </c>
       <c r="C2" s="2">
         <v>100</v>
@@ -1308,7 +1317,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>9590</v>
+        <v>9543</v>
       </c>
       <c r="C4" s="2">
         <v>100</v>
@@ -1379,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
@@ -1425,42 +1434,42 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2">
-        <v>169.3099975585938</v>
+        <v>216.5599975585937</v>
       </c>
       <c r="G2">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>539.6199951171875</v>
+        <v>169.3099975585938</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="H3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1471,42 +1480,42 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4">
-        <v>454.15</v>
+        <v>539.6199951171875</v>
       </c>
       <c r="G4">
         <v>-1</v>
       </c>
       <c r="H4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5">
-        <v>-301.6000061035156</v>
+        <v>30</v>
+      </c>
+      <c r="F5">
+        <v>454.15</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1517,42 +1526,42 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6">
-        <v>99.54000091552734</v>
+        <v>31</v>
+      </c>
+      <c r="E6">
+        <v>-301.6000061035156</v>
       </c>
       <c r="G6">
-        <v>-8</v>
+        <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7">
-        <v>-356.2999877929688</v>
+        <v>32</v>
+      </c>
+      <c r="F7">
+        <v>99.54000091552734</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="H7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1563,88 +1572,88 @@
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8">
-        <v>-528.2349853515625</v>
+        <v>-356.2999877929688</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E9">
-        <v>-945</v>
+        <v>-528.2349853515625</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10">
-        <v>-116.7699966430664</v>
+        <v>-945</v>
       </c>
       <c r="G10">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E11">
-        <v>-256.2999877929688</v>
+        <v>-116.7699966430664</v>
       </c>
       <c r="G11">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1655,19 +1664,19 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E12">
-        <v>-378.3500061035156</v>
+        <v>-256.2999877929688</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1678,19 +1687,19 @@
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E13">
-        <v>-546</v>
+        <v>-378.3500061035156</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1701,42 +1710,42 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E14">
-        <v>-52.58</v>
+        <v>-546</v>
       </c>
       <c r="G14">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E15">
-        <v>-332.7950134277344</v>
+        <v>-52.58</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1747,157 +1756,157 @@
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E16">
-        <v>-733.2050170898438</v>
+        <v>-332.7950134277344</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E17">
-        <v>-406.4700012207031</v>
+        <v>-733.2050170898438</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E18">
-        <v>-186.384994506836</v>
+        <v>-406.4700012207031</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E19">
-        <v>-290</v>
+        <v>-186.384994506836</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E20">
-        <v>-636.4500122070312</v>
+        <v>-290</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E21">
-        <v>-124.1699981689453</v>
+        <v>-636.4500122070312</v>
       </c>
       <c r="G21">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E22">
-        <v>-236.0549926757812</v>
+        <v>-124.1699981689453</v>
       </c>
       <c r="G22">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1907,23 +1916,46 @@
       <c r="B23" t="s">
         <v>2</v>
       </c>
-      <c r="C23">
-        <v>10000</v>
+      <c r="D23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23">
+        <v>-236.0549926757812</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
       </c>
       <c r="H23" t="s">
         <v>44</v>
       </c>
       <c r="J23" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24">
+        <v>10000</v>
+      </c>
+      <c r="H24" t="s">
+        <v>45</v>
+      </c>
+      <c r="J24" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B23">
+  <conditionalFormatting sqref="B2:B24">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>$B2="option"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C23">
+  <conditionalFormatting sqref="C2:C24">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1931,7 +1963,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E23">
+  <conditionalFormatting sqref="E2:E24">
     <cfRule type="cellIs" dxfId="4" priority="4" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1939,7 +1971,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F23">
+  <conditionalFormatting sqref="F2:F24">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1947,7 +1979,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G23">
+  <conditionalFormatting sqref="G2:G24">
     <cfRule type="cellIs" dxfId="4" priority="8" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1961,7 +1993,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:GA10"/>
+  <dimension ref="A1:GA12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
@@ -1969,10 +2001,10 @@
   <sheetData>
     <row r="1" spans="1:183">
       <c r="A1" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>3</v>
@@ -1981,573 +2013,573 @@
         <v>8</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AL1" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BE1" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="BF1" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BL1" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BM1" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BN1" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BO1" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BP1" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="BQ1" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BR1" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="BS1" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="BT1" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="BU1" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="BV1" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="BW1" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="BX1" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="BY1" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BZ1" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="CA1" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="CB1" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="CC1" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="CD1" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="CE1" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="CF1" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="CH1" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="CI1" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="CJ1" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="CK1" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="CL1" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="CM1" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="CN1" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="CO1" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="CP1" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="CQ1" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="CR1" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="CS1" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="CT1" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="CU1" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="CV1" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="CW1" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="CX1" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="CY1" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="CZ1" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="DA1" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="DB1" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="DC1" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="DD1" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="DE1" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="DF1" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="DG1" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="DH1" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="DI1" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="DJ1" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="DK1" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="DL1" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="DM1" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="DN1" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="DO1" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="DP1" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="DQ1" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="DR1" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="DS1" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="DT1" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="DU1" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="DV1" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="DW1" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="DX1" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="DY1" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="DZ1" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="EA1" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="EB1" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="EC1" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="ED1" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="EE1" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="EF1" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="EG1" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="EH1" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="EI1" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="EJ1" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="EK1" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="EL1" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="EM1" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="EN1" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="EO1" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="EP1" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="EQ1" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="ER1" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="ES1" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="ET1" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="EU1" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="EV1" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="EW1" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="EX1" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="EY1" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="EZ1" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="FA1" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="FB1" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="FC1" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="FD1" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="FE1" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="FF1" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="FG1" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="FH1" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="FI1" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="FJ1" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="FK1" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="FL1" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="FM1" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="FN1" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="FO1" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="FP1" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="FQ1" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="FR1" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="FS1" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="FT1" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="FU1" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="FV1" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="FW1" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="FX1" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="FY1" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="FZ1" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="GA1" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" spans="1:183">
       <c r="A2" s="9" t="s">
-        <v>17</v>
+        <v>250</v>
       </c>
       <c r="B2">
-        <v>9589.634938386749</v>
+        <v>9542.835049995636</v>
       </c>
       <c r="C2">
-        <v>-996.3249996625673</v>
+        <v>-130.2149454267276</v>
       </c>
       <c r="D2">
-        <v>1385.96205741272</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>10000</v>
       </c>
       <c r="F2">
-        <v>-0.04103650616132504</v>
+        <v>-0.0457164950004364</v>
       </c>
       <c r="G2">
-        <v>-2.543401568603515</v>
+        <v>2.099001385498049</v>
       </c>
       <c r="H2">
-        <v>-0.006606232173333065</v>
+        <v>0.00413048691284505</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>342</v>
+        <v>342.9400024414062</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2556,16 +2588,16 @@
         <v>2</v>
       </c>
       <c r="N2">
-        <v>9.204986572265625</v>
+        <v>10.14498901367188</v>
       </c>
       <c r="O2">
-        <v>0.02765962890325713</v>
+        <v>0.03048419779244926</v>
       </c>
       <c r="P2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>539.4400024414062</v>
+        <v>533.52001953125</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -2574,16 +2606,16 @@
         <v>1</v>
       </c>
       <c r="U2">
-        <v>11.20501708984375</v>
+        <v>5.2850341796875</v>
       </c>
       <c r="V2">
-        <v>0.0212121828363685</v>
+        <v>0.01000508168948722</v>
       </c>
       <c r="W2">
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>349.2200012207031</v>
+        <v>344.1799926757812</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2592,16 +2624,16 @@
         <v>2</v>
       </c>
       <c r="AB2">
-        <v>-7.079986572265625</v>
+        <v>-12.1199951171875</v>
       </c>
       <c r="AC2">
-        <v>-0.01987085830712831</v>
+        <v>-0.03401626587826301</v>
       </c>
       <c r="AD2">
         <v>1</v>
       </c>
       <c r="AF2">
-        <v>254.759994506836</v>
+        <v>262.4500122070312</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -2610,16 +2642,16 @@
         <v>3</v>
       </c>
       <c r="AI2">
-        <v>-1.539993286132784</v>
+        <v>6.1500244140625</v>
       </c>
       <c r="AJ2">
-        <v>-0.006008557781815971</v>
+        <v>0.02399541438538932</v>
       </c>
       <c r="AK2">
         <v>1</v>
       </c>
       <c r="AM2">
-        <v>736.719970703125</v>
+        <v>705.4400024414062</v>
       </c>
       <c r="AN2">
         <v>0</v>
@@ -2628,16 +2660,16 @@
         <v>1</v>
       </c>
       <c r="AP2">
-        <v>3.51495361328125</v>
+        <v>-27.7650146484375</v>
       </c>
       <c r="AQ2">
-        <v>0.00479395739438937</v>
+        <v>-0.03786800963070236</v>
       </c>
       <c r="AR2">
         <v>1</v>
       </c>
       <c r="AT2">
-        <v>362.4400024414063</v>
+        <v>368.0599975585938</v>
       </c>
       <c r="AU2">
         <v>0</v>
@@ -2646,28 +2678,19 @@
         <v>2</v>
       </c>
       <c r="AW2">
-        <v>-15.91000366210932</v>
+        <v>-10.29000854492188</v>
       </c>
       <c r="AX2">
-        <v>-0.04205101996947336</v>
+        <v>-0.02719706192394389</v>
       </c>
       <c r="AY2">
-        <v>1</v>
-      </c>
-      <c r="BA2">
-        <v>217.229995727539</v>
+        <v>0</v>
       </c>
       <c r="BB2">
         <v>0</v>
       </c>
       <c r="BC2">
-        <v>4</v>
-      </c>
-      <c r="BD2">
-        <v>-18.82499694824222</v>
-      </c>
-      <c r="BE2">
-        <v>-0.07974835327502738</v>
+        <v>0</v>
       </c>
       <c r="BF2">
         <v>0</v>
@@ -2682,7 +2705,7 @@
         <v>1</v>
       </c>
       <c r="BO2">
-        <v>57.15999984741211</v>
+        <v>56.5099983215332</v>
       </c>
       <c r="BP2">
         <v>0</v>
@@ -2691,10 +2714,10 @@
         <v>18</v>
       </c>
       <c r="BR2">
-        <v>4.579999847412111</v>
+        <v>3.929998321533205</v>
       </c>
       <c r="BS2">
-        <v>0.08710536035397709</v>
+        <v>0.07474321646126292</v>
       </c>
       <c r="BT2">
         <v>0</v>
@@ -2727,7 +2750,7 @@
         <v>1</v>
       </c>
       <c r="CQ2">
-        <v>109.8499984741211</v>
+        <v>106.5</v>
       </c>
       <c r="CR2">
         <v>0</v>
@@ -2736,16 +2759,16 @@
         <v>8</v>
       </c>
       <c r="CT2">
-        <v>-6.919998168945312</v>
+        <v>-10.26999664306641</v>
       </c>
       <c r="CU2">
-        <v>-0.05926178271716354</v>
+        <v>-0.08795064604188474</v>
       </c>
       <c r="CV2">
         <v>1</v>
       </c>
       <c r="CX2">
-        <v>978.010009765625</v>
+        <v>995.530029296875</v>
       </c>
       <c r="CY2">
         <v>0</v>
@@ -2754,10 +2777,10 @@
         <v>1</v>
       </c>
       <c r="DA2">
-        <v>33.010009765625</v>
+        <v>50.530029296875</v>
       </c>
       <c r="DB2">
-        <v>0.03493122726521158</v>
+        <v>0.05347093047288354</v>
       </c>
       <c r="DC2">
         <v>0</v>
@@ -2789,26 +2812,17 @@
       <c r="DX2">
         <v>0</v>
       </c>
-      <c r="DZ2">
-        <v>539.6199951171875</v>
-      </c>
       <c r="EA2">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="EB2">
         <v>0</v>
       </c>
-      <c r="EC2">
-        <v>-96.83001708984375</v>
-      </c>
-      <c r="ED2">
-        <v>-0.1521408048278046</v>
-      </c>
       <c r="EE2">
         <v>1</v>
       </c>
       <c r="EG2">
-        <v>279.1199951171875</v>
+        <v>276.1499938964844</v>
       </c>
       <c r="EH2">
         <v>0</v>
@@ -2817,16 +2831,16 @@
         <v>3</v>
       </c>
       <c r="EJ2">
-        <v>-10.8800048828125</v>
+        <v>-13.85000610351562</v>
       </c>
       <c r="EK2">
-        <v>-0.0375172582165948</v>
+        <v>-0.04775864173626077</v>
       </c>
       <c r="EL2">
         <v>1</v>
       </c>
       <c r="EN2">
-        <v>330.1700134277344</v>
+        <v>325.6199951171875</v>
       </c>
       <c r="EO2">
         <v>0</v>
@@ -2835,10 +2849,10 @@
         <v>3</v>
       </c>
       <c r="EQ2">
-        <v>28.57000732421875</v>
+        <v>24.01998901367188</v>
       </c>
       <c r="ER2">
-        <v>0.09472813907839539</v>
+        <v>0.07964187177578408</v>
       </c>
       <c r="ES2">
         <v>0</v>
@@ -2852,26 +2866,17 @@
       <c r="EZ2">
         <v>0</v>
       </c>
-      <c r="FB2">
-        <v>169.3099975585938</v>
-      </c>
       <c r="FC2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="FD2">
         <v>0</v>
       </c>
-      <c r="FE2">
-        <v>-17.07499694824222</v>
-      </c>
-      <c r="FF2">
-        <v>-0.09161143574578889</v>
-      </c>
       <c r="FG2">
         <v>1</v>
       </c>
       <c r="FI2">
-        <v>427.8599853515625</v>
+        <v>433.1799926757813</v>
       </c>
       <c r="FJ2">
         <v>0</v>
@@ -2880,10 +2885,10 @@
         <v>2</v>
       </c>
       <c r="FL2">
-        <v>21.38998413085938</v>
+        <v>26.70999145507818</v>
       </c>
       <c r="FM2">
-        <v>0.05262377067587121</v>
+        <v>0.06571208545492468</v>
       </c>
       <c r="FN2">
         <v>0</v>
@@ -2906,28 +2911,28 @@
     </row>
     <row r="3" spans="1:183">
       <c r="A3" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3">
-        <v>9600.492880668853</v>
+        <v>9462.825070747589</v>
       </c>
       <c r="C3">
-        <v>-2382.287057075287</v>
+        <v>-130.2149454267276</v>
       </c>
       <c r="D3">
-        <v>-450.8538608132935</v>
+        <v>866.1100542358397</v>
       </c>
       <c r="E3">
         <v>10000</v>
       </c>
       <c r="F3">
-        <v>-0.03995071193311472</v>
+        <v>-0.05371749292524108</v>
       </c>
       <c r="G3">
-        <v>-3.674000000000001</v>
+        <v>-0.7797998046875012</v>
       </c>
       <c r="H3">
-        <v>-0.006728937728937732</v>
+        <v>-0.003303466687351735</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -2984,13 +2989,22 @@
         <v>2</v>
       </c>
       <c r="AY3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>216.5599975585937</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="BC3">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>-19.49499511718753</v>
+      </c>
+      <c r="BE3">
+        <v>-0.08258666718379337</v>
       </c>
       <c r="BF3">
         <v>0</v>
@@ -3083,13 +3097,13 @@
         <v>0</v>
       </c>
       <c r="DX3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EA3">
         <v>0</v>
       </c>
       <c r="EB3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EE3">
         <v>1</v>
@@ -3103,11 +3117,8 @@
       <c r="EL3">
         <v>1</v>
       </c>
-      <c r="EM3">
-        <v>-301.6000061035156</v>
-      </c>
       <c r="EO3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="EP3">
         <v>3</v>
@@ -3122,13 +3133,13 @@
         <v>0</v>
       </c>
       <c r="EZ3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FC3">
         <v>0</v>
       </c>
       <c r="FD3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="FG3">
         <v>1</v>
@@ -3151,46 +3162,37 @@
       <c r="FU3">
         <v>0</v>
       </c>
-      <c r="FW3">
-        <v>454.15</v>
-      </c>
       <c r="FX3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="FY3">
         <v>0</v>
-      </c>
-      <c r="FZ3">
-        <v>-91.85000000000002</v>
-      </c>
-      <c r="GA3">
-        <v>-0.1682234432234433</v>
       </c>
     </row>
     <row r="4" spans="1:183">
       <c r="A4" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4">
-        <v>9752.886795803435</v>
+        <v>9589.634938386749</v>
       </c>
       <c r="C4">
-        <v>-1931.433196261994</v>
+        <v>-996.3249996625673</v>
       </c>
       <c r="D4">
-        <v>83.49369374084472</v>
+        <v>1385.96205741272</v>
       </c>
       <c r="E4">
         <v>10000</v>
       </c>
       <c r="F4">
-        <v>-0.02471132041965651</v>
+        <v>-0.04103650616132504</v>
       </c>
       <c r="G4">
-        <v>-0.9851998901367194</v>
+        <v>-4.556200561523439</v>
       </c>
       <c r="H4">
-        <v>-0.007934282875612668</v>
+        <v>-0.009750089622943738</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -3213,11 +3215,8 @@
       <c r="W4">
         <v>1</v>
       </c>
-      <c r="X4">
-        <v>-356.2999877929688</v>
-      </c>
       <c r="Z4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA4">
         <v>2</v>
@@ -3297,20 +3296,11 @@
       <c r="CH4">
         <v>0</v>
       </c>
-      <c r="CJ4">
-        <v>99.54000091552734</v>
-      </c>
       <c r="CK4">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="CL4">
         <v>0</v>
-      </c>
-      <c r="CM4">
-        <v>-24.62999725341798</v>
-      </c>
-      <c r="CN4">
-        <v>-0.1983570718903167</v>
       </c>
       <c r="CO4">
         <v>1</v>
@@ -3358,13 +3348,22 @@
         <v>0</v>
       </c>
       <c r="DX4">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="DZ4">
+        <v>539.6199951171875</v>
       </c>
       <c r="EA4">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="EB4">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="EC4">
+        <v>-96.83001708984375</v>
+      </c>
+      <c r="ED4">
+        <v>-0.1521408048278046</v>
       </c>
       <c r="EE4">
         <v>1</v>
@@ -3376,13 +3375,13 @@
         <v>3</v>
       </c>
       <c r="EL4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EO4">
         <v>0</v>
       </c>
       <c r="EP4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="ES4">
         <v>0</v>
@@ -3394,13 +3393,22 @@
         <v>0</v>
       </c>
       <c r="EZ4">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="FB4">
+        <v>169.3099975585938</v>
       </c>
       <c r="FC4">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="FD4">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="FE4">
+        <v>-17.07499694824222</v>
+      </c>
+      <c r="FF4">
+        <v>-0.09161143574578889</v>
       </c>
       <c r="FG4">
         <v>1</v>
@@ -3421,33 +3429,39 @@
         <v>0</v>
       </c>
       <c r="FU4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FX4">
         <v>0</v>
       </c>
       <c r="FY4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:183">
       <c r="A5" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5">
-        <v>9804.852986706146</v>
+        <v>9600.492880668853</v>
       </c>
       <c r="C5">
-        <v>-2014.926890002838</v>
+        <v>-2382.287057075287</v>
       </c>
       <c r="D5">
-        <v>-3176.771366113281</v>
+        <v>-450.8538608132935</v>
       </c>
       <c r="E5">
         <v>10000</v>
       </c>
       <c r="F5">
-        <v>-0.01951470132938538</v>
+        <v>-0.03995071193311472</v>
+      </c>
+      <c r="G5">
+        <v>-3.674000000000001</v>
+      </c>
+      <c r="H5">
+        <v>-0.006728937728937732</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -3461,32 +3475,26 @@
       <c r="P5">
         <v>1</v>
       </c>
-      <c r="Q5">
-        <v>-528.2349853515625</v>
-      </c>
       <c r="S5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5">
         <v>1</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5">
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD5">
         <v>1</v>
       </c>
-      <c r="AE5">
-        <v>-256.2999877929688</v>
-      </c>
       <c r="AG5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH5">
         <v>3</v>
@@ -3555,22 +3563,19 @@
         <v>0</v>
       </c>
       <c r="CH5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CK5">
         <v>0</v>
       </c>
       <c r="CL5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CO5">
         <v>1</v>
       </c>
-      <c r="CP5">
-        <v>-116.7699966430664</v>
-      </c>
       <c r="CR5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CS5">
         <v>8</v>
@@ -3578,11 +3583,8 @@
       <c r="CV5">
         <v>1</v>
       </c>
-      <c r="CW5">
-        <v>-945</v>
-      </c>
       <c r="CY5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CZ5">
         <v>1</v>
@@ -3633,13 +3635,16 @@
         <v>3</v>
       </c>
       <c r="EL5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="EM5">
+        <v>-301.6000061035156</v>
       </c>
       <c r="EO5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="EP5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="ES5">
         <v>0</v>
@@ -3678,33 +3683,48 @@
         <v>0</v>
       </c>
       <c r="FU5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="FW5">
+        <v>454.15</v>
       </c>
       <c r="FX5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="FY5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="FZ5">
+        <v>-91.85000000000002</v>
+      </c>
+      <c r="GA5">
+        <v>-0.1682234432234433</v>
       </c>
     </row>
     <row r="6" spans="1:183">
       <c r="A6" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6">
-        <v>9904.144532567963</v>
+        <v>9752.886795803435</v>
       </c>
       <c r="C6">
-        <v>1161.844476110443</v>
+        <v>-1931.433196261994</v>
       </c>
       <c r="D6">
-        <v>-756.8135172088623</v>
+        <v>83.49369374084472</v>
       </c>
       <c r="E6">
         <v>10000</v>
       </c>
       <c r="F6">
-        <v>-0.009585546743203666</v>
+        <v>-0.02471132041965651</v>
+      </c>
+      <c r="G6">
+        <v>-0.9851998901367194</v>
+      </c>
+      <c r="H6">
+        <v>-0.007934282875612668</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -3716,31 +3736,34 @@
         <v>2</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>-356.2999877929688</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6">
         <v>0</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK6">
         <v>1</v>
@@ -3754,11 +3777,8 @@
       <c r="AR6">
         <v>1</v>
       </c>
-      <c r="AS6">
-        <v>-378.3500061035156</v>
-      </c>
       <c r="AU6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV6">
         <v>2</v>
@@ -3809,31 +3829,40 @@
         <v>0</v>
       </c>
       <c r="CH6">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="CJ6">
+        <v>99.54000091552734</v>
       </c>
       <c r="CK6">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="CL6">
+        <v>0</v>
+      </c>
+      <c r="CM6">
+        <v>-24.62999725341798</v>
+      </c>
+      <c r="CN6">
+        <v>-0.1983570718903167</v>
+      </c>
+      <c r="CO6">
+        <v>1</v>
+      </c>
+      <c r="CR6">
+        <v>0</v>
+      </c>
+      <c r="CS6">
         <v>8</v>
       </c>
-      <c r="CO6">
-        <v>0</v>
-      </c>
-      <c r="CR6">
-        <v>0</v>
-      </c>
-      <c r="CS6">
-        <v>0</v>
-      </c>
       <c r="CV6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY6">
         <v>0</v>
       </c>
       <c r="CZ6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC6">
         <v>0</v>
@@ -3937,22 +3966,22 @@
     </row>
     <row r="7" spans="1:183">
       <c r="A7" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7">
-        <v>9950.788089754853</v>
+        <v>9804.852986706146</v>
       </c>
       <c r="C7">
-        <v>1918.657993319305</v>
+        <v>-2014.926890002838</v>
       </c>
       <c r="D7">
-        <v>-546.0819</v>
+        <v>-3176.771366113281</v>
       </c>
       <c r="E7">
         <v>10000</v>
       </c>
       <c r="F7">
-        <v>-0.004921191024514715</v>
+        <v>-0.01951470132938538</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -3964,13 +3993,16 @@
         <v>2</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>-528.2349853515625</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7">
         <v>0</v>
@@ -3982,13 +4014,16 @@
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AE7">
+        <v>-256.2999877929688</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK7">
         <v>1</v>
@@ -4000,13 +4035,13 @@
         <v>1</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU7">
         <v>0</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY7">
         <v>1</v>
@@ -4063,22 +4098,28 @@
         <v>8</v>
       </c>
       <c r="CO7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CP7">
+        <v>-116.7699966430664</v>
       </c>
       <c r="CR7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CS7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CV7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CW7">
+        <v>-945</v>
       </c>
       <c r="CY7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CZ7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC7">
         <v>0</v>
@@ -4173,11 +4214,8 @@
       <c r="FU7">
         <v>1</v>
       </c>
-      <c r="FV7">
-        <v>-546</v>
-      </c>
       <c r="FX7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FY7">
         <v>1</v>
@@ -4185,31 +4223,28 @@
     </row>
     <row r="8" spans="1:183">
       <c r="A8" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8">
-        <v>9970.279909493622</v>
+        <v>9904.144532567963</v>
       </c>
       <c r="C8">
-        <v>2464.739893319305</v>
+        <v>1161.844476110443</v>
       </c>
       <c r="D8">
-        <v>-1612.271831359497</v>
+        <v>-756.8135172088623</v>
       </c>
       <c r="E8">
         <v>10000</v>
       </c>
       <c r="F8">
-        <v>-0.00297200905063788</v>
+        <v>-0.009585546743203666</v>
       </c>
       <c r="I8">
         <v>1</v>
       </c>
-      <c r="J8">
-        <v>-332.7950134277344</v>
-      </c>
       <c r="L8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <v>2</v>
@@ -4251,13 +4286,16 @@
         <v>1</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AS8">
+        <v>-378.3500061035156</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY8">
         <v>1</v>
@@ -4280,11 +4318,8 @@
       <c r="BM8">
         <v>1</v>
       </c>
-      <c r="BN8">
-        <v>-52.58</v>
-      </c>
       <c r="BP8">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BQ8">
         <v>18</v>
@@ -4425,42 +4460,42 @@
         <v>0</v>
       </c>
       <c r="FU8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FX8">
         <v>0</v>
       </c>
       <c r="FY8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:183">
       <c r="A9" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9">
-        <v>9919.091680733491</v>
+        <v>9950.788089754853</v>
       </c>
       <c r="C9">
-        <v>4077.011724678802</v>
+        <v>1918.657993319305</v>
       </c>
       <c r="D9">
-        <v>-5922.988275321198</v>
+        <v>-546.0819</v>
       </c>
       <c r="E9">
         <v>10000</v>
       </c>
       <c r="F9">
-        <v>-0.008090831926650943</v>
+        <v>-0.004921191024514715</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -4492,11 +4527,8 @@
       <c r="AK9">
         <v>1</v>
       </c>
-      <c r="AL9">
-        <v>-733.2050170898438</v>
-      </c>
       <c r="AN9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO9">
         <v>1</v>
@@ -4513,11 +4545,8 @@
       <c r="AY9">
         <v>1</v>
       </c>
-      <c r="AZ9">
-        <v>-236.0549926757812</v>
-      </c>
       <c r="BB9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BC9">
         <v>4</v>
@@ -4532,13 +4561,13 @@
         <v>0</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP9">
         <v>0</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BT9">
         <v>0</v>
@@ -4561,11 +4590,8 @@
       <c r="CH9">
         <v>1</v>
       </c>
-      <c r="CI9">
-        <v>-124.1699981689453</v>
-      </c>
       <c r="CK9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CL9">
         <v>8</v>
@@ -4618,11 +4644,8 @@
       <c r="DX9">
         <v>1</v>
       </c>
-      <c r="DY9">
-        <v>-636.4500122070312</v>
-      </c>
       <c r="EA9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB9">
         <v>1</v>
@@ -4630,11 +4653,8 @@
       <c r="EE9">
         <v>1</v>
       </c>
-      <c r="EF9">
-        <v>-290</v>
-      </c>
       <c r="EH9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="EI9">
         <v>3</v>
@@ -4660,11 +4680,8 @@
       <c r="EZ9">
         <v>1</v>
       </c>
-      <c r="FA9">
-        <v>-186.384994506836</v>
-      </c>
       <c r="FC9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="FD9">
         <v>5</v>
@@ -4672,11 +4689,8 @@
       <c r="FG9">
         <v>1</v>
       </c>
-      <c r="FH9">
-        <v>-406.4700012207031</v>
-      </c>
       <c r="FJ9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="FK9">
         <v>2</v>
@@ -4691,42 +4705,48 @@
         <v>0</v>
       </c>
       <c r="FU9">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FV9">
+        <v>-546</v>
       </c>
       <c r="FX9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FY9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:183">
       <c r="A10" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10">
-        <v>10000</v>
+        <v>9970.279909493622</v>
       </c>
       <c r="C10">
-        <v>10000</v>
+        <v>2464.739893319305</v>
       </c>
       <c r="D10">
-        <v>10000</v>
+        <v>-1612.271831359497</v>
       </c>
       <c r="E10">
         <v>10000</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>-0.00297200905063788</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>-332.7950134277344</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -4756,13 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN10">
         <v>0</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -4774,13 +4794,13 @@
         <v>0</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB10">
         <v>0</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF10">
         <v>0</v>
@@ -4792,13 +4812,16 @@
         <v>0</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BN10">
+        <v>-52.58</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BT10">
         <v>0</v>
@@ -4819,13 +4842,13 @@
         <v>0</v>
       </c>
       <c r="CH10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CK10">
         <v>0</v>
       </c>
       <c r="CL10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CO10">
         <v>0</v>
@@ -4873,22 +4896,22 @@
         <v>0</v>
       </c>
       <c r="DX10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EA10">
         <v>0</v>
       </c>
       <c r="EB10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EE10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EH10">
         <v>0</v>
       </c>
       <c r="EI10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="EL10">
         <v>0</v>
@@ -4909,22 +4932,22 @@
         <v>0</v>
       </c>
       <c r="EZ10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FC10">
         <v>0</v>
       </c>
       <c r="FD10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="FG10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FJ10">
         <v>0</v>
       </c>
       <c r="FK10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="FN10">
         <v>0</v>
@@ -4942,11 +4965,522 @@
         <v>0</v>
       </c>
       <c r="FY10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:183">
+      <c r="A11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <v>9919.091680733491</v>
+      </c>
+      <c r="C11">
+        <v>4077.011724678802</v>
+      </c>
+      <c r="D11">
+        <v>-5922.988275321198</v>
+      </c>
+      <c r="E11">
+        <v>10000</v>
+      </c>
+      <c r="F11">
+        <v>-0.008090831926650943</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>1</v>
+      </c>
+      <c r="AL11">
+        <v>-733.2050170898438</v>
+      </c>
+      <c r="AN11">
+        <v>1</v>
+      </c>
+      <c r="AO11">
+        <v>1</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>1</v>
+      </c>
+      <c r="AZ11">
+        <v>-236.0549926757812</v>
+      </c>
+      <c r="BB11">
+        <v>4</v>
+      </c>
+      <c r="BC11">
+        <v>4</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CD11">
+        <v>0</v>
+      </c>
+      <c r="CE11">
+        <v>0</v>
+      </c>
+      <c r="CH11">
+        <v>1</v>
+      </c>
+      <c r="CI11">
+        <v>-124.1699981689453</v>
+      </c>
+      <c r="CK11">
+        <v>8</v>
+      </c>
+      <c r="CL11">
+        <v>8</v>
+      </c>
+      <c r="CO11">
+        <v>0</v>
+      </c>
+      <c r="CR11">
+        <v>0</v>
+      </c>
+      <c r="CS11">
+        <v>0</v>
+      </c>
+      <c r="CV11">
+        <v>0</v>
+      </c>
+      <c r="CY11">
+        <v>0</v>
+      </c>
+      <c r="CZ11">
+        <v>0</v>
+      </c>
+      <c r="DC11">
+        <v>0</v>
+      </c>
+      <c r="DF11">
+        <v>0</v>
+      </c>
+      <c r="DG11">
+        <v>0</v>
+      </c>
+      <c r="DJ11">
+        <v>0</v>
+      </c>
+      <c r="DM11">
+        <v>0</v>
+      </c>
+      <c r="DN11">
+        <v>0</v>
+      </c>
+      <c r="DQ11">
+        <v>0</v>
+      </c>
+      <c r="DT11">
+        <v>0</v>
+      </c>
+      <c r="DU11">
+        <v>0</v>
+      </c>
+      <c r="DX11">
+        <v>1</v>
+      </c>
+      <c r="DY11">
+        <v>-636.4500122070312</v>
+      </c>
+      <c r="EA11">
+        <v>1</v>
+      </c>
+      <c r="EB11">
+        <v>1</v>
+      </c>
+      <c r="EE11">
+        <v>1</v>
+      </c>
+      <c r="EF11">
+        <v>-290</v>
+      </c>
+      <c r="EH11">
+        <v>3</v>
+      </c>
+      <c r="EI11">
+        <v>3</v>
+      </c>
+      <c r="EL11">
+        <v>0</v>
+      </c>
+      <c r="EO11">
+        <v>0</v>
+      </c>
+      <c r="EP11">
+        <v>0</v>
+      </c>
+      <c r="ES11">
+        <v>0</v>
+      </c>
+      <c r="EV11">
+        <v>0</v>
+      </c>
+      <c r="EW11">
+        <v>0</v>
+      </c>
+      <c r="EZ11">
+        <v>1</v>
+      </c>
+      <c r="FA11">
+        <v>-186.384994506836</v>
+      </c>
+      <c r="FC11">
+        <v>5</v>
+      </c>
+      <c r="FD11">
+        <v>5</v>
+      </c>
+      <c r="FG11">
+        <v>1</v>
+      </c>
+      <c r="FH11">
+        <v>-406.4700012207031</v>
+      </c>
+      <c r="FJ11">
+        <v>2</v>
+      </c>
+      <c r="FK11">
+        <v>2</v>
+      </c>
+      <c r="FN11">
+        <v>0</v>
+      </c>
+      <c r="FQ11">
+        <v>0</v>
+      </c>
+      <c r="FR11">
+        <v>0</v>
+      </c>
+      <c r="FU11">
+        <v>0</v>
+      </c>
+      <c r="FX11">
+        <v>0</v>
+      </c>
+      <c r="FY11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:183">
+      <c r="A12" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12">
+        <v>10000</v>
+      </c>
+      <c r="C12">
+        <v>10000</v>
+      </c>
+      <c r="D12">
+        <v>10000</v>
+      </c>
+      <c r="E12">
+        <v>10000</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CD12">
+        <v>0</v>
+      </c>
+      <c r="CE12">
+        <v>0</v>
+      </c>
+      <c r="CH12">
+        <v>0</v>
+      </c>
+      <c r="CK12">
+        <v>0</v>
+      </c>
+      <c r="CL12">
+        <v>0</v>
+      </c>
+      <c r="CO12">
+        <v>0</v>
+      </c>
+      <c r="CR12">
+        <v>0</v>
+      </c>
+      <c r="CS12">
+        <v>0</v>
+      </c>
+      <c r="CV12">
+        <v>0</v>
+      </c>
+      <c r="CY12">
+        <v>0</v>
+      </c>
+      <c r="CZ12">
+        <v>0</v>
+      </c>
+      <c r="DC12">
+        <v>0</v>
+      </c>
+      <c r="DF12">
+        <v>0</v>
+      </c>
+      <c r="DG12">
+        <v>0</v>
+      </c>
+      <c r="DJ12">
+        <v>0</v>
+      </c>
+      <c r="DM12">
+        <v>0</v>
+      </c>
+      <c r="DN12">
+        <v>0</v>
+      </c>
+      <c r="DQ12">
+        <v>0</v>
+      </c>
+      <c r="DT12">
+        <v>0</v>
+      </c>
+      <c r="DU12">
+        <v>0</v>
+      </c>
+      <c r="DX12">
+        <v>0</v>
+      </c>
+      <c r="EA12">
+        <v>0</v>
+      </c>
+      <c r="EB12">
+        <v>0</v>
+      </c>
+      <c r="EE12">
+        <v>0</v>
+      </c>
+      <c r="EH12">
+        <v>0</v>
+      </c>
+      <c r="EI12">
+        <v>0</v>
+      </c>
+      <c r="EL12">
+        <v>0</v>
+      </c>
+      <c r="EO12">
+        <v>0</v>
+      </c>
+      <c r="EP12">
+        <v>0</v>
+      </c>
+      <c r="ES12">
+        <v>0</v>
+      </c>
+      <c r="EV12">
+        <v>0</v>
+      </c>
+      <c r="EW12">
+        <v>0</v>
+      </c>
+      <c r="EZ12">
+        <v>0</v>
+      </c>
+      <c r="FC12">
+        <v>0</v>
+      </c>
+      <c r="FD12">
+        <v>0</v>
+      </c>
+      <c r="FG12">
+        <v>0</v>
+      </c>
+      <c r="FJ12">
+        <v>0</v>
+      </c>
+      <c r="FK12">
+        <v>0</v>
+      </c>
+      <c r="FN12">
+        <v>0</v>
+      </c>
+      <c r="FQ12">
+        <v>0</v>
+      </c>
+      <c r="FR12">
+        <v>0</v>
+      </c>
+      <c r="FU12">
+        <v>0</v>
+      </c>
+      <c r="FX12">
+        <v>0</v>
+      </c>
+      <c r="FY12">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AA2:AA10">
+  <conditionalFormatting sqref="AA2:AA12">
     <cfRule type="cellIs" dxfId="4" priority="25" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4954,7 +5488,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE2:AE10">
+  <conditionalFormatting sqref="AE2:AE12">
     <cfRule type="cellIs" dxfId="4" priority="27" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4962,7 +5496,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF2:AF10">
+  <conditionalFormatting sqref="AF2:AF12">
     <cfRule type="cellIs" dxfId="4" priority="29" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4970,7 +5504,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG2:AG10">
+  <conditionalFormatting sqref="AG2:AG12">
     <cfRule type="cellIs" dxfId="4" priority="31" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4978,7 +5512,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH2:AH10">
+  <conditionalFormatting sqref="AH2:AH12">
     <cfRule type="cellIs" dxfId="4" priority="33" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4986,7 +5520,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL2:AL10">
+  <conditionalFormatting sqref="AL2:AL12">
     <cfRule type="cellIs" dxfId="4" priority="35" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4994,7 +5528,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM2:AM10">
+  <conditionalFormatting sqref="AM2:AM12">
     <cfRule type="cellIs" dxfId="4" priority="37" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5002,7 +5536,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AN2:AN10">
+  <conditionalFormatting sqref="AN2:AN12">
     <cfRule type="cellIs" dxfId="4" priority="39" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5010,7 +5544,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AO2:AO10">
+  <conditionalFormatting sqref="AO2:AO12">
     <cfRule type="cellIs" dxfId="4" priority="41" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5018,7 +5552,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AS2:AS10">
+  <conditionalFormatting sqref="AS2:AS12">
     <cfRule type="cellIs" dxfId="4" priority="43" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5026,7 +5560,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AT2:AT10">
+  <conditionalFormatting sqref="AT2:AT12">
     <cfRule type="cellIs" dxfId="4" priority="45" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5034,7 +5568,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU2:AU10">
+  <conditionalFormatting sqref="AU2:AU12">
     <cfRule type="cellIs" dxfId="4" priority="47" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5042,7 +5576,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AV2:AV10">
+  <conditionalFormatting sqref="AV2:AV12">
     <cfRule type="cellIs" dxfId="4" priority="49" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5050,7 +5584,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AZ2:AZ10">
+  <conditionalFormatting sqref="AZ2:AZ12">
     <cfRule type="cellIs" dxfId="4" priority="51" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5058,7 +5592,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BA2:BA10">
+  <conditionalFormatting sqref="BA2:BA12">
     <cfRule type="cellIs" dxfId="4" priority="53" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5066,7 +5600,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB2:BB10">
+  <conditionalFormatting sqref="BB2:BB12">
     <cfRule type="cellIs" dxfId="4" priority="55" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5074,7 +5608,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BC2:BC10">
+  <conditionalFormatting sqref="BC2:BC12">
     <cfRule type="cellIs" dxfId="4" priority="57" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5082,7 +5616,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BG2:BG10">
+  <conditionalFormatting sqref="BG2:BG12">
     <cfRule type="cellIs" dxfId="4" priority="59" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5090,7 +5624,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BH2:BH10">
+  <conditionalFormatting sqref="BH2:BH12">
     <cfRule type="cellIs" dxfId="4" priority="61" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5098,7 +5632,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BI2:BI10">
+  <conditionalFormatting sqref="BI2:BI12">
     <cfRule type="cellIs" dxfId="4" priority="63" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5106,7 +5640,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BJ2:BJ10">
+  <conditionalFormatting sqref="BJ2:BJ12">
     <cfRule type="cellIs" dxfId="4" priority="65" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5114,7 +5648,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BN2:BN10">
+  <conditionalFormatting sqref="BN2:BN12">
     <cfRule type="cellIs" dxfId="4" priority="67" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5122,7 +5656,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BO2:BO10">
+  <conditionalFormatting sqref="BO2:BO12">
     <cfRule type="cellIs" dxfId="4" priority="69" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5130,7 +5664,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BP2:BP10">
+  <conditionalFormatting sqref="BP2:BP12">
     <cfRule type="cellIs" dxfId="4" priority="71" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5138,7 +5672,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BQ2:BQ10">
+  <conditionalFormatting sqref="BQ2:BQ12">
     <cfRule type="cellIs" dxfId="4" priority="73" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5146,7 +5680,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BU2:BU10">
+  <conditionalFormatting sqref="BU2:BU12">
     <cfRule type="cellIs" dxfId="4" priority="75" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5154,7 +5688,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BV2:BV10">
+  <conditionalFormatting sqref="BV2:BV12">
     <cfRule type="cellIs" dxfId="4" priority="77" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5162,7 +5696,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BW2:BW10">
+  <conditionalFormatting sqref="BW2:BW12">
     <cfRule type="cellIs" dxfId="4" priority="79" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5170,7 +5704,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BX2:BX10">
+  <conditionalFormatting sqref="BX2:BX12">
     <cfRule type="cellIs" dxfId="4" priority="81" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5178,7 +5712,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CB2:CB10">
+  <conditionalFormatting sqref="CB2:CB12">
     <cfRule type="cellIs" dxfId="4" priority="83" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5186,7 +5720,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CC2:CC10">
+  <conditionalFormatting sqref="CC2:CC12">
     <cfRule type="cellIs" dxfId="4" priority="85" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5194,7 +5728,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CD2:CD10">
+  <conditionalFormatting sqref="CD2:CD12">
     <cfRule type="cellIs" dxfId="4" priority="87" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5202,7 +5736,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CE2:CE10">
+  <conditionalFormatting sqref="CE2:CE12">
     <cfRule type="cellIs" dxfId="4" priority="89" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5210,7 +5744,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CI2:CI10">
+  <conditionalFormatting sqref="CI2:CI12">
     <cfRule type="cellIs" dxfId="4" priority="91" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5218,7 +5752,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CJ2:CJ10">
+  <conditionalFormatting sqref="CJ2:CJ12">
     <cfRule type="cellIs" dxfId="4" priority="93" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5226,7 +5760,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CK2:CK10">
+  <conditionalFormatting sqref="CK2:CK12">
     <cfRule type="cellIs" dxfId="4" priority="95" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5234,7 +5768,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CL2:CL10">
+  <conditionalFormatting sqref="CL2:CL12">
     <cfRule type="cellIs" dxfId="4" priority="97" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5242,7 +5776,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CP2:CP10">
+  <conditionalFormatting sqref="CP2:CP12">
     <cfRule type="cellIs" dxfId="4" priority="99" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5250,7 +5784,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CQ2:CQ10">
+  <conditionalFormatting sqref="CQ2:CQ12">
     <cfRule type="cellIs" dxfId="4" priority="101" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5258,7 +5792,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CR2:CR10">
+  <conditionalFormatting sqref="CR2:CR12">
     <cfRule type="cellIs" dxfId="4" priority="103" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5266,7 +5800,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CS2:CS10">
+  <conditionalFormatting sqref="CS2:CS12">
     <cfRule type="cellIs" dxfId="4" priority="105" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5274,7 +5808,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CW2:CW10">
+  <conditionalFormatting sqref="CW2:CW12">
     <cfRule type="cellIs" dxfId="4" priority="107" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5282,7 +5816,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CX2:CX10">
+  <conditionalFormatting sqref="CX2:CX12">
     <cfRule type="cellIs" dxfId="4" priority="109" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5290,7 +5824,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CY2:CY10">
+  <conditionalFormatting sqref="CY2:CY12">
     <cfRule type="cellIs" dxfId="4" priority="111" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5298,7 +5832,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CZ2:CZ10">
+  <conditionalFormatting sqref="CZ2:CZ12">
     <cfRule type="cellIs" dxfId="4" priority="113" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5306,7 +5840,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D10">
+  <conditionalFormatting sqref="D2:D12">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5314,7 +5848,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DD2:DD10">
+  <conditionalFormatting sqref="DD2:DD12">
     <cfRule type="cellIs" dxfId="4" priority="115" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5322,7 +5856,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DE2:DE10">
+  <conditionalFormatting sqref="DE2:DE12">
     <cfRule type="cellIs" dxfId="4" priority="117" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5330,7 +5864,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DF2:DF10">
+  <conditionalFormatting sqref="DF2:DF12">
     <cfRule type="cellIs" dxfId="4" priority="119" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5338,7 +5872,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DG2:DG10">
+  <conditionalFormatting sqref="DG2:DG12">
     <cfRule type="cellIs" dxfId="4" priority="121" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5346,7 +5880,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DK2:DK10">
+  <conditionalFormatting sqref="DK2:DK12">
     <cfRule type="cellIs" dxfId="4" priority="123" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5354,7 +5888,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DL2:DL10">
+  <conditionalFormatting sqref="DL2:DL12">
     <cfRule type="cellIs" dxfId="4" priority="125" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5362,7 +5896,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DM2:DM10">
+  <conditionalFormatting sqref="DM2:DM12">
     <cfRule type="cellIs" dxfId="4" priority="127" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5370,7 +5904,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DN2:DN10">
+  <conditionalFormatting sqref="DN2:DN12">
     <cfRule type="cellIs" dxfId="4" priority="129" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5378,7 +5912,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DR2:DR10">
+  <conditionalFormatting sqref="DR2:DR12">
     <cfRule type="cellIs" dxfId="4" priority="131" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5386,7 +5920,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DS2:DS10">
+  <conditionalFormatting sqref="DS2:DS12">
     <cfRule type="cellIs" dxfId="4" priority="133" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5394,7 +5928,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DT2:DT10">
+  <conditionalFormatting sqref="DT2:DT12">
     <cfRule type="cellIs" dxfId="4" priority="135" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5402,7 +5936,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DU2:DU10">
+  <conditionalFormatting sqref="DU2:DU12">
     <cfRule type="cellIs" dxfId="4" priority="137" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5410,7 +5944,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DY2:DY10">
+  <conditionalFormatting sqref="DY2:DY12">
     <cfRule type="cellIs" dxfId="4" priority="139" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5418,7 +5952,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DZ2:DZ10">
+  <conditionalFormatting sqref="DZ2:DZ12">
     <cfRule type="cellIs" dxfId="4" priority="141" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5426,7 +5960,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EA2:EA10">
+  <conditionalFormatting sqref="EA2:EA12">
     <cfRule type="cellIs" dxfId="4" priority="143" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5434,7 +5968,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EB2:EB10">
+  <conditionalFormatting sqref="EB2:EB12">
     <cfRule type="cellIs" dxfId="4" priority="145" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5442,7 +5976,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EF2:EF10">
+  <conditionalFormatting sqref="EF2:EF12">
     <cfRule type="cellIs" dxfId="4" priority="147" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5450,7 +5984,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EG2:EG10">
+  <conditionalFormatting sqref="EG2:EG12">
     <cfRule type="cellIs" dxfId="4" priority="149" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5458,7 +5992,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EH2:EH10">
+  <conditionalFormatting sqref="EH2:EH12">
     <cfRule type="cellIs" dxfId="4" priority="151" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5466,7 +6000,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EI2:EI10">
+  <conditionalFormatting sqref="EI2:EI12">
     <cfRule type="cellIs" dxfId="4" priority="153" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5474,7 +6008,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EM2:EM10">
+  <conditionalFormatting sqref="EM2:EM12">
     <cfRule type="cellIs" dxfId="4" priority="155" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5482,7 +6016,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EN2:EN10">
+  <conditionalFormatting sqref="EN2:EN12">
     <cfRule type="cellIs" dxfId="4" priority="157" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5490,7 +6024,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EO2:EO10">
+  <conditionalFormatting sqref="EO2:EO12">
     <cfRule type="cellIs" dxfId="4" priority="159" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5498,7 +6032,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EP2:EP10">
+  <conditionalFormatting sqref="EP2:EP12">
     <cfRule type="cellIs" dxfId="4" priority="161" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5506,7 +6040,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="ET2:ET10">
+  <conditionalFormatting sqref="ET2:ET12">
     <cfRule type="cellIs" dxfId="4" priority="163" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5514,7 +6048,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EU2:EU10">
+  <conditionalFormatting sqref="EU2:EU12">
     <cfRule type="cellIs" dxfId="4" priority="165" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5522,7 +6056,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EV2:EV10">
+  <conditionalFormatting sqref="EV2:EV12">
     <cfRule type="cellIs" dxfId="4" priority="167" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5530,7 +6064,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EW2:EW10">
+  <conditionalFormatting sqref="EW2:EW12">
     <cfRule type="cellIs" dxfId="4" priority="169" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5538,7 +6072,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FA2:FA10">
+  <conditionalFormatting sqref="FA2:FA12">
     <cfRule type="cellIs" dxfId="4" priority="171" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5546,7 +6080,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FB2:FB10">
+  <conditionalFormatting sqref="FB2:FB12">
     <cfRule type="cellIs" dxfId="4" priority="173" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5554,7 +6088,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FC2:FC10">
+  <conditionalFormatting sqref="FC2:FC12">
     <cfRule type="cellIs" dxfId="4" priority="175" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5562,7 +6096,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FD2:FD10">
+  <conditionalFormatting sqref="FD2:FD12">
     <cfRule type="cellIs" dxfId="4" priority="177" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5570,7 +6104,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FH2:FH10">
+  <conditionalFormatting sqref="FH2:FH12">
     <cfRule type="cellIs" dxfId="4" priority="179" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5578,7 +6112,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FI2:FI10">
+  <conditionalFormatting sqref="FI2:FI12">
     <cfRule type="cellIs" dxfId="4" priority="181" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5586,7 +6120,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FJ2:FJ10">
+  <conditionalFormatting sqref="FJ2:FJ12">
     <cfRule type="cellIs" dxfId="4" priority="183" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5594,7 +6128,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FK2:FK10">
+  <conditionalFormatting sqref="FK2:FK12">
     <cfRule type="cellIs" dxfId="4" priority="185" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5602,7 +6136,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FO2:FO10">
+  <conditionalFormatting sqref="FO2:FO12">
     <cfRule type="cellIs" dxfId="4" priority="187" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5610,7 +6144,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FP2:FP10">
+  <conditionalFormatting sqref="FP2:FP12">
     <cfRule type="cellIs" dxfId="4" priority="189" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5618,7 +6152,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FQ2:FQ10">
+  <conditionalFormatting sqref="FQ2:FQ12">
     <cfRule type="cellIs" dxfId="4" priority="191" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5626,7 +6160,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FR2:FR10">
+  <conditionalFormatting sqref="FR2:FR12">
     <cfRule type="cellIs" dxfId="4" priority="193" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5634,7 +6168,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FV2:FV10">
+  <conditionalFormatting sqref="FV2:FV12">
     <cfRule type="cellIs" dxfId="4" priority="195" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5642,7 +6176,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FW2:FW10">
+  <conditionalFormatting sqref="FW2:FW12">
     <cfRule type="cellIs" dxfId="4" priority="197" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5650,7 +6184,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FX2:FX10">
+  <conditionalFormatting sqref="FX2:FX12">
     <cfRule type="cellIs" dxfId="4" priority="199" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5658,7 +6192,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FY2:FY10">
+  <conditionalFormatting sqref="FY2:FY12">
     <cfRule type="cellIs" dxfId="4" priority="201" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5666,7 +6200,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J10">
+  <conditionalFormatting sqref="J2:J12">
     <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5674,7 +6208,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K10">
+  <conditionalFormatting sqref="K2:K12">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5682,7 +6216,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L10">
+  <conditionalFormatting sqref="L2:L12">
     <cfRule type="cellIs" dxfId="4" priority="7" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5690,7 +6224,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M10">
+  <conditionalFormatting sqref="M2:M12">
     <cfRule type="cellIs" dxfId="4" priority="9" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5698,7 +6232,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q10">
+  <conditionalFormatting sqref="Q2:Q12">
     <cfRule type="cellIs" dxfId="4" priority="11" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5706,7 +6240,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R10">
+  <conditionalFormatting sqref="R2:R12">
     <cfRule type="cellIs" dxfId="4" priority="13" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5714,7 +6248,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S10">
+  <conditionalFormatting sqref="S2:S12">
     <cfRule type="cellIs" dxfId="4" priority="15" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5722,7 +6256,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T10">
+  <conditionalFormatting sqref="T2:T12">
     <cfRule type="cellIs" dxfId="4" priority="17" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5730,7 +6264,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X10">
+  <conditionalFormatting sqref="X2:X12">
     <cfRule type="cellIs" dxfId="4" priority="19" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5738,7 +6272,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y10">
+  <conditionalFormatting sqref="Y2:Y12">
     <cfRule type="cellIs" dxfId="4" priority="21" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5746,7 +6280,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:Z10">
+  <conditionalFormatting sqref="Z2:Z12">
     <cfRule type="cellIs" dxfId="4" priority="23" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>

--- a/reports/paper_trade_trx.xlsx
+++ b/reports/paper_trade_trx.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="256">
   <si>
     <t>NAV</t>
   </si>
@@ -36,7 +36,7 @@
     <t>last_updated</t>
   </si>
   <si>
-    <t>2026-10-19 18:03:42</t>
+    <t>2026-10-22 18:02:15</t>
   </si>
   <si>
     <t>pf_id</t>
@@ -69,6 +69,12 @@
     <t>date</t>
   </si>
   <si>
+    <t>2026-10-22</t>
+  </si>
+  <si>
+    <t>2026-10-20</t>
+  </si>
+  <si>
     <t>2026-10-16</t>
   </si>
   <si>
@@ -99,6 +105,15 @@
     <t>2026-09-29</t>
   </si>
   <si>
+    <t>CSCO</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
     <t>NVDA</t>
   </si>
   <si>
@@ -117,21 +132,15 @@
     <t>INTC</t>
   </si>
   <si>
-    <t>GOOGL</t>
+    <t>COST</t>
+  </si>
+  <si>
+    <t>AMZN</t>
   </si>
   <si>
     <t>MSFT</t>
   </si>
   <si>
-    <t>COST</t>
-  </si>
-  <si>
-    <t>CSCO</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
     <t>TSLA</t>
   </si>
   <si>
@@ -156,6 +165,15 @@
     <t>initial</t>
   </si>
   <si>
+    <t>2026-10-22_39469eef04d845891f293927079fe206</t>
+  </si>
+  <si>
+    <t>2026-10-22_b4f11f7f10892df97eb691c23dee7b86</t>
+  </si>
+  <si>
+    <t>2026-10-20_b0da2c9c51943c794154c51c7152811f</t>
+  </si>
+  <si>
     <t>2026-10-16_5989af14de8535428a112c8e80fa9e27</t>
   </si>
   <si>
@@ -177,18 +195,18 @@
     <t>2026-10-13_572bd3499a20b8e64a30af391461ef95</t>
   </si>
   <si>
+    <t>2026-10-09_a65360c396f5991e9fa841dde59b8684</t>
+  </si>
+  <si>
+    <t>2026-10-09_cbfa34b7b92b8c9ddd53b2ba7394c363</t>
+  </si>
+  <si>
+    <t>2026-10-09_603d3f285d1e0ad7f8d04d423ef9ecc5</t>
+  </si>
+  <si>
     <t>2026-10-09_4c574a6fffe0157d7c23fe8d2682dfb9</t>
   </si>
   <si>
-    <t>2026-10-09_cbfa34b7b92b8c9ddd53b2ba7394c363</t>
-  </si>
-  <si>
-    <t>2026-10-09_a65360c396f5991e9fa841dde59b8684</t>
-  </si>
-  <si>
-    <t>2026-10-09_603d3f285d1e0ad7f8d04d423ef9ecc5</t>
-  </si>
-  <si>
     <t>2026-10-07_dc7e32e4c69a2eb8b2d77f7cc32b45cf</t>
   </si>
   <si>
@@ -766,9 +784,6 @@
   </si>
   <si>
     <t>Date</t>
-  </si>
-  <si>
-    <t>2026-10-19</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1308,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>9543</v>
+        <v>9649</v>
       </c>
       <c r="C2" s="2">
         <v>100</v>
@@ -1317,7 +1332,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1">
-        <v>9543</v>
+        <v>9649</v>
       </c>
       <c r="C4" s="2">
         <v>100</v>
@@ -1388,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
@@ -1434,42 +1449,42 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F2">
-        <v>216.5599975585937</v>
+        <v>105.7399978637695</v>
       </c>
       <c r="G2">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="H2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>169.3099975585938</v>
+        <v>330.2049865722656</v>
       </c>
       <c r="G3">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1480,19 +1495,19 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4">
-        <v>539.6199951171875</v>
+        <v>31</v>
+      </c>
+      <c r="E4">
+        <v>-249.8300018310547</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1503,42 +1518,42 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>454.15</v>
+        <v>216.5599975585937</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="H5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6">
-        <v>-301.6000061035156</v>
+        <v>33</v>
+      </c>
+      <c r="F6">
+        <v>169.3099975585938</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="H6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1549,42 +1564,42 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F7">
-        <v>99.54000091552734</v>
+        <v>539.6199951171875</v>
       </c>
       <c r="G7">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8">
-        <v>-356.2999877929688</v>
+        <v>35</v>
+      </c>
+      <c r="F8">
+        <v>454.15</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="H8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1595,93 +1610,93 @@
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E9">
-        <v>-528.2349853515625</v>
+        <v>-301.6000061035156</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10">
-        <v>-945</v>
+        <v>37</v>
+      </c>
+      <c r="F10">
+        <v>99.54000091552734</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="H10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E11">
-        <v>-116.7699966430664</v>
+        <v>-356.2999877929688</v>
       </c>
       <c r="G11">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E12">
-        <v>-256.2999877929688</v>
+        <v>-116.7699966430664</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H12" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
@@ -1690,16 +1705,16 @@
         <v>38</v>
       </c>
       <c r="E13">
-        <v>-378.3500061035156</v>
+        <v>-945</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1710,42 +1725,42 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E14">
-        <v>-546</v>
+        <v>-256.2999877929688</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E15">
-        <v>-52.58</v>
+        <v>-528.2349853515625</v>
       </c>
       <c r="G15">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1756,19 +1771,19 @@
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E16">
-        <v>-332.7950134277344</v>
+        <v>-378.3500061035156</v>
       </c>
       <c r="G16">
         <v>2</v>
       </c>
       <c r="H16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J16" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1779,24 +1794,24 @@
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E17">
-        <v>-733.2050170898438</v>
+        <v>-546</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J17" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -1805,157 +1820,226 @@
         <v>42</v>
       </c>
       <c r="E18">
-        <v>-406.4700012207031</v>
+        <v>-52.58</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H18" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J18" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E19">
-        <v>-186.384994506836</v>
+        <v>-332.7950134277344</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H19" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J19" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E20">
-        <v>-290</v>
+        <v>-733.2050170898438</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J20" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s">
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E21">
-        <v>-636.4500122070312</v>
+        <v>-406.4700012207031</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J21" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E22">
-        <v>-124.1699981689453</v>
+        <v>-186.384994506836</v>
       </c>
       <c r="G22">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H22" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J22" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="E23">
-        <v>-236.0549926757812</v>
+        <v>-290</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J23" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
         <v>2</v>
       </c>
-      <c r="C24">
+      <c r="D24" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24">
+        <v>-636.4500122070312</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>47</v>
+      </c>
+      <c r="J24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25">
+        <v>-124.1699981689453</v>
+      </c>
+      <c r="G25">
+        <v>8</v>
+      </c>
+      <c r="H25" t="s">
+        <v>47</v>
+      </c>
+      <c r="J25" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26">
+        <v>-236.0549926757812</v>
+      </c>
+      <c r="G26">
+        <v>4</v>
+      </c>
+      <c r="H26" t="s">
+        <v>47</v>
+      </c>
+      <c r="J26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27">
         <v>10000</v>
       </c>
-      <c r="H24" t="s">
-        <v>45</v>
-      </c>
-      <c r="J24" t="s">
-        <v>68</v>
+      <c r="H27" t="s">
+        <v>48</v>
+      </c>
+      <c r="J27" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B24">
+  <conditionalFormatting sqref="B2:B27">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>$B2="option"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C24">
+  <conditionalFormatting sqref="C2:C27">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1963,7 +2047,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E24">
+  <conditionalFormatting sqref="E2:E27">
     <cfRule type="cellIs" dxfId="4" priority="4" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1971,7 +2055,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F24">
+  <conditionalFormatting sqref="F2:F27">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1979,7 +2063,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G24">
+  <conditionalFormatting sqref="G2:G27">
     <cfRule type="cellIs" dxfId="4" priority="8" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -1993,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:GA12"/>
+  <dimension ref="A1:GA13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="26" width="10.7109375" customWidth="1"/>
@@ -2001,10 +2085,10 @@
   <sheetData>
     <row r="1" spans="1:183">
       <c r="A1" s="3" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>3</v>
@@ -2013,573 +2097,573 @@
         <v>8</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="AL1" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="BE1" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="BF1" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="BL1" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="BM1" s="3" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="BN1" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="BO1" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="BP1" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="BQ1" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="BR1" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="BS1" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="BT1" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="BU1" s="3" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="BV1" s="3" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="BW1" s="3" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="BX1" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="BY1" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="BZ1" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="CA1" s="3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="CB1" s="3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="CC1" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="CD1" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="CE1" s="3" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="CF1" s="3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="CH1" s="3" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="CI1" s="3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="CJ1" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="CK1" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="CL1" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="CM1" s="3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="CN1" s="3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="CO1" s="3" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="CP1" s="3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="CQ1" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="CR1" s="3" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="CS1" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="CT1" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="CU1" s="3" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="CV1" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="CW1" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="CX1" s="3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="CY1" s="3" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="CZ1" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="DA1" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="DB1" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="DC1" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="DD1" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="DE1" s="3" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="DF1" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="DG1" s="3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="DH1" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="DI1" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="DJ1" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="DK1" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="DL1" s="3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="DM1" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="DN1" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="DO1" s="3" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="DP1" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="DQ1" s="3" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="DR1" s="3" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="DS1" s="3" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="DT1" s="3" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="DU1" s="3" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="DV1" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="DW1" s="3" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="DX1" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="DY1" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="DZ1" s="3" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="EA1" s="3" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="EB1" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="EC1" s="3" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="ED1" s="3" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="EE1" s="3" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="EF1" s="3" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="EG1" s="3" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="EH1" s="3" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="EI1" s="3" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="EJ1" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="EK1" s="3" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="EL1" s="3" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="EM1" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="EN1" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="EO1" s="3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="EP1" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EQ1" s="3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="ER1" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="ES1" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="ET1" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="EU1" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="EV1" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="EW1" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="EX1" s="3" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="EY1" s="3" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="EZ1" s="3" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="FA1" s="3" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="FB1" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="FC1" s="3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="FD1" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="FE1" s="3" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="FF1" s="3" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="FG1" s="3" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="FH1" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="FI1" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="FJ1" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="FK1" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="FL1" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="FM1" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="FN1" s="3" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="FO1" s="3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="FP1" s="3" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="FQ1" s="3" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="FR1" s="3" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="FS1" s="3" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="FT1" s="3" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="FU1" s="3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="FV1" s="3" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="FW1" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="FX1" s="3" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="FY1" s="3" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="FZ1" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="GA1" s="3" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" spans="1:183">
       <c r="A2" s="9" t="s">
-        <v>250</v>
+        <v>17</v>
       </c>
       <c r="B2">
-        <v>9542.835049995636</v>
+        <v>9649.346591552185</v>
       </c>
       <c r="C2">
-        <v>-130.2149454267276</v>
+        <v>626.2866321405636</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1506.104006561279</v>
       </c>
       <c r="E2">
         <v>10000</v>
       </c>
       <c r="F2">
-        <v>-0.0457164950004364</v>
+        <v>-0.03506534084478152</v>
       </c>
       <c r="G2">
-        <v>2.099001385498049</v>
+        <v>2.246599041748047</v>
       </c>
       <c r="H2">
-        <v>0.00413048691284505</v>
+        <v>0.008164763653475111</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>342.9400024414062</v>
+        <v>348.2200012207031</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2588,16 +2672,16 @@
         <v>2</v>
       </c>
       <c r="N2">
-        <v>10.14498901367188</v>
+        <v>15.42498779296875</v>
       </c>
       <c r="O2">
-        <v>0.03048419779244926</v>
+        <v>0.04634981646537883</v>
       </c>
       <c r="P2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>533.52001953125</v>
+        <v>521.0800170898438</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -2606,34 +2690,34 @@
         <v>1</v>
       </c>
       <c r="U2">
-        <v>5.2850341796875</v>
+        <v>-7.15496826171875</v>
       </c>
       <c r="V2">
-        <v>0.01000508168948722</v>
+        <v>-0.0135450480565138</v>
       </c>
       <c r="W2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>344.1799926757812</v>
+        <v>330.2049865722656</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AA2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>-12.1199951171875</v>
+        <v>-26.09500122070312</v>
       </c>
       <c r="AC2">
-        <v>-0.03401626587826301</v>
+        <v>-0.07323884960632066</v>
       </c>
       <c r="AD2">
         <v>1</v>
       </c>
       <c r="AF2">
-        <v>262.4500122070312</v>
+        <v>250.3800048828125</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -2642,16 +2726,16 @@
         <v>3</v>
       </c>
       <c r="AI2">
-        <v>6.1500244140625</v>
+        <v>-5.91998291015625</v>
       </c>
       <c r="AJ2">
-        <v>0.02399541438538932</v>
+        <v>-0.02309786653184798</v>
       </c>
       <c r="AK2">
         <v>1</v>
       </c>
       <c r="AM2">
-        <v>705.4400024414062</v>
+        <v>648.8499755859375</v>
       </c>
       <c r="AN2">
         <v>0</v>
@@ -2660,16 +2744,16 @@
         <v>1</v>
       </c>
       <c r="AP2">
-        <v>-27.7650146484375</v>
+        <v>-84.35504150390625</v>
       </c>
       <c r="AQ2">
-        <v>-0.03786800963070236</v>
+        <v>-0.1150497330729118</v>
       </c>
       <c r="AR2">
         <v>1</v>
       </c>
       <c r="AT2">
-        <v>368.0599975585938</v>
+        <v>374.5799865722656</v>
       </c>
       <c r="AU2">
         <v>0</v>
@@ -2678,10 +2762,10 @@
         <v>2</v>
       </c>
       <c r="AW2">
-        <v>-10.29000854492188</v>
+        <v>-3.77001953125</v>
       </c>
       <c r="AX2">
-        <v>-0.02719706192394389</v>
+        <v>-0.009964370213908613</v>
       </c>
       <c r="AY2">
         <v>0</v>
@@ -2705,7 +2789,7 @@
         <v>1</v>
       </c>
       <c r="BO2">
-        <v>56.5099983215332</v>
+        <v>57.53499984741211</v>
       </c>
       <c r="BP2">
         <v>0</v>
@@ -2714,19 +2798,28 @@
         <v>18</v>
       </c>
       <c r="BR2">
-        <v>3.929998321533205</v>
+        <v>4.954999847412111</v>
       </c>
       <c r="BS2">
-        <v>0.07474321646126292</v>
+        <v>0.09423734970353959</v>
       </c>
       <c r="BT2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BV2">
+        <v>270.5499877929688</v>
       </c>
       <c r="BW2">
         <v>0</v>
       </c>
       <c r="BX2">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="BY2">
+        <v>20.71998596191406</v>
+      </c>
+      <c r="BZ2">
+        <v>0.08293633995137939</v>
       </c>
       <c r="CA2">
         <v>0</v>
@@ -2747,28 +2840,28 @@
         <v>0</v>
       </c>
       <c r="CO2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ2">
-        <v>106.5</v>
+        <v>105.7399978637695</v>
       </c>
       <c r="CR2">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="CS2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CT2">
-        <v>-10.26999664306641</v>
+        <v>-11.02999877929689</v>
       </c>
       <c r="CU2">
-        <v>-0.08795064604188474</v>
+        <v>-0.09445918554757304</v>
       </c>
       <c r="CV2">
         <v>1</v>
       </c>
       <c r="CX2">
-        <v>995.530029296875</v>
+        <v>1018.210021972656</v>
       </c>
       <c r="CY2">
         <v>0</v>
@@ -2777,10 +2870,10 @@
         <v>1</v>
       </c>
       <c r="DA2">
-        <v>50.530029296875</v>
+        <v>73.21002197265625</v>
       </c>
       <c r="DB2">
-        <v>0.05347093047288354</v>
+        <v>0.07747092272238754</v>
       </c>
       <c r="DC2">
         <v>0</v>
@@ -2822,7 +2915,7 @@
         <v>1</v>
       </c>
       <c r="EG2">
-        <v>276.1499938964844</v>
+        <v>279.5</v>
       </c>
       <c r="EH2">
         <v>0</v>
@@ -2831,16 +2924,16 @@
         <v>3</v>
       </c>
       <c r="EJ2">
-        <v>-13.85000610351562</v>
+        <v>-10.5</v>
       </c>
       <c r="EK2">
-        <v>-0.04775864173626077</v>
+        <v>-0.03620689655172415</v>
       </c>
       <c r="EL2">
         <v>1</v>
       </c>
       <c r="EN2">
-        <v>325.6199951171875</v>
+        <v>354.8999938964844</v>
       </c>
       <c r="EO2">
         <v>0</v>
@@ -2849,10 +2942,10 @@
         <v>3</v>
       </c>
       <c r="EQ2">
-        <v>24.01998901367188</v>
+        <v>53.29998779296875</v>
       </c>
       <c r="ER2">
-        <v>0.07964187177578408</v>
+        <v>0.176724093880406</v>
       </c>
       <c r="ES2">
         <v>0</v>
@@ -2876,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="FI2">
-        <v>433.1799926757813</v>
+        <v>443.8500061035156</v>
       </c>
       <c r="FJ2">
         <v>0</v>
@@ -2885,10 +2978,10 @@
         <v>2</v>
       </c>
       <c r="FL2">
-        <v>26.70999145507818</v>
+        <v>37.3800048828125</v>
       </c>
       <c r="FM2">
-        <v>0.06571208545492468</v>
+        <v>0.09196251819458645</v>
       </c>
       <c r="FN2">
         <v>0</v>
@@ -2911,28 +3004,22 @@
     </row>
     <row r="3" spans="1:183">
       <c r="A3" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>9462.825070747589</v>
+        <v>9603.382637786315</v>
       </c>
       <c r="C3">
-        <v>-130.2149454267276</v>
+        <v>-879.8173744207156</v>
       </c>
       <c r="D3">
-        <v>866.1100542358397</v>
+        <v>-749.602428993988</v>
       </c>
       <c r="E3">
         <v>10000</v>
       </c>
       <c r="F3">
-        <v>-0.05371749292524108</v>
-      </c>
-      <c r="G3">
-        <v>-0.7797998046875012</v>
-      </c>
-      <c r="H3">
-        <v>-0.003303466687351735</v>
+        <v>-0.03966173622136848</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -2991,20 +3078,11 @@
       <c r="AY3">
         <v>0</v>
       </c>
-      <c r="BA3">
-        <v>216.5599975585937</v>
-      </c>
       <c r="BB3">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="BC3">
         <v>0</v>
-      </c>
-      <c r="BD3">
-        <v>-19.49499511718753</v>
-      </c>
-      <c r="BE3">
-        <v>-0.08258666718379337</v>
       </c>
       <c r="BF3">
         <v>0</v>
@@ -3025,13 +3103,16 @@
         <v>18</v>
       </c>
       <c r="BT3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BU3">
+        <v>-249.8300018310547</v>
       </c>
       <c r="BW3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BX3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CA3">
         <v>0</v>
@@ -3171,28 +3252,28 @@
     </row>
     <row r="4" spans="1:183">
       <c r="A4" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4">
-        <v>9589.634938386749</v>
+        <v>9462.825070747589</v>
       </c>
       <c r="C4">
-        <v>-996.3249996625673</v>
+        <v>-130.2149454267276</v>
       </c>
       <c r="D4">
-        <v>1385.96205741272</v>
+        <v>866.1100542358397</v>
       </c>
       <c r="E4">
         <v>10000</v>
       </c>
       <c r="F4">
-        <v>-0.04103650616132504</v>
+        <v>-0.05371749292524108</v>
       </c>
       <c r="G4">
-        <v>-4.556200561523439</v>
+        <v>-0.7797998046875012</v>
       </c>
       <c r="H4">
-        <v>-0.009750089622943738</v>
+        <v>-0.003303466687351735</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -3249,13 +3330,22 @@
         <v>2</v>
       </c>
       <c r="AY4">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>216.5599975585937</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="BC4">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>-19.49499511718753</v>
+      </c>
+      <c r="BE4">
+        <v>-0.08258666718379337</v>
       </c>
       <c r="BF4">
         <v>0</v>
@@ -3350,20 +3440,11 @@
       <c r="DX4">
         <v>0</v>
       </c>
-      <c r="DZ4">
-        <v>539.6199951171875</v>
-      </c>
       <c r="EA4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="EB4">
         <v>0</v>
-      </c>
-      <c r="EC4">
-        <v>-96.83001708984375</v>
-      </c>
-      <c r="ED4">
-        <v>-0.1521408048278046</v>
       </c>
       <c r="EE4">
         <v>1</v>
@@ -3395,20 +3476,11 @@
       <c r="EZ4">
         <v>0</v>
       </c>
-      <c r="FB4">
-        <v>169.3099975585938</v>
-      </c>
       <c r="FC4">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="FD4">
         <v>0</v>
-      </c>
-      <c r="FE4">
-        <v>-17.07499694824222</v>
-      </c>
-      <c r="FF4">
-        <v>-0.09161143574578889</v>
       </c>
       <c r="FG4">
         <v>1</v>
@@ -3440,28 +3512,28 @@
     </row>
     <row r="5" spans="1:183">
       <c r="A5" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5">
-        <v>9600.492880668853</v>
+        <v>9589.634938386749</v>
       </c>
       <c r="C5">
-        <v>-2382.287057075287</v>
+        <v>-996.3249996625673</v>
       </c>
       <c r="D5">
-        <v>-450.8538608132935</v>
+        <v>1385.96205741272</v>
       </c>
       <c r="E5">
         <v>10000</v>
       </c>
       <c r="F5">
-        <v>-0.03995071193311472</v>
+        <v>-0.04103650616132504</v>
       </c>
       <c r="G5">
-        <v>-3.674000000000001</v>
+        <v>-4.556200561523439</v>
       </c>
       <c r="H5">
-        <v>-0.006728937728937732</v>
+        <v>-0.009750089622943738</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -3617,13 +3689,22 @@
         <v>0</v>
       </c>
       <c r="DX5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="DZ5">
+        <v>539.6199951171875</v>
       </c>
       <c r="EA5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="EB5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="EC5">
+        <v>-96.83001708984375</v>
+      </c>
+      <c r="ED5">
+        <v>-0.1521408048278046</v>
       </c>
       <c r="EE5">
         <v>1</v>
@@ -3637,11 +3718,8 @@
       <c r="EL5">
         <v>1</v>
       </c>
-      <c r="EM5">
-        <v>-301.6000061035156</v>
-      </c>
       <c r="EO5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="EP5">
         <v>3</v>
@@ -3656,13 +3734,22 @@
         <v>0</v>
       </c>
       <c r="EZ5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="FB5">
+        <v>169.3099975585938</v>
       </c>
       <c r="FC5">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="FD5">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="FE5">
+        <v>-17.07499694824222</v>
+      </c>
+      <c r="FF5">
+        <v>-0.09161143574578889</v>
       </c>
       <c r="FG5">
         <v>1</v>
@@ -3685,46 +3772,37 @@
       <c r="FU5">
         <v>0</v>
       </c>
-      <c r="FW5">
-        <v>454.15</v>
-      </c>
       <c r="FX5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="FY5">
         <v>0</v>
-      </c>
-      <c r="FZ5">
-        <v>-91.85000000000002</v>
-      </c>
-      <c r="GA5">
-        <v>-0.1682234432234433</v>
       </c>
     </row>
     <row r="6" spans="1:183">
       <c r="A6" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>9752.886795803435</v>
+        <v>9600.492880668853</v>
       </c>
       <c r="C6">
-        <v>-1931.433196261994</v>
+        <v>-2382.287057075287</v>
       </c>
       <c r="D6">
-        <v>83.49369374084472</v>
+        <v>-450.8538608132935</v>
       </c>
       <c r="E6">
         <v>10000</v>
       </c>
       <c r="F6">
-        <v>-0.02471132041965651</v>
+        <v>-0.03995071193311472</v>
       </c>
       <c r="G6">
-        <v>-0.9851998901367194</v>
+        <v>-3.674000000000001</v>
       </c>
       <c r="H6">
-        <v>-0.007934282875612668</v>
+        <v>-0.006728937728937732</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -3747,11 +3825,8 @@
       <c r="W6">
         <v>1</v>
       </c>
-      <c r="X6">
-        <v>-356.2999877929688</v>
-      </c>
       <c r="Z6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA6">
         <v>2</v>
@@ -3831,20 +3906,11 @@
       <c r="CH6">
         <v>0</v>
       </c>
-      <c r="CJ6">
-        <v>99.54000091552734</v>
-      </c>
       <c r="CK6">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="CL6">
         <v>0</v>
-      </c>
-      <c r="CM6">
-        <v>-24.62999725341798</v>
-      </c>
-      <c r="CN6">
-        <v>-0.1983570718903167</v>
       </c>
       <c r="CO6">
         <v>1</v>
@@ -3910,13 +3976,16 @@
         <v>3</v>
       </c>
       <c r="EL6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="EM6">
+        <v>-301.6000061035156</v>
       </c>
       <c r="EO6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="EP6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="ES6">
         <v>0</v>
@@ -3955,33 +4024,48 @@
         <v>0</v>
       </c>
       <c r="FU6">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="FW6">
+        <v>454.15</v>
       </c>
       <c r="FX6">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="FY6">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="FZ6">
+        <v>-91.85000000000002</v>
+      </c>
+      <c r="GA6">
+        <v>-0.1682234432234433</v>
       </c>
     </row>
     <row r="7" spans="1:183">
       <c r="A7" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>9804.852986706146</v>
+        <v>9752.886795803435</v>
       </c>
       <c r="C7">
-        <v>-2014.926890002838</v>
+        <v>-1931.433196261994</v>
       </c>
       <c r="D7">
-        <v>-3176.771366113281</v>
+        <v>83.49369374084472</v>
       </c>
       <c r="E7">
         <v>10000</v>
       </c>
       <c r="F7">
-        <v>-0.01951470132938538</v>
+        <v>-0.02471132041965651</v>
+      </c>
+      <c r="G7">
+        <v>-0.9851998901367194</v>
+      </c>
+      <c r="H7">
+        <v>-0.007934282875612668</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -3995,32 +4079,29 @@
       <c r="P7">
         <v>1</v>
       </c>
-      <c r="Q7">
-        <v>-528.2349853515625</v>
-      </c>
       <c r="S7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7">
         <v>1</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>-356.2999877929688</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD7">
         <v>1</v>
       </c>
-      <c r="AE7">
-        <v>-256.2999877929688</v>
-      </c>
       <c r="AG7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH7">
         <v>3</v>
@@ -4089,22 +4170,28 @@
         <v>0</v>
       </c>
       <c r="CH7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="CJ7">
+        <v>99.54000091552734</v>
       </c>
       <c r="CK7">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="CL7">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="CM7">
+        <v>-24.62999725341798</v>
+      </c>
+      <c r="CN7">
+        <v>-0.1983570718903167</v>
       </c>
       <c r="CO7">
         <v>1</v>
       </c>
-      <c r="CP7">
-        <v>-116.7699966430664</v>
-      </c>
       <c r="CR7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CS7">
         <v>8</v>
@@ -4112,11 +4199,8 @@
       <c r="CV7">
         <v>1</v>
       </c>
-      <c r="CW7">
-        <v>-945</v>
-      </c>
       <c r="CY7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CZ7">
         <v>1</v>
@@ -4223,22 +4307,22 @@
     </row>
     <row r="8" spans="1:183">
       <c r="A8" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8">
-        <v>9904.144532567963</v>
+        <v>9804.852986706146</v>
       </c>
       <c r="C8">
-        <v>1161.844476110443</v>
+        <v>-2014.926890002838</v>
       </c>
       <c r="D8">
-        <v>-756.8135172088623</v>
+        <v>-3176.771366113281</v>
       </c>
       <c r="E8">
         <v>10000</v>
       </c>
       <c r="F8">
-        <v>-0.009585546743203666</v>
+        <v>-0.01951470132938538</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -4250,13 +4334,16 @@
         <v>2</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>-528.2349853515625</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8">
         <v>0</v>
@@ -4268,13 +4355,16 @@
         <v>0</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>-256.2999877929688</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK8">
         <v>1</v>
@@ -4288,11 +4378,8 @@
       <c r="AR8">
         <v>1</v>
       </c>
-      <c r="AS8">
-        <v>-378.3500061035156</v>
-      </c>
       <c r="AU8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV8">
         <v>2</v>
@@ -4352,22 +4439,28 @@
         <v>8</v>
       </c>
       <c r="CO8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CP8">
+        <v>-116.7699966430664</v>
       </c>
       <c r="CR8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CS8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CV8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CW8">
+        <v>-945</v>
       </c>
       <c r="CY8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CZ8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC8">
         <v>0</v>
@@ -4471,22 +4564,22 @@
     </row>
     <row r="9" spans="1:183">
       <c r="A9" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9">
-        <v>9950.788089754853</v>
+        <v>9904.144532567963</v>
       </c>
       <c r="C9">
-        <v>1918.657993319305</v>
+        <v>1161.844476110443</v>
       </c>
       <c r="D9">
-        <v>-546.0819</v>
+        <v>-756.8135172088623</v>
       </c>
       <c r="E9">
         <v>10000</v>
       </c>
       <c r="F9">
-        <v>-0.004921191024514715</v>
+        <v>-0.009585546743203666</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -4534,13 +4627,16 @@
         <v>1</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AS9">
+        <v>-378.3500061035156</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY9">
         <v>1</v>
@@ -4707,11 +4803,8 @@
       <c r="FU9">
         <v>1</v>
       </c>
-      <c r="FV9">
-        <v>-546</v>
-      </c>
       <c r="FX9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FY9">
         <v>1</v>
@@ -4719,31 +4812,28 @@
     </row>
     <row r="10" spans="1:183">
       <c r="A10" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10">
-        <v>9970.279909493622</v>
+        <v>9950.788089754853</v>
       </c>
       <c r="C10">
-        <v>2464.739893319305</v>
+        <v>1918.657993319305</v>
       </c>
       <c r="D10">
-        <v>-1612.271831359497</v>
+        <v>-546.0819</v>
       </c>
       <c r="E10">
         <v>10000</v>
       </c>
       <c r="F10">
-        <v>-0.00297200905063788</v>
+        <v>-0.004921191024514715</v>
       </c>
       <c r="I10">
         <v>1</v>
       </c>
-      <c r="J10">
-        <v>-332.7950134277344</v>
-      </c>
       <c r="L10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10">
         <v>2</v>
@@ -4814,11 +4904,8 @@
       <c r="BM10">
         <v>1</v>
       </c>
-      <c r="BN10">
-        <v>-52.58</v>
-      </c>
       <c r="BP10">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BQ10">
         <v>18</v>
@@ -4959,42 +5046,48 @@
         <v>0</v>
       </c>
       <c r="FU10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FV10">
+        <v>-546</v>
       </c>
       <c r="FX10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FY10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:183">
       <c r="A11" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11">
-        <v>9919.091680733491</v>
+        <v>9970.279909493622</v>
       </c>
       <c r="C11">
-        <v>4077.011724678802</v>
+        <v>2464.739893319305</v>
       </c>
       <c r="D11">
-        <v>-5922.988275321198</v>
+        <v>-1612.271831359497</v>
       </c>
       <c r="E11">
         <v>10000</v>
       </c>
       <c r="F11">
-        <v>-0.008090831926650943</v>
+        <v>-0.00297200905063788</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>-332.7950134277344</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -5026,11 +5119,8 @@
       <c r="AK11">
         <v>1</v>
       </c>
-      <c r="AL11">
-        <v>-733.2050170898438</v>
-      </c>
       <c r="AN11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO11">
         <v>1</v>
@@ -5047,11 +5137,8 @@
       <c r="AY11">
         <v>1</v>
       </c>
-      <c r="AZ11">
-        <v>-236.0549926757812</v>
-      </c>
       <c r="BB11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BC11">
         <v>4</v>
@@ -5066,13 +5153,16 @@
         <v>0</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BN11">
+        <v>-52.58</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BT11">
         <v>0</v>
@@ -5095,11 +5185,8 @@
       <c r="CH11">
         <v>1</v>
       </c>
-      <c r="CI11">
-        <v>-124.1699981689453</v>
-      </c>
       <c r="CK11">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CL11">
         <v>8</v>
@@ -5152,11 +5239,8 @@
       <c r="DX11">
         <v>1</v>
       </c>
-      <c r="DY11">
-        <v>-636.4500122070312</v>
-      </c>
       <c r="EA11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB11">
         <v>1</v>
@@ -5164,11 +5248,8 @@
       <c r="EE11">
         <v>1</v>
       </c>
-      <c r="EF11">
-        <v>-290</v>
-      </c>
       <c r="EH11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="EI11">
         <v>3</v>
@@ -5194,11 +5275,8 @@
       <c r="EZ11">
         <v>1</v>
       </c>
-      <c r="FA11">
-        <v>-186.384994506836</v>
-      </c>
       <c r="FC11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="FD11">
         <v>5</v>
@@ -5206,11 +5284,8 @@
       <c r="FG11">
         <v>1</v>
       </c>
-      <c r="FH11">
-        <v>-406.4700012207031</v>
-      </c>
       <c r="FJ11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="FK11">
         <v>2</v>
@@ -5236,22 +5311,22 @@
     </row>
     <row r="12" spans="1:183">
       <c r="A12" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12">
-        <v>10000</v>
+        <v>9919.091680733491</v>
       </c>
       <c r="C12">
-        <v>10000</v>
+        <v>4077.011724678802</v>
       </c>
       <c r="D12">
-        <v>10000</v>
+        <v>-5922.988275321198</v>
       </c>
       <c r="E12">
         <v>10000</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>-0.008090831926650943</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -5290,13 +5365,16 @@
         <v>0</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AL12">
+        <v>-733.2050170898438</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -5308,13 +5386,16 @@
         <v>0</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AZ12">
+        <v>-236.0549926757812</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF12">
         <v>0</v>
@@ -5353,13 +5434,16 @@
         <v>0</v>
       </c>
       <c r="CH12">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CI12">
+        <v>-124.1699981689453</v>
       </c>
       <c r="CK12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CL12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CO12">
         <v>0</v>
@@ -5407,22 +5491,28 @@
         <v>0</v>
       </c>
       <c r="DX12">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="DY12">
+        <v>-636.4500122070312</v>
       </c>
       <c r="EA12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EB12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EE12">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="EF12">
+        <v>-290</v>
       </c>
       <c r="EH12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="EI12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="EL12">
         <v>0</v>
@@ -5443,22 +5533,28 @@
         <v>0</v>
       </c>
       <c r="EZ12">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FA12">
+        <v>-186.384994506836</v>
       </c>
       <c r="FC12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="FD12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="FG12">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="FH12">
+        <v>-406.4700012207031</v>
       </c>
       <c r="FJ12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="FK12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="FN12">
         <v>0</v>
@@ -5476,11 +5572,256 @@
         <v>0</v>
       </c>
       <c r="FY12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:183">
+      <c r="A13" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13">
+        <v>10000</v>
+      </c>
+      <c r="C13">
+        <v>10000</v>
+      </c>
+      <c r="D13">
+        <v>10000</v>
+      </c>
+      <c r="E13">
+        <v>10000</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CD13">
+        <v>0</v>
+      </c>
+      <c r="CE13">
+        <v>0</v>
+      </c>
+      <c r="CH13">
+        <v>0</v>
+      </c>
+      <c r="CK13">
+        <v>0</v>
+      </c>
+      <c r="CL13">
+        <v>0</v>
+      </c>
+      <c r="CO13">
+        <v>0</v>
+      </c>
+      <c r="CR13">
+        <v>0</v>
+      </c>
+      <c r="CS13">
+        <v>0</v>
+      </c>
+      <c r="CV13">
+        <v>0</v>
+      </c>
+      <c r="CY13">
+        <v>0</v>
+      </c>
+      <c r="CZ13">
+        <v>0</v>
+      </c>
+      <c r="DC13">
+        <v>0</v>
+      </c>
+      <c r="DF13">
+        <v>0</v>
+      </c>
+      <c r="DG13">
+        <v>0</v>
+      </c>
+      <c r="DJ13">
+        <v>0</v>
+      </c>
+      <c r="DM13">
+        <v>0</v>
+      </c>
+      <c r="DN13">
+        <v>0</v>
+      </c>
+      <c r="DQ13">
+        <v>0</v>
+      </c>
+      <c r="DT13">
+        <v>0</v>
+      </c>
+      <c r="DU13">
+        <v>0</v>
+      </c>
+      <c r="DX13">
+        <v>0</v>
+      </c>
+      <c r="EA13">
+        <v>0</v>
+      </c>
+      <c r="EB13">
+        <v>0</v>
+      </c>
+      <c r="EE13">
+        <v>0</v>
+      </c>
+      <c r="EH13">
+        <v>0</v>
+      </c>
+      <c r="EI13">
+        <v>0</v>
+      </c>
+      <c r="EL13">
+        <v>0</v>
+      </c>
+      <c r="EO13">
+        <v>0</v>
+      </c>
+      <c r="EP13">
+        <v>0</v>
+      </c>
+      <c r="ES13">
+        <v>0</v>
+      </c>
+      <c r="EV13">
+        <v>0</v>
+      </c>
+      <c r="EW13">
+        <v>0</v>
+      </c>
+      <c r="EZ13">
+        <v>0</v>
+      </c>
+      <c r="FC13">
+        <v>0</v>
+      </c>
+      <c r="FD13">
+        <v>0</v>
+      </c>
+      <c r="FG13">
+        <v>0</v>
+      </c>
+      <c r="FJ13">
+        <v>0</v>
+      </c>
+      <c r="FK13">
+        <v>0</v>
+      </c>
+      <c r="FN13">
+        <v>0</v>
+      </c>
+      <c r="FQ13">
+        <v>0</v>
+      </c>
+      <c r="FR13">
+        <v>0</v>
+      </c>
+      <c r="FU13">
+        <v>0</v>
+      </c>
+      <c r="FX13">
+        <v>0</v>
+      </c>
+      <c r="FY13">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AA2:AA12">
+  <conditionalFormatting sqref="AA2:AA13">
     <cfRule type="cellIs" dxfId="4" priority="25" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5488,7 +5829,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE2:AE12">
+  <conditionalFormatting sqref="AE2:AE13">
     <cfRule type="cellIs" dxfId="4" priority="27" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5496,7 +5837,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF2:AF12">
+  <conditionalFormatting sqref="AF2:AF13">
     <cfRule type="cellIs" dxfId="4" priority="29" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5504,7 +5845,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG2:AG12">
+  <conditionalFormatting sqref="AG2:AG13">
     <cfRule type="cellIs" dxfId="4" priority="31" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5512,7 +5853,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH2:AH12">
+  <conditionalFormatting sqref="AH2:AH13">
     <cfRule type="cellIs" dxfId="4" priority="33" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5520,7 +5861,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL2:AL12">
+  <conditionalFormatting sqref="AL2:AL13">
     <cfRule type="cellIs" dxfId="4" priority="35" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5528,7 +5869,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM2:AM12">
+  <conditionalFormatting sqref="AM2:AM13">
     <cfRule type="cellIs" dxfId="4" priority="37" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5536,7 +5877,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AN2:AN12">
+  <conditionalFormatting sqref="AN2:AN13">
     <cfRule type="cellIs" dxfId="4" priority="39" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5544,7 +5885,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AO2:AO12">
+  <conditionalFormatting sqref="AO2:AO13">
     <cfRule type="cellIs" dxfId="4" priority="41" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5552,7 +5893,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AS2:AS12">
+  <conditionalFormatting sqref="AS2:AS13">
     <cfRule type="cellIs" dxfId="4" priority="43" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5560,7 +5901,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AT2:AT12">
+  <conditionalFormatting sqref="AT2:AT13">
     <cfRule type="cellIs" dxfId="4" priority="45" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5568,7 +5909,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU2:AU12">
+  <conditionalFormatting sqref="AU2:AU13">
     <cfRule type="cellIs" dxfId="4" priority="47" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5576,7 +5917,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AV2:AV12">
+  <conditionalFormatting sqref="AV2:AV13">
     <cfRule type="cellIs" dxfId="4" priority="49" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5584,7 +5925,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AZ2:AZ12">
+  <conditionalFormatting sqref="AZ2:AZ13">
     <cfRule type="cellIs" dxfId="4" priority="51" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5592,7 +5933,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BA2:BA12">
+  <conditionalFormatting sqref="BA2:BA13">
     <cfRule type="cellIs" dxfId="4" priority="53" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5600,7 +5941,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB2:BB12">
+  <conditionalFormatting sqref="BB2:BB13">
     <cfRule type="cellIs" dxfId="4" priority="55" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5608,7 +5949,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BC2:BC12">
+  <conditionalFormatting sqref="BC2:BC13">
     <cfRule type="cellIs" dxfId="4" priority="57" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5616,7 +5957,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BG2:BG12">
+  <conditionalFormatting sqref="BG2:BG13">
     <cfRule type="cellIs" dxfId="4" priority="59" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5624,7 +5965,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BH2:BH12">
+  <conditionalFormatting sqref="BH2:BH13">
     <cfRule type="cellIs" dxfId="4" priority="61" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5632,7 +5973,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BI2:BI12">
+  <conditionalFormatting sqref="BI2:BI13">
     <cfRule type="cellIs" dxfId="4" priority="63" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5640,7 +5981,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BJ2:BJ12">
+  <conditionalFormatting sqref="BJ2:BJ13">
     <cfRule type="cellIs" dxfId="4" priority="65" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5648,7 +5989,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BN2:BN12">
+  <conditionalFormatting sqref="BN2:BN13">
     <cfRule type="cellIs" dxfId="4" priority="67" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5656,7 +5997,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BO2:BO12">
+  <conditionalFormatting sqref="BO2:BO13">
     <cfRule type="cellIs" dxfId="4" priority="69" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5664,7 +6005,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BP2:BP12">
+  <conditionalFormatting sqref="BP2:BP13">
     <cfRule type="cellIs" dxfId="4" priority="71" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5672,7 +6013,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BQ2:BQ12">
+  <conditionalFormatting sqref="BQ2:BQ13">
     <cfRule type="cellIs" dxfId="4" priority="73" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5680,7 +6021,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BU2:BU12">
+  <conditionalFormatting sqref="BU2:BU13">
     <cfRule type="cellIs" dxfId="4" priority="75" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5688,7 +6029,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BV2:BV12">
+  <conditionalFormatting sqref="BV2:BV13">
     <cfRule type="cellIs" dxfId="4" priority="77" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5696,7 +6037,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BW2:BW12">
+  <conditionalFormatting sqref="BW2:BW13">
     <cfRule type="cellIs" dxfId="4" priority="79" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5704,7 +6045,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BX2:BX12">
+  <conditionalFormatting sqref="BX2:BX13">
     <cfRule type="cellIs" dxfId="4" priority="81" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5712,7 +6053,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CB2:CB12">
+  <conditionalFormatting sqref="CB2:CB13">
     <cfRule type="cellIs" dxfId="4" priority="83" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5720,7 +6061,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CC2:CC12">
+  <conditionalFormatting sqref="CC2:CC13">
     <cfRule type="cellIs" dxfId="4" priority="85" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5728,7 +6069,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CD2:CD12">
+  <conditionalFormatting sqref="CD2:CD13">
     <cfRule type="cellIs" dxfId="4" priority="87" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5736,7 +6077,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CE2:CE12">
+  <conditionalFormatting sqref="CE2:CE13">
     <cfRule type="cellIs" dxfId="4" priority="89" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5744,7 +6085,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CI2:CI12">
+  <conditionalFormatting sqref="CI2:CI13">
     <cfRule type="cellIs" dxfId="4" priority="91" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5752,7 +6093,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CJ2:CJ12">
+  <conditionalFormatting sqref="CJ2:CJ13">
     <cfRule type="cellIs" dxfId="4" priority="93" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5760,7 +6101,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CK2:CK12">
+  <conditionalFormatting sqref="CK2:CK13">
     <cfRule type="cellIs" dxfId="4" priority="95" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5768,7 +6109,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CL2:CL12">
+  <conditionalFormatting sqref="CL2:CL13">
     <cfRule type="cellIs" dxfId="4" priority="97" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5776,7 +6117,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CP2:CP12">
+  <conditionalFormatting sqref="CP2:CP13">
     <cfRule type="cellIs" dxfId="4" priority="99" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5784,7 +6125,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CQ2:CQ12">
+  <conditionalFormatting sqref="CQ2:CQ13">
     <cfRule type="cellIs" dxfId="4" priority="101" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5792,7 +6133,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CR2:CR12">
+  <conditionalFormatting sqref="CR2:CR13">
     <cfRule type="cellIs" dxfId="4" priority="103" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5800,7 +6141,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CS2:CS12">
+  <conditionalFormatting sqref="CS2:CS13">
     <cfRule type="cellIs" dxfId="4" priority="105" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5808,7 +6149,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CW2:CW12">
+  <conditionalFormatting sqref="CW2:CW13">
     <cfRule type="cellIs" dxfId="4" priority="107" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5816,7 +6157,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CX2:CX12">
+  <conditionalFormatting sqref="CX2:CX13">
     <cfRule type="cellIs" dxfId="4" priority="109" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5824,7 +6165,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CY2:CY12">
+  <conditionalFormatting sqref="CY2:CY13">
     <cfRule type="cellIs" dxfId="4" priority="111" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5832,7 +6173,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CZ2:CZ12">
+  <conditionalFormatting sqref="CZ2:CZ13">
     <cfRule type="cellIs" dxfId="4" priority="113" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5840,7 +6181,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D12">
+  <conditionalFormatting sqref="D2:D13">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5848,7 +6189,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DD2:DD12">
+  <conditionalFormatting sqref="DD2:DD13">
     <cfRule type="cellIs" dxfId="4" priority="115" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5856,7 +6197,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DE2:DE12">
+  <conditionalFormatting sqref="DE2:DE13">
     <cfRule type="cellIs" dxfId="4" priority="117" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5864,7 +6205,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DF2:DF12">
+  <conditionalFormatting sqref="DF2:DF13">
     <cfRule type="cellIs" dxfId="4" priority="119" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5872,7 +6213,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DG2:DG12">
+  <conditionalFormatting sqref="DG2:DG13">
     <cfRule type="cellIs" dxfId="4" priority="121" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5880,7 +6221,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DK2:DK12">
+  <conditionalFormatting sqref="DK2:DK13">
     <cfRule type="cellIs" dxfId="4" priority="123" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5888,7 +6229,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DL2:DL12">
+  <conditionalFormatting sqref="DL2:DL13">
     <cfRule type="cellIs" dxfId="4" priority="125" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5896,7 +6237,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DM2:DM12">
+  <conditionalFormatting sqref="DM2:DM13">
     <cfRule type="cellIs" dxfId="4" priority="127" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5904,7 +6245,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DN2:DN12">
+  <conditionalFormatting sqref="DN2:DN13">
     <cfRule type="cellIs" dxfId="4" priority="129" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5912,7 +6253,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DR2:DR12">
+  <conditionalFormatting sqref="DR2:DR13">
     <cfRule type="cellIs" dxfId="4" priority="131" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5920,7 +6261,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DS2:DS12">
+  <conditionalFormatting sqref="DS2:DS13">
     <cfRule type="cellIs" dxfId="4" priority="133" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5928,7 +6269,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DT2:DT12">
+  <conditionalFormatting sqref="DT2:DT13">
     <cfRule type="cellIs" dxfId="4" priority="135" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5936,7 +6277,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DU2:DU12">
+  <conditionalFormatting sqref="DU2:DU13">
     <cfRule type="cellIs" dxfId="4" priority="137" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5944,7 +6285,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DY2:DY12">
+  <conditionalFormatting sqref="DY2:DY13">
     <cfRule type="cellIs" dxfId="4" priority="139" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5952,7 +6293,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DZ2:DZ12">
+  <conditionalFormatting sqref="DZ2:DZ13">
     <cfRule type="cellIs" dxfId="4" priority="141" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5960,7 +6301,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EA2:EA12">
+  <conditionalFormatting sqref="EA2:EA13">
     <cfRule type="cellIs" dxfId="4" priority="143" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5968,7 +6309,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EB2:EB12">
+  <conditionalFormatting sqref="EB2:EB13">
     <cfRule type="cellIs" dxfId="4" priority="145" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5976,7 +6317,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EF2:EF12">
+  <conditionalFormatting sqref="EF2:EF13">
     <cfRule type="cellIs" dxfId="4" priority="147" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5984,7 +6325,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EG2:EG12">
+  <conditionalFormatting sqref="EG2:EG13">
     <cfRule type="cellIs" dxfId="4" priority="149" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -5992,7 +6333,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EH2:EH12">
+  <conditionalFormatting sqref="EH2:EH13">
     <cfRule type="cellIs" dxfId="4" priority="151" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6000,7 +6341,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EI2:EI12">
+  <conditionalFormatting sqref="EI2:EI13">
     <cfRule type="cellIs" dxfId="4" priority="153" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6008,7 +6349,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EM2:EM12">
+  <conditionalFormatting sqref="EM2:EM13">
     <cfRule type="cellIs" dxfId="4" priority="155" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6016,7 +6357,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EN2:EN12">
+  <conditionalFormatting sqref="EN2:EN13">
     <cfRule type="cellIs" dxfId="4" priority="157" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6024,7 +6365,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EO2:EO12">
+  <conditionalFormatting sqref="EO2:EO13">
     <cfRule type="cellIs" dxfId="4" priority="159" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6032,7 +6373,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EP2:EP12">
+  <conditionalFormatting sqref="EP2:EP13">
     <cfRule type="cellIs" dxfId="4" priority="161" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6040,7 +6381,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="ET2:ET12">
+  <conditionalFormatting sqref="ET2:ET13">
     <cfRule type="cellIs" dxfId="4" priority="163" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6048,7 +6389,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EU2:EU12">
+  <conditionalFormatting sqref="EU2:EU13">
     <cfRule type="cellIs" dxfId="4" priority="165" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6056,7 +6397,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EV2:EV12">
+  <conditionalFormatting sqref="EV2:EV13">
     <cfRule type="cellIs" dxfId="4" priority="167" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6064,7 +6405,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EW2:EW12">
+  <conditionalFormatting sqref="EW2:EW13">
     <cfRule type="cellIs" dxfId="4" priority="169" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6072,7 +6413,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FA2:FA12">
+  <conditionalFormatting sqref="FA2:FA13">
     <cfRule type="cellIs" dxfId="4" priority="171" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6080,7 +6421,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FB2:FB12">
+  <conditionalFormatting sqref="FB2:FB13">
     <cfRule type="cellIs" dxfId="4" priority="173" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6088,7 +6429,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FC2:FC12">
+  <conditionalFormatting sqref="FC2:FC13">
     <cfRule type="cellIs" dxfId="4" priority="175" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6096,7 +6437,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FD2:FD12">
+  <conditionalFormatting sqref="FD2:FD13">
     <cfRule type="cellIs" dxfId="4" priority="177" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6104,7 +6445,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FH2:FH12">
+  <conditionalFormatting sqref="FH2:FH13">
     <cfRule type="cellIs" dxfId="4" priority="179" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6112,7 +6453,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FI2:FI12">
+  <conditionalFormatting sqref="FI2:FI13">
     <cfRule type="cellIs" dxfId="4" priority="181" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6120,7 +6461,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FJ2:FJ12">
+  <conditionalFormatting sqref="FJ2:FJ13">
     <cfRule type="cellIs" dxfId="4" priority="183" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6128,7 +6469,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FK2:FK12">
+  <conditionalFormatting sqref="FK2:FK13">
     <cfRule type="cellIs" dxfId="4" priority="185" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6136,7 +6477,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FO2:FO12">
+  <conditionalFormatting sqref="FO2:FO13">
     <cfRule type="cellIs" dxfId="4" priority="187" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6144,7 +6485,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FP2:FP12">
+  <conditionalFormatting sqref="FP2:FP13">
     <cfRule type="cellIs" dxfId="4" priority="189" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6152,7 +6493,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FQ2:FQ12">
+  <conditionalFormatting sqref="FQ2:FQ13">
     <cfRule type="cellIs" dxfId="4" priority="191" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6160,7 +6501,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FR2:FR12">
+  <conditionalFormatting sqref="FR2:FR13">
     <cfRule type="cellIs" dxfId="4" priority="193" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6168,7 +6509,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FV2:FV12">
+  <conditionalFormatting sqref="FV2:FV13">
     <cfRule type="cellIs" dxfId="4" priority="195" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6176,7 +6517,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FW2:FW12">
+  <conditionalFormatting sqref="FW2:FW13">
     <cfRule type="cellIs" dxfId="4" priority="197" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6184,7 +6525,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FX2:FX12">
+  <conditionalFormatting sqref="FX2:FX13">
     <cfRule type="cellIs" dxfId="4" priority="199" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6192,7 +6533,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="FY2:FY12">
+  <conditionalFormatting sqref="FY2:FY13">
     <cfRule type="cellIs" dxfId="4" priority="201" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6200,7 +6541,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J12">
+  <conditionalFormatting sqref="J2:J13">
     <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6208,7 +6549,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K12">
+  <conditionalFormatting sqref="K2:K13">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6216,7 +6557,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L12">
+  <conditionalFormatting sqref="L2:L13">
     <cfRule type="cellIs" dxfId="4" priority="7" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6224,7 +6565,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M12">
+  <conditionalFormatting sqref="M2:M13">
     <cfRule type="cellIs" dxfId="4" priority="9" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6232,7 +6573,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q12">
+  <conditionalFormatting sqref="Q2:Q13">
     <cfRule type="cellIs" dxfId="4" priority="11" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6240,7 +6581,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R12">
+  <conditionalFormatting sqref="R2:R13">
     <cfRule type="cellIs" dxfId="4" priority="13" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6248,7 +6589,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S12">
+  <conditionalFormatting sqref="S2:S13">
     <cfRule type="cellIs" dxfId="4" priority="15" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6256,7 +6597,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T12">
+  <conditionalFormatting sqref="T2:T13">
     <cfRule type="cellIs" dxfId="4" priority="17" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6264,7 +6605,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X12">
+  <conditionalFormatting sqref="X2:X13">
     <cfRule type="cellIs" dxfId="4" priority="19" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6272,7 +6613,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y12">
+  <conditionalFormatting sqref="Y2:Y13">
     <cfRule type="cellIs" dxfId="4" priority="21" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -6280,7 +6621,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:Z12">
+  <conditionalFormatting sqref="Z2:Z13">
     <cfRule type="cellIs" dxfId="4" priority="23" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
